--- a/examples/outputs/Birgo RR Exhibits - Maven @ 806v07.01.26.xlsx
+++ b/examples/outputs/Birgo RR Exhibits - Maven @ 806v07.01.26.xlsx
@@ -882,43 +882,43 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>6038</v>
+        <v>16746</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>670.8888888888889</v>
+        <v>644.0769230769231</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>10986</v>
+        <v>30185</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>1220.666666666667</v>
+        <v>1160.961538461539</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>1.819476647896654</v>
+        <v>1.80252000477726</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>10885.3</v>
+        <v>29100.3</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>1209.477777777778</v>
+        <v>1164.012</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>1.802798940046373</v>
+        <v>1.815818045675777</v>
       </c>
       <c r="P6" s="11" t="n">
         <v>1325</v>
       </c>
       <c r="Q6" s="11" t="n">
-        <v>1197</v>
+        <v>4068</v>
       </c>
       <c r="S6" s="10" t="n">
-        <v>6038</v>
+        <v>16026</v>
       </c>
     </row>
     <row r="7">
@@ -929,211 +929,262 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>16436</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>821.8</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>27229</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>1361.45</v>
+      </c>
+      <c r="L7" s="12" t="n">
+        <v>1.656668289121441</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>20761</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>1297.5625</v>
+      </c>
+      <c r="O7" s="12" t="n">
+        <v>1.536599807564207</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>1394</v>
+      </c>
+      <c r="Q7" s="11" t="n">
+        <v>2159</v>
+      </c>
+      <c r="S7" s="10" t="n">
+        <v>13511</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
           <t>2 BD / 2 BA</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F8" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H8" s="10" t="n">
         <v>5194</v>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="I8" s="10" t="n">
         <v>1038.8</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J8" s="11" t="n">
         <v>8795</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K8" s="11" t="n">
         <v>1759</v>
       </c>
-      <c r="L7" s="12" t="n">
+      <c r="L8" s="12" t="n">
         <v>1.693299961494032</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M8" s="11" t="n">
         <v>1799</v>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="N8" s="11" t="n">
         <v>1799</v>
       </c>
-      <c r="O7" s="12" t="n">
+      <c r="O8" s="12" t="n">
         <v>2.131516587677725</v>
       </c>
-      <c r="P7" s="11" t="n">
+      <c r="P8" s="11" t="n">
         <v>1799</v>
       </c>
-      <c r="Q7" s="11" t="n">
-        <v>5164</v>
-      </c>
-      <c r="S7" s="10" t="n">
+      <c r="Q8" s="11" t="n">
+        <v>134</v>
+      </c>
+      <c r="S8" s="10" t="n">
         <v>844</v>
       </c>
     </row>
-    <row r="8">
-      <c r="C8" s="13" t="inlineStr">
+    <row r="9">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Total/Wtd Average</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>11232</v>
-      </c>
-      <c r="I8" s="16" t="n">
-        <v>802.2857142857143</v>
-      </c>
-      <c r="J8" s="17" t="n">
-        <v>19781</v>
-      </c>
-      <c r="K8" s="17" t="n">
-        <v>1412.928571428571</v>
-      </c>
-      <c r="L8" s="18" t="n">
-        <v>1.761128917378917</v>
-      </c>
-      <c r="M8" s="17" t="n">
-        <v>12684.3</v>
-      </c>
-      <c r="N8" s="17" t="n">
-        <v>1268.43</v>
-      </c>
-      <c r="O8" s="18" t="n">
-        <v>1.843112467306016</v>
-      </c>
-      <c r="P8" s="17" t="n">
-        <v>1494.285714285714</v>
-      </c>
-      <c r="Q8" s="17" t="n">
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>51</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>38376</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>752.4705882352941</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>66209</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>1298.21568627451</v>
+      </c>
+      <c r="L9" s="18" t="n">
+        <v>1.725271002710027</v>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>51660.3</v>
+      </c>
+      <c r="N9" s="17" t="n">
+        <v>1230.007142857143</v>
+      </c>
+      <c r="O9" s="18" t="n">
+        <v>1.700414732892268</v>
+      </c>
+      <c r="P9" s="17" t="n">
+        <v>1398.529411764706</v>
+      </c>
+      <c r="Q9" s="17" t="n">
         <v>6361</v>
       </c>
-      <c r="S8" s="16" t="n">
-        <v>6882</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>Total Units</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="21" t="n">
-        <v>14</v>
+      <c r="S9" s="16" t="n">
+        <v>30381</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>Occupied Units</t>
+          <t>Total Units</t>
         </is>
       </c>
       <c r="D11" s="20" t="n"/>
       <c r="E11" s="20" t="n"/>
       <c r="F11" s="20" t="n"/>
       <c r="G11" s="21" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>Unit Occupancy</t>
+          <t>Occupied Units</t>
         </is>
       </c>
       <c r="D12" s="20" t="n"/>
       <c r="E12" s="20" t="n"/>
       <c r="F12" s="20" t="n"/>
-      <c r="G12" s="22" t="n">
-        <v>0.7142857142857143</v>
+      <c r="G12" s="21" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>Total Square Feet</t>
+          <t>Unit Occupancy</t>
         </is>
       </c>
       <c r="D13" s="20" t="n"/>
       <c r="E13" s="20" t="n"/>
       <c r="F13" s="20" t="n"/>
-      <c r="G13" s="23" t="n">
-        <v>11232</v>
+      <c r="G13" s="22" t="n">
+        <v>0.8235294117647058</v>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>Occupied Square Feet</t>
+          <t>Total Square Feet</t>
         </is>
       </c>
       <c r="D14" s="20" t="n"/>
       <c r="E14" s="20" t="n"/>
       <c r="F14" s="20" t="n"/>
       <c r="G14" s="23" t="n">
-        <v>6882</v>
+        <v>38376</v>
       </c>
     </row>
     <row r="15">
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>Square Feet Occupancy</t>
+          <t>Occupied Square Feet</t>
         </is>
       </c>
       <c r="D15" s="20" t="n"/>
       <c r="E15" s="20" t="n"/>
       <c r="F15" s="20" t="n"/>
-      <c r="G15" s="22" t="n">
-        <v>0.6127136752136753</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>Market Rent Annualized</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="20" t="n"/>
-      <c r="G17" s="24" t="n">
-        <v>237372</v>
+      <c r="G15" s="23" t="n">
+        <v>30381</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Square Feet Occupancy</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="20" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="22" t="n">
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="18">
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>In-Place Rent Annualized</t>
+          <t>Market Rent Annualized</t>
         </is>
       </c>
       <c r="D18" s="20" t="n"/>
       <c r="E18" s="20" t="n"/>
       <c r="F18" s="20" t="n"/>
       <c r="G18" s="24" t="n">
-        <v>152211.6</v>
+        <v>794508</v>
       </c>
     </row>
     <row r="19">
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>Other Income Annualized</t>
+          <t>In-Place Rent Annualized</t>
         </is>
       </c>
       <c r="D19" s="20" t="n"/>
       <c r="E19" s="20" t="n"/>
       <c r="F19" s="20" t="n"/>
       <c r="G19" s="24" t="n">
+        <v>619923.6000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>Other Income Annualized</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="24" t="n">
         <v>76332</v>
       </c>
     </row>
@@ -1151,7 +1202,7 @@
         </is>
       </c>
       <c r="W42" s="27" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43">
@@ -1161,7 +1212,7 @@
         </is>
       </c>
       <c r="W43" s="27" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
@@ -1171,7 +1222,7 @@
         </is>
       </c>
       <c r="W44" s="28" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8235294117647058</v>
       </c>
     </row>
     <row r="45">
@@ -1181,7 +1232,7 @@
         </is>
       </c>
       <c r="W45" s="27" t="n">
-        <v>11232</v>
+        <v>38376</v>
       </c>
     </row>
     <row r="46">
@@ -1191,7 +1242,7 @@
         </is>
       </c>
       <c r="W46" s="27" t="n">
-        <v>6882</v>
+        <v>30381</v>
       </c>
     </row>
     <row r="47">
@@ -1201,7 +1252,7 @@
         </is>
       </c>
       <c r="W47" s="28" t="n">
-        <v>0.6127136752136753</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="48">
@@ -1211,7 +1262,7 @@
         </is>
       </c>
       <c r="W48" s="27" t="n">
-        <v>19781</v>
+        <v>66209</v>
       </c>
     </row>
     <row r="49">
@@ -1221,7 +1272,7 @@
         </is>
       </c>
       <c r="W49" s="27" t="n">
-        <v>12684.3</v>
+        <v>51660.3</v>
       </c>
     </row>
     <row r="50">
@@ -1474,52 +1525,52 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>16746</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>644.0769230769231</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>1160.961538461539</v>
+      </c>
+      <c r="K7" s="38" t="n">
+        <v>1167.8</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>1164.012</v>
+      </c>
+      <c r="M7" s="39" t="n">
+        <v>0.9967562938859393</v>
+      </c>
+      <c r="N7" s="38" t="n">
+        <v>1133.53</v>
+      </c>
+      <c r="O7" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>1121.144444444444</v>
+      </c>
+      <c r="Q7" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>6038</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>670.8888888888889</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>1220.666666666667</v>
-      </c>
-      <c r="K7" s="38" t="n">
-        <v>1220.666666666667</v>
-      </c>
-      <c r="L7" s="11" t="n">
-        <v>1209.477777777778</v>
-      </c>
-      <c r="M7" s="39" t="n">
-        <v>0.9908337884580374</v>
-      </c>
-      <c r="N7" s="38" t="n">
-        <v>1173.46</v>
-      </c>
-      <c r="O7" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="P7" s="11" t="n">
-        <v>1173.46</v>
-      </c>
-      <c r="Q7" s="40" t="n">
-        <v>5</v>
-      </c>
       <c r="R7" s="11" t="n">
-        <v>1173.46</v>
+        <v>1140.328571428571</v>
       </c>
       <c r="S7" s="40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7" s="11" t="n">
-        <v>1173.46</v>
+        <v>1142.883333333333</v>
       </c>
       <c r="U7" s="40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V7" s="11" t="n">
         <v>1234.5</v>
@@ -1536,143 +1587,209 @@
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="F8" s="37" t="n">
+        <v>16</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>16436</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>821.8</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>1361.45</v>
+      </c>
+      <c r="K8" s="38" t="n">
+        <v>1363.0625</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>1297.5625</v>
+      </c>
+      <c r="M8" s="39" t="n">
+        <v>0.9519464441285708</v>
+      </c>
+      <c r="N8" s="38" t="n">
+        <v>1302.666666666667</v>
+      </c>
+      <c r="O8" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>1286.4</v>
+      </c>
+      <c r="Q8" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" s="11" t="n">
+        <v>1294.25</v>
+      </c>
+      <c r="S8" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" s="11" t="n">
+        <v>1374.5</v>
+      </c>
+      <c r="U8" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="11" t="n">
+        <v>1355</v>
+      </c>
+      <c r="W8" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
           <t>2 BD / 2 BA</t>
         </is>
       </c>
-      <c r="F8" s="37" t="n">
+      <c r="F9" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H9" s="10" t="n">
         <v>5194</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I9" s="10" t="n">
         <v>1038.8</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J9" s="11" t="n">
         <v>1759</v>
       </c>
-      <c r="K8" s="38" t="n">
+      <c r="K9" s="38" t="n">
         <v>1599</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L9" s="11" t="n">
         <v>1799</v>
       </c>
-      <c r="M8" s="39" t="n">
+      <c r="M9" s="39" t="n">
         <v>1.125078173858662</v>
       </c>
-      <c r="N8" s="38" t="n">
+      <c r="N9" s="38" t="n">
         <v>1799</v>
       </c>
-      <c r="O8" s="40" t="n">
+      <c r="O9" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="P8" s="11" t="inlineStr">
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="Q8" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="11" t="inlineStr">
+      <c r="Q9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="S8" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="11" t="inlineStr">
+      <c r="S9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="11" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="U8" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="11" t="inlineStr">
+      <c r="U9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="11" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="W8" s="40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="C9" s="13" t="inlineStr">
+      <c r="W9" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Total/Wtd Average</t>
         </is>
       </c>
-      <c r="D9" s="41" t="n"/>
-      <c r="E9" s="41" t="n"/>
-      <c r="F9" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" s="15" t="n">
+      <c r="D10" s="41" t="n"/>
+      <c r="E10" s="41" t="n"/>
+      <c r="F10" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>51</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>38376</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>752.4705882352941</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>1298.21568627451</v>
+      </c>
+      <c r="K10" s="42" t="n">
+        <v>1252.452380952381</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <v>1230.007142857143</v>
+      </c>
+      <c r="M10" s="43" t="n">
+        <v>0.9820789688801019</v>
+      </c>
+      <c r="N10" s="42" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="O10" s="44" t="n">
+        <v>17</v>
+      </c>
+      <c r="P10" s="17" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q10" s="44" t="n">
         <v>14</v>
       </c>
-      <c r="H9" s="16" t="n">
-        <v>11232</v>
-      </c>
-      <c r="I9" s="16" t="n">
-        <v>802.2857142857143</v>
-      </c>
-      <c r="J9" s="17" t="n">
-        <v>1412.928571428571</v>
-      </c>
-      <c r="K9" s="42" t="n">
-        <v>1258.5</v>
-      </c>
-      <c r="L9" s="17" t="n">
-        <v>1268.43</v>
-      </c>
-      <c r="M9" s="43" t="n">
-        <v>1.007890345649583</v>
-      </c>
-      <c r="N9" s="42" t="inlineStr">
+      <c r="R10" s="17" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="O9" s="44" t="n">
-        <v>6</v>
-      </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="S10" s="44" t="n">
+        <v>11</v>
+      </c>
+      <c r="T10" s="17" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="Q9" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="U10" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="V10" s="17" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="S9" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" s="17" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="U9" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="V9" s="17" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="W9" s="45" t="n">
-        <v>2</v>
+      <c r="W10" s="45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1689,7 +1806,7 @@
         </is>
       </c>
       <c r="AB59" s="27" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60">
@@ -1699,7 +1816,7 @@
         </is>
       </c>
       <c r="AB60" s="27" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61">
@@ -1709,7 +1826,7 @@
         </is>
       </c>
       <c r="AB61" s="28" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8235294117647058</v>
       </c>
     </row>
     <row r="62">
@@ -1719,7 +1836,7 @@
         </is>
       </c>
       <c r="AB62" s="27" t="n">
-        <v>11232</v>
+        <v>38376</v>
       </c>
     </row>
     <row r="63">
@@ -1729,7 +1846,7 @@
         </is>
       </c>
       <c r="AB63" s="27" t="n">
-        <v>6882</v>
+        <v>30381</v>
       </c>
     </row>
     <row r="64">
@@ -1739,7 +1856,7 @@
         </is>
       </c>
       <c r="AB64" s="28" t="n">
-        <v>0.6127136752136753</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="65">
@@ -1749,7 +1866,7 @@
         </is>
       </c>
       <c r="AB65" s="27" t="n">
-        <v>19781</v>
+        <v>66209</v>
       </c>
     </row>
     <row r="66">
@@ -1759,7 +1876,7 @@
         </is>
       </c>
       <c r="AB66" s="27" t="n">
-        <v>12684.3</v>
+        <v>51660.3</v>
       </c>
     </row>
   </sheetData>
@@ -1913,43 +2030,43 @@
         <v>1</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>6038</v>
+        <v>16746</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>670.8888888888889</v>
+        <v>644.0769230769231</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>10986</v>
+        <v>30185</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>1220.666666666667</v>
+        <v>1160.961538461539</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>1.819476647896654</v>
+        <v>1.80252000477726</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>10885.3</v>
+        <v>29100.3</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>1209.477777777778</v>
+        <v>1164.012</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>1.802798940046373</v>
+        <v>1.815818045675777</v>
       </c>
       <c r="P6" s="11" t="n">
         <v>1325</v>
       </c>
       <c r="Q6" s="11" t="n">
-        <v>1197</v>
+        <v>4068</v>
       </c>
       <c r="S6" s="10" t="n">
-        <v>6038</v>
+        <v>16026</v>
       </c>
     </row>
     <row r="7">
@@ -1962,43 +2079,43 @@
         <v>2</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>5194</v>
+        <v>21630</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1038.8</v>
+        <v>865.2</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>8795</v>
+        <v>36024</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>1759</v>
+        <v>1440.96</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>1.693299961494032</v>
+        <v>1.665464632454924</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>1799</v>
+        <v>22560</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>1799</v>
+        <v>1327.058823529412</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>2.131516587677725</v>
+        <v>1.571577847439916</v>
       </c>
       <c r="P7" s="11" t="n">
         <v>1799</v>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>5164</v>
+        <v>2293</v>
       </c>
       <c r="S7" s="10" t="n">
-        <v>844</v>
+        <v>14355</v>
       </c>
     </row>
     <row r="8">
@@ -2010,34 +2127,34 @@
       <c r="D8" s="13" t="n"/>
       <c r="E8" s="13" t="n"/>
       <c r="F8" s="14" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>11232</v>
+        <v>38376</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>802.2857142857143</v>
+        <v>752.4705882352941</v>
       </c>
       <c r="J8" s="17" t="n">
-        <v>19781</v>
+        <v>66209</v>
       </c>
       <c r="K8" s="17" t="n">
-        <v>1412.928571428571</v>
+        <v>1298.21568627451</v>
       </c>
       <c r="L8" s="18" t="n">
-        <v>1.761128917378917</v>
+        <v>1.725271002710027</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>12684.3</v>
+        <v>51660.3</v>
       </c>
       <c r="N8" s="17" t="n">
-        <v>1268.43</v>
+        <v>1230.007142857143</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>1.843112467306016</v>
+        <v>1.700414732892268</v>
       </c>
       <c r="P8" s="17" t="inlineStr">
         <is>
@@ -2048,7 +2165,7 @@
         <v>6361</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>6882</v>
+        <v>30381</v>
       </c>
     </row>
     <row r="10">
@@ -2061,7 +2178,7 @@
       <c r="E10" s="20" t="n"/>
       <c r="F10" s="20" t="n"/>
       <c r="G10" s="21" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -2074,7 +2191,7 @@
       <c r="E11" s="20" t="n"/>
       <c r="F11" s="20" t="n"/>
       <c r="G11" s="21" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -2087,7 +2204,7 @@
       <c r="E12" s="20" t="n"/>
       <c r="F12" s="20" t="n"/>
       <c r="G12" s="22" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8235294117647058</v>
       </c>
     </row>
     <row r="13">
@@ -2100,7 +2217,7 @@
       <c r="E13" s="20" t="n"/>
       <c r="F13" s="20" t="n"/>
       <c r="G13" s="23" t="n">
-        <v>11232</v>
+        <v>38376</v>
       </c>
     </row>
     <row r="14">
@@ -2113,7 +2230,7 @@
       <c r="E14" s="20" t="n"/>
       <c r="F14" s="20" t="n"/>
       <c r="G14" s="23" t="n">
-        <v>6882</v>
+        <v>30381</v>
       </c>
     </row>
     <row r="15">
@@ -2126,7 +2243,7 @@
       <c r="E15" s="20" t="n"/>
       <c r="F15" s="20" t="n"/>
       <c r="G15" s="22" t="n">
-        <v>0.6127136752136753</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2139,7 +2256,7 @@
       <c r="E17" s="20" t="n"/>
       <c r="F17" s="20" t="n"/>
       <c r="G17" s="24" t="n">
-        <v>237372</v>
+        <v>794508</v>
       </c>
     </row>
     <row r="18">
@@ -2152,7 +2269,7 @@
       <c r="E18" s="20" t="n"/>
       <c r="F18" s="20" t="n"/>
       <c r="G18" s="24" t="n">
-        <v>152211.6</v>
+        <v>619923.6000000001</v>
       </c>
     </row>
     <row r="19">
@@ -2179,7 +2296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:AG22"/>
+  <dimension ref="C3:AG59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="0.9" customWidth="1" min="1" max="1"/>
@@ -3428,63 +3545,2420 @@
         <v>0</v>
       </c>
       <c r="Y21" s="58" t="n">
-        <v>5030</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="60" t="inlineStr">
+      <c r="D22" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E22" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-1</t>
+        </is>
+      </c>
+      <c r="F22" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G22" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K22" s="36" t="inlineStr">
+        <is>
+          <t>Collins, Nancy</t>
+        </is>
+      </c>
+      <c r="L22" s="55" t="n">
+        <v>810</v>
+      </c>
+      <c r="M22" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U22" s="58" t="n">
+        <v>1379</v>
+      </c>
+      <c r="V22" s="58" t="n">
+        <v>1249</v>
+      </c>
+      <c r="W22" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="58" t="n">
+        <v>99</v>
+      </c>
+      <c r="Z22" s="59" t="n">
+        <v>44075</v>
+      </c>
+      <c r="AA22" s="59" t="n">
+        <v>45901</v>
+      </c>
+      <c r="AB22" s="59" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="D23" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E23" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-2</t>
+        </is>
+      </c>
+      <c r="F23" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G23" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K23" s="36" t="inlineStr">
+        <is>
+          <t>Humphrey, Alyson</t>
+        </is>
+      </c>
+      <c r="L23" s="55" t="n">
+        <v>935</v>
+      </c>
+      <c r="M23" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U23" s="58" t="n">
+        <v>1379</v>
+      </c>
+      <c r="V23" s="58" t="n">
+        <v>1249</v>
+      </c>
+      <c r="W23" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="58" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z23" s="59" t="n">
+        <v>45551</v>
+      </c>
+      <c r="AA23" s="59" t="n">
+        <v>45916</v>
+      </c>
+      <c r="AB23" s="59" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="D24" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E24" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-3</t>
+        </is>
+      </c>
+      <c r="F24" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G24" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K24" s="36" t="inlineStr">
+        <is>
+          <t>Waugh, Christopher</t>
+        </is>
+      </c>
+      <c r="L24" s="55" t="n">
+        <v>820</v>
+      </c>
+      <c r="M24" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U24" s="58" t="n">
+        <v>1404</v>
+      </c>
+      <c r="V24" s="58" t="n">
+        <v>1245</v>
+      </c>
+      <c r="W24" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="58" t="n">
+        <v>99</v>
+      </c>
+      <c r="Z24" s="59" t="n">
+        <v>45121</v>
+      </c>
+      <c r="AA24" s="59" t="n">
+        <v>45879</v>
+      </c>
+      <c r="AB24" s="59" t="n">
+        <v>46243</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="D25" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E25" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-4</t>
+        </is>
+      </c>
+      <c r="F25" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G25" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K25" s="36" t="inlineStr">
+        <is>
+          <t>McClarty, Nicole</t>
+        </is>
+      </c>
+      <c r="L25" s="55" t="n">
+        <v>935</v>
+      </c>
+      <c r="M25" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U25" s="58" t="n">
+        <v>1404</v>
+      </c>
+      <c r="V25" s="58" t="n">
+        <v>1215</v>
+      </c>
+      <c r="W25" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="58" t="n">
+        <v>131</v>
+      </c>
+      <c r="Z25" s="59" t="n">
+        <v>44241</v>
+      </c>
+      <c r="AA25" s="59" t="n">
+        <v>45805</v>
+      </c>
+      <c r="AB25" s="59" t="n">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E26" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-5</t>
+        </is>
+      </c>
+      <c r="F26" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G26" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K26" s="36" t="inlineStr">
+        <is>
+          <t>Belcher, Keira</t>
+        </is>
+      </c>
+      <c r="L26" s="55" t="n">
+        <v>1066</v>
+      </c>
+      <c r="M26" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U26" s="58" t="n">
+        <v>1349</v>
+      </c>
+      <c r="V26" s="58" t="n">
+        <v>1345</v>
+      </c>
+      <c r="W26" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="58" t="n">
+        <v>131</v>
+      </c>
+      <c r="Z26" s="59" t="n">
+        <v>45495</v>
+      </c>
+      <c r="AA26" s="59" t="n">
+        <v>45860</v>
+      </c>
+      <c r="AB26" s="59" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E27" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-6</t>
+        </is>
+      </c>
+      <c r="F27" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G27" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K27" s="36" t="inlineStr">
+        <is>
+          <t>Harrison, Davis</t>
+        </is>
+      </c>
+      <c r="L27" s="55" t="n">
+        <v>840</v>
+      </c>
+      <c r="M27" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U27" s="58" t="n">
+        <v>1374</v>
+      </c>
+      <c r="V27" s="58" t="n">
+        <v>1244</v>
+      </c>
+      <c r="W27" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="58" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z27" s="59" t="n">
+        <v>45709</v>
+      </c>
+      <c r="AA27" s="59" t="n">
+        <v>46074</v>
+      </c>
+      <c r="AB27" s="59" t="n">
+        <v>46438</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E28" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-7</t>
+        </is>
+      </c>
+      <c r="F28" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G28" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K28" s="36" t="inlineStr">
+        <is>
+          <t>Steele, Christopher</t>
+        </is>
+      </c>
+      <c r="L28" s="55" t="n">
+        <v>965</v>
+      </c>
+      <c r="M28" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U28" s="58" t="n">
+        <v>1374</v>
+      </c>
+      <c r="V28" s="58" t="n">
+        <v>1320</v>
+      </c>
+      <c r="W28" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="58" t="n">
+        <v>166</v>
+      </c>
+      <c r="Z28" s="59" t="n">
+        <v>44281</v>
+      </c>
+      <c r="AA28" s="59" t="n">
+        <v>45926</v>
+      </c>
+      <c r="AB28" s="59" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E29" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-8</t>
+        </is>
+      </c>
+      <c r="F29" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G29" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K29" s="36" t="inlineStr">
+        <is>
+          <t>Rodriguez, Larissa</t>
+        </is>
+      </c>
+      <c r="L29" s="55" t="n">
+        <v>475</v>
+      </c>
+      <c r="M29" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U29" s="58" t="n">
+        <v>1049</v>
+      </c>
+      <c r="V29" s="58" t="n">
+        <v>1049</v>
+      </c>
+      <c r="W29" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="58" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z29" s="59" t="n">
+        <v>46042</v>
+      </c>
+      <c r="AA29" s="59" t="n">
+        <v>46042</v>
+      </c>
+      <c r="AB29" s="59" t="n">
+        <v>46496</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E30" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-9</t>
+        </is>
+      </c>
+      <c r="F30" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G30" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K30" s="36" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="L30" s="55" t="n">
+        <v>723</v>
+      </c>
+      <c r="M30" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="57" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="U30" s="58" t="n">
+        <v>1355</v>
+      </c>
+      <c r="V30" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E31" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-10</t>
+        </is>
+      </c>
+      <c r="F31" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G31" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K31" s="36" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="L31" s="55" t="n">
+        <v>744</v>
+      </c>
+      <c r="M31" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="57" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="U31" s="58" t="n">
+        <v>1355</v>
+      </c>
+      <c r="V31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="D32" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E32" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-11</t>
+        </is>
+      </c>
+      <c r="F32" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G32" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K32" s="36" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="L32" s="55" t="n">
+        <v>720</v>
+      </c>
+      <c r="M32" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="57" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="U32" s="58" t="n">
+        <v>990</v>
+      </c>
+      <c r="V32" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E33" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-12</t>
+        </is>
+      </c>
+      <c r="F33" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G33" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K33" s="36" t="inlineStr">
+        <is>
+          <t>Montgomery-Lewis, Jaylynne</t>
+        </is>
+      </c>
+      <c r="L33" s="55" t="n">
+        <v>656</v>
+      </c>
+      <c r="M33" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U33" s="58" t="n">
+        <v>1139</v>
+      </c>
+      <c r="V33" s="58" t="n">
+        <v>1139</v>
+      </c>
+      <c r="W33" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="58" t="n">
+        <v>131</v>
+      </c>
+      <c r="Z33" s="59" t="n">
+        <v>45863</v>
+      </c>
+      <c r="AA33" s="59" t="n">
+        <v>45863</v>
+      </c>
+      <c r="AB33" s="59" t="n">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="D34" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E34" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-14</t>
+        </is>
+      </c>
+      <c r="F34" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G34" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K34" s="36" t="inlineStr">
+        <is>
+          <t>Von Hassell, Damontay</t>
+        </is>
+      </c>
+      <c r="L34" s="55" t="n">
+        <v>476</v>
+      </c>
+      <c r="M34" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U34" s="58" t="n">
+        <v>1049</v>
+      </c>
+      <c r="V34" s="58" t="n">
+        <v>1099</v>
+      </c>
+      <c r="W34" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="58" t="n">
+        <v>131</v>
+      </c>
+      <c r="Z34" s="59" t="n">
+        <v>45831</v>
+      </c>
+      <c r="AA34" s="59" t="n">
+        <v>45831</v>
+      </c>
+      <c r="AB34" s="59" t="n">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="D35" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E35" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-15</t>
+        </is>
+      </c>
+      <c r="F35" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G35" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K35" s="36" t="inlineStr">
+        <is>
+          <t>Sorrells, Kashon</t>
+        </is>
+      </c>
+      <c r="L35" s="55" t="n">
+        <v>723</v>
+      </c>
+      <c r="M35" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U35" s="58" t="n">
+        <v>1164</v>
+      </c>
+      <c r="V35" s="58" t="n">
+        <v>990</v>
+      </c>
+      <c r="W35" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="58" t="n">
+        <v>434</v>
+      </c>
+      <c r="Z35" s="59" t="n">
+        <v>44250</v>
+      </c>
+      <c r="AA35" s="59" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="D36" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E36" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-16</t>
+        </is>
+      </c>
+      <c r="F36" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G36" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K36" s="36" t="inlineStr">
+        <is>
+          <t>Pitvorec, Jeremy</t>
+        </is>
+      </c>
+      <c r="L36" s="55" t="n">
+        <v>516</v>
+      </c>
+      <c r="M36" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U36" s="58" t="n">
+        <v>1149</v>
+      </c>
+      <c r="V36" s="58" t="n">
+        <v>1125</v>
+      </c>
+      <c r="W36" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="58" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z36" s="59" t="n">
+        <v>44621</v>
+      </c>
+      <c r="AA36" s="59" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB36" s="59" t="n">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="D37" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E37" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-17</t>
+        </is>
+      </c>
+      <c r="F37" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G37" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K37" s="36" t="inlineStr">
+        <is>
+          <t>Quiroz, Espie</t>
+        </is>
+      </c>
+      <c r="L37" s="55" t="n">
+        <v>765</v>
+      </c>
+      <c r="M37" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U37" s="58" t="n">
+        <v>1179</v>
+      </c>
+      <c r="V37" s="58" t="n">
+        <v>1179</v>
+      </c>
+      <c r="W37" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="58" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z37" s="59" t="n">
+        <v>45971</v>
+      </c>
+      <c r="AA37" s="59" t="n">
+        <v>45971</v>
+      </c>
+      <c r="AB37" s="59" t="n">
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="D38" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E38" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-18</t>
+        </is>
+      </c>
+      <c r="F38" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G38" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K38" s="36" t="inlineStr">
+        <is>
+          <t>Ostrander, Bradley</t>
+        </is>
+      </c>
+      <c r="L38" s="55" t="n">
+        <v>765</v>
+      </c>
+      <c r="M38" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U38" s="58" t="n">
+        <v>1124</v>
+      </c>
+      <c r="V38" s="58" t="n">
+        <v>1124</v>
+      </c>
+      <c r="W38" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="58" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z38" s="59" t="n">
+        <v>45946</v>
+      </c>
+      <c r="AA38" s="59" t="n">
+        <v>45946</v>
+      </c>
+      <c r="AB38" s="59" t="n">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="D39" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E39" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-19</t>
+        </is>
+      </c>
+      <c r="F39" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G39" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K39" s="36" t="inlineStr">
+        <is>
+          <t>Webb, Kennetha</t>
+        </is>
+      </c>
+      <c r="L39" s="55" t="n">
+        <v>781</v>
+      </c>
+      <c r="M39" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U39" s="58" t="n">
+        <v>1324</v>
+      </c>
+      <c r="V39" s="58" t="n">
+        <v>1324</v>
+      </c>
+      <c r="W39" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="58" t="n">
+        <v>164</v>
+      </c>
+      <c r="Z39" s="59" t="n">
+        <v>45926</v>
+      </c>
+      <c r="AA39" s="59" t="n">
+        <v>45926</v>
+      </c>
+      <c r="AB39" s="59" t="n">
+        <v>46381</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="D40" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E40" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-20</t>
+        </is>
+      </c>
+      <c r="F40" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G40" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K40" s="36" t="inlineStr">
+        <is>
+          <t>Keaton, Aniya</t>
+        </is>
+      </c>
+      <c r="L40" s="55" t="n">
+        <v>515</v>
+      </c>
+      <c r="M40" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U40" s="58" t="n">
+        <v>1114</v>
+      </c>
+      <c r="V40" s="58" t="n">
+        <v>1114</v>
+      </c>
+      <c r="W40" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="58" t="n">
+        <v>131</v>
+      </c>
+      <c r="Z40" s="59" t="n">
+        <v>45836</v>
+      </c>
+      <c r="AA40" s="59" t="n">
+        <v>45836</v>
+      </c>
+      <c r="AB40" s="59" t="n">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="D41" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E41" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-21</t>
+        </is>
+      </c>
+      <c r="F41" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G41" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K41" s="36" t="inlineStr">
+        <is>
+          <t>Sanchez Hernandez, Jose Adolfo</t>
+        </is>
+      </c>
+      <c r="L41" s="55" t="n">
+        <v>515</v>
+      </c>
+      <c r="M41" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U41" s="58" t="n">
+        <v>1169</v>
+      </c>
+      <c r="V41" s="58" t="n">
+        <v>1245</v>
+      </c>
+      <c r="W41" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="58" t="n">
+        <v>99</v>
+      </c>
+      <c r="Z41" s="59" t="n">
+        <v>45623</v>
+      </c>
+      <c r="AA41" s="59" t="n">
+        <v>45988</v>
+      </c>
+      <c r="AB41" s="59" t="n">
+        <v>46352</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="D42" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E42" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-22</t>
+        </is>
+      </c>
+      <c r="F42" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G42" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K42" s="36" t="inlineStr">
+        <is>
+          <t>Sablas, Mary</t>
+        </is>
+      </c>
+      <c r="L42" s="55" t="n">
+        <v>748</v>
+      </c>
+      <c r="M42" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U42" s="58" t="n">
+        <v>1109</v>
+      </c>
+      <c r="V42" s="58" t="n">
+        <v>1059</v>
+      </c>
+      <c r="W42" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="58" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z42" s="59" t="n">
+        <v>45308</v>
+      </c>
+      <c r="AA42" s="59" t="n">
+        <v>46039</v>
+      </c>
+      <c r="AB42" s="59" t="n">
+        <v>46493</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="D43" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E43" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-23</t>
+        </is>
+      </c>
+      <c r="F43" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G43" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K43" s="36" t="inlineStr">
+        <is>
+          <t>Sell, Miranda</t>
+        </is>
+      </c>
+      <c r="L43" s="55" t="n">
+        <v>888</v>
+      </c>
+      <c r="M43" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N43" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U43" s="58" t="n">
+        <v>1384</v>
+      </c>
+      <c r="V43" s="58" t="n">
+        <v>1384</v>
+      </c>
+      <c r="W43" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="58" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z43" s="59" t="n">
+        <v>45990</v>
+      </c>
+      <c r="AA43" s="59" t="n">
+        <v>45990</v>
+      </c>
+      <c r="AB43" s="59" t="n">
+        <v>46354</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="D44" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E44" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-24</t>
+        </is>
+      </c>
+      <c r="F44" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G44" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K44" s="36" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="L44" s="55" t="n">
+        <v>683</v>
+      </c>
+      <c r="M44" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N44" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="57" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="U44" s="58" t="n">
+        <v>1355</v>
+      </c>
+      <c r="V44" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="D45" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E45" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-25</t>
+        </is>
+      </c>
+      <c r="F45" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G45" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K45" s="36" t="inlineStr">
+        <is>
+          <t>Williams, Andre</t>
+        </is>
+      </c>
+      <c r="L45" s="55" t="n">
+        <v>781</v>
+      </c>
+      <c r="M45" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U45" s="58" t="n">
+        <v>1314</v>
+      </c>
+      <c r="V45" s="58" t="n">
+        <v>1184</v>
+      </c>
+      <c r="W45" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="58" t="n">
+        <v>169</v>
+      </c>
+      <c r="Z45" s="59" t="n">
+        <v>45717</v>
+      </c>
+      <c r="AA45" s="59" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB45" s="59" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="D46" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E46" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-26</t>
+        </is>
+      </c>
+      <c r="F46" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G46" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K46" s="36" t="inlineStr">
+        <is>
+          <t>Hausley, Isaiah</t>
+        </is>
+      </c>
+      <c r="L46" s="55" t="n">
+        <v>685</v>
+      </c>
+      <c r="M46" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U46" s="58" t="n">
+        <v>1364</v>
+      </c>
+      <c r="V46" s="58" t="n">
+        <v>1255</v>
+      </c>
+      <c r="W46" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="58" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z46" s="59" t="n">
+        <v>44909</v>
+      </c>
+      <c r="AA46" s="59" t="n">
+        <v>46039</v>
+      </c>
+      <c r="AB46" s="59" t="n">
+        <v>46403</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="D47" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E47" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-27</t>
+        </is>
+      </c>
+      <c r="F47" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G47" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K47" s="36" t="inlineStr">
+        <is>
+          <t>West, Brayden</t>
+        </is>
+      </c>
+      <c r="L47" s="55" t="n">
+        <v>516</v>
+      </c>
+      <c r="M47" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U47" s="58" t="n">
+        <v>1149</v>
+      </c>
+      <c r="V47" s="58" t="n">
+        <v>1149</v>
+      </c>
+      <c r="W47" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="58" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z47" s="59" t="n">
+        <v>45869</v>
+      </c>
+      <c r="AA47" s="59" t="n">
+        <v>45869</v>
+      </c>
+      <c r="AB47" s="59" t="n">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="D48" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E48" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-28</t>
+        </is>
+      </c>
+      <c r="F48" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G48" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K48" s="36" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="L48" s="55" t="n">
+        <v>775</v>
+      </c>
+      <c r="M48" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N48" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="57" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="U48" s="58" t="n">
+        <v>1355</v>
+      </c>
+      <c r="V48" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="D49" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E49" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-29</t>
+        </is>
+      </c>
+      <c r="F49" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G49" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K49" s="36" t="inlineStr">
+        <is>
+          <t>Ndiaye, Omar</t>
+        </is>
+      </c>
+      <c r="L49" s="55" t="n">
+        <v>712</v>
+      </c>
+      <c r="M49" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U49" s="58" t="n">
+        <v>1349</v>
+      </c>
+      <c r="V49" s="58" t="n">
+        <v>1330</v>
+      </c>
+      <c r="W49" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="58" t="n">
+        <v>96</v>
+      </c>
+      <c r="Z49" s="59" t="n">
+        <v>45120</v>
+      </c>
+      <c r="AA49" s="59" t="n">
+        <v>45851</v>
+      </c>
+      <c r="AB49" s="59" t="n">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="D50" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E50" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-30</t>
+        </is>
+      </c>
+      <c r="F50" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G50" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K50" s="36" t="inlineStr">
+        <is>
+          <t>Ogundipe, Eniola</t>
+        </is>
+      </c>
+      <c r="L50" s="55" t="n">
+        <v>712</v>
+      </c>
+      <c r="M50" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U50" s="58" t="n">
+        <v>1124</v>
+      </c>
+      <c r="V50" s="58" t="n">
+        <v>1185</v>
+      </c>
+      <c r="W50" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="58" t="n">
+        <v>131</v>
+      </c>
+      <c r="Z50" s="59" t="n">
+        <v>45077</v>
+      </c>
+      <c r="AA50" s="59" t="n">
+        <v>45808</v>
+      </c>
+      <c r="AB50" s="59" t="n">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="D51" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E51" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-31</t>
+        </is>
+      </c>
+      <c r="F51" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G51" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K51" s="36" t="inlineStr">
+        <is>
+          <t>HUTZELL, LILLIAN</t>
+        </is>
+      </c>
+      <c r="L51" s="55" t="n">
+        <v>781</v>
+      </c>
+      <c r="M51" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N51" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U51" s="58" t="n">
+        <v>1349</v>
+      </c>
+      <c r="V51" s="58" t="n">
+        <v>1355</v>
+      </c>
+      <c r="W51" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="58" t="n">
+        <v>169</v>
+      </c>
+      <c r="Z51" s="59" t="n">
+        <v>44678</v>
+      </c>
+      <c r="AA51" s="59" t="n">
+        <v>46139</v>
+      </c>
+      <c r="AB51" s="59" t="n">
+        <v>46503</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="D52" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E52" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-32</t>
+        </is>
+      </c>
+      <c r="F52" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G52" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K52" s="36" t="inlineStr">
+        <is>
+          <t>La Flower, Michael</t>
+        </is>
+      </c>
+      <c r="L52" s="55" t="n">
+        <v>686</v>
+      </c>
+      <c r="M52" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U52" s="58" t="n">
+        <v>1334</v>
+      </c>
+      <c r="V52" s="58" t="n">
+        <v>1334</v>
+      </c>
+      <c r="W52" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="58" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z52" s="59" t="n">
+        <v>45898</v>
+      </c>
+      <c r="AA52" s="59" t="n">
+        <v>45898</v>
+      </c>
+      <c r="AB52" s="59" t="n">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="D53" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E53" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-33</t>
+        </is>
+      </c>
+      <c r="F53" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G53" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K53" s="36" t="inlineStr">
+        <is>
+          <t>Bowman, Katherine</t>
+        </is>
+      </c>
+      <c r="L53" s="55" t="n">
+        <v>516</v>
+      </c>
+      <c r="M53" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U53" s="58" t="n">
+        <v>1124</v>
+      </c>
+      <c r="V53" s="58" t="n">
+        <v>1124</v>
+      </c>
+      <c r="W53" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="58" t="n">
+        <v>131</v>
+      </c>
+      <c r="Z53" s="59" t="n">
+        <v>45821</v>
+      </c>
+      <c r="AA53" s="59" t="n">
+        <v>45821</v>
+      </c>
+      <c r="AB53" s="59" t="n">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="D54" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E54" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-34</t>
+        </is>
+      </c>
+      <c r="F54" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G54" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K54" s="36" t="inlineStr">
+        <is>
+          <t>Asher, Derrick</t>
+        </is>
+      </c>
+      <c r="L54" s="55" t="n">
+        <v>748</v>
+      </c>
+      <c r="M54" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U54" s="58" t="n">
+        <v>1334</v>
+      </c>
+      <c r="V54" s="58" t="n">
+        <v>1334</v>
+      </c>
+      <c r="W54" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="58" t="n">
+        <v>131</v>
+      </c>
+      <c r="Z54" s="59" t="n">
+        <v>45855</v>
+      </c>
+      <c r="AA54" s="59" t="n">
+        <v>45855</v>
+      </c>
+      <c r="AB54" s="59" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="D55" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E55" s="54" t="inlineStr">
+        <is>
+          <t>CL - 806-35</t>
+        </is>
+      </c>
+      <c r="F55" s="54" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="G55" s="54" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K55" s="36" t="inlineStr">
+        <is>
+          <t>Mack, Morgan</t>
+        </is>
+      </c>
+      <c r="L55" s="55" t="n">
+        <v>1078</v>
+      </c>
+      <c r="M55" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U55" s="58" t="n">
+        <v>1394</v>
+      </c>
+      <c r="V55" s="58" t="n">
+        <v>1394</v>
+      </c>
+      <c r="W55" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="58" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z55" s="59" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AA55" s="59" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AB55" s="59" t="n">
+        <v>46476</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="D56" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E56" s="54" t="inlineStr">
+        <is>
+          <t>CL - 816-1</t>
+        </is>
+      </c>
+      <c r="F56" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G56" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K56" s="36" t="inlineStr">
+        <is>
+          <t>Miller, Brian</t>
+        </is>
+      </c>
+      <c r="L56" s="55" t="n">
+        <v>540</v>
+      </c>
+      <c r="M56" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U56" s="58" t="n">
+        <v>1189</v>
+      </c>
+      <c r="V56" s="58" t="n">
+        <v>1300</v>
+      </c>
+      <c r="W56" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="58" t="n">
+        <v>284</v>
+      </c>
+      <c r="Z56" s="59" t="n">
+        <v>45595</v>
+      </c>
+      <c r="AA56" s="59" t="n">
+        <v>45960</v>
+      </c>
+      <c r="AB56" s="59" t="n">
+        <v>46416</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="D57" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E57" s="54" t="inlineStr">
+        <is>
+          <t>CL - 816-2</t>
+        </is>
+      </c>
+      <c r="F57" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G57" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K57" s="36" t="inlineStr">
+        <is>
+          <t>Holbrook, Kendrick</t>
+        </is>
+      </c>
+      <c r="L57" s="55" t="n">
+        <v>775</v>
+      </c>
+      <c r="M57" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U57" s="58" t="n">
+        <v>1189</v>
+      </c>
+      <c r="V57" s="58" t="n">
+        <v>1145</v>
+      </c>
+      <c r="W57" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="58" t="n">
+        <v>311</v>
+      </c>
+      <c r="Z57" s="59" t="n">
+        <v>45456</v>
+      </c>
+      <c r="AA57" s="59" t="n">
+        <v>45821</v>
+      </c>
+      <c r="AB57" s="59" t="n">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="D58" s="36" t="inlineStr">
+        <is>
+          <t>Maven @ 806</t>
+        </is>
+      </c>
+      <c r="E58" s="54" t="inlineStr">
+        <is>
+          <t>CL - 816-3</t>
+        </is>
+      </c>
+      <c r="F58" s="54" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="G58" s="54" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="K58" s="36" t="inlineStr">
+        <is>
+          <t>Bariff, Mae</t>
+        </is>
+      </c>
+      <c r="L58" s="55" t="n">
+        <v>775</v>
+      </c>
+      <c r="M58" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="57" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="U58" s="58" t="n">
+        <v>1189</v>
+      </c>
+      <c r="V58" s="58" t="n">
+        <v>1189</v>
+      </c>
+      <c r="W58" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="58" t="n">
+        <v>284</v>
+      </c>
+      <c r="Z58" s="59" t="n">
+        <v>45838</v>
+      </c>
+      <c r="AA58" s="59" t="n">
+        <v>45838</v>
+      </c>
+      <c r="AB58" s="59" t="n">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" s="60" t="inlineStr">
         <is>
           <t>Total / Wtd. Average</t>
         </is>
       </c>
-      <c r="D22" s="61" t="n"/>
-      <c r="E22" s="61" t="n"/>
-      <c r="F22" s="61" t="n"/>
-      <c r="G22" s="62" t="n">
-        <v>14</v>
-      </c>
-      <c r="H22" s="61" t="n"/>
-      <c r="I22" s="61" t="n"/>
-      <c r="J22" s="61" t="n"/>
-      <c r="K22" s="61" t="n"/>
-      <c r="L22" s="63" t="n">
-        <v>11232</v>
-      </c>
-      <c r="M22" s="61" t="n"/>
-      <c r="N22" s="61" t="n"/>
-      <c r="O22" s="61" t="n"/>
-      <c r="P22" s="61" t="n"/>
-      <c r="Q22" s="61" t="n"/>
-      <c r="R22" s="61" t="n"/>
-      <c r="S22" s="61" t="n"/>
-      <c r="T22" s="61" t="n"/>
-      <c r="U22" s="64" t="n">
-        <v>19781</v>
-      </c>
-      <c r="V22" s="64" t="n">
-        <v>12684.3</v>
-      </c>
-      <c r="W22" s="64" t="n">
+      <c r="D59" s="61" t="n"/>
+      <c r="E59" s="61" t="n"/>
+      <c r="F59" s="61" t="n"/>
+      <c r="G59" s="62" t="n">
+        <v>51</v>
+      </c>
+      <c r="H59" s="61" t="n"/>
+      <c r="I59" s="61" t="n"/>
+      <c r="J59" s="61" t="n"/>
+      <c r="K59" s="61" t="n"/>
+      <c r="L59" s="63" t="n">
+        <v>38376</v>
+      </c>
+      <c r="M59" s="61" t="n"/>
+      <c r="N59" s="61" t="n"/>
+      <c r="O59" s="61" t="n"/>
+      <c r="P59" s="61" t="n"/>
+      <c r="Q59" s="61" t="n"/>
+      <c r="R59" s="61" t="n"/>
+      <c r="S59" s="61" t="n"/>
+      <c r="T59" s="61" t="n"/>
+      <c r="U59" s="64" t="n">
+        <v>66209</v>
+      </c>
+      <c r="V59" s="64" t="n">
+        <v>51660.3</v>
+      </c>
+      <c r="W59" s="64" t="n">
         <v>-374.7</v>
       </c>
-      <c r="X22" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="64" t="n">
+      <c r="X59" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="64" t="n">
         <v>6361</v>
       </c>
-      <c r="Z22" s="61" t="n"/>
-      <c r="AA22" s="61" t="n"/>
-      <c r="AB22" s="61" t="n"/>
-      <c r="AC22" s="61" t="n"/>
-      <c r="AD22" s="61" t="n"/>
-      <c r="AE22" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="66" t="n"/>
+      <c r="Z59" s="61" t="n"/>
+      <c r="AA59" s="61" t="n"/>
+      <c r="AB59" s="61" t="n"/>
+      <c r="AC59" s="61" t="n"/>
+      <c r="AD59" s="61" t="n"/>
+      <c r="AE59" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="66" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3497,7 +5971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:AS45"/>
+  <dimension ref="A3:AS82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.6" customWidth="1" min="1" max="1"/>
@@ -3639,239 +6113,381 @@
         </is>
       </c>
       <c r="H5" s="75">
-        <f>COUNTIFS($D$32:$D$45,$C5)</f>
+        <f>COUNTIFS($D$32:$D$82,$C5)</f>
         <v/>
       </c>
       <c r="I5" s="75">
-        <f>COUNTIFS($D$32:$D$45,$C5,$C$32:$C$45,"Occ")+COUNTIFS($D$32:$D$45,$C5,$C$32:$C$45,"Admin")+COUNTIFS($D$32:$D$45,$C5,$C$32:$C$45,"Down")+COUNTIFS($D$32:$D$45,$C5,$C$32:$C$45,"Super")+COUNTIFS($D$32:$D$45,$C5,$C$32:$C$45,"Model")</f>
+        <f>COUNTIFS($D$32:$D$82,$C5,$C$32:$C$82,"Occ")+COUNTIFS($D$32:$D$82,$C5,$C$32:$C$82,"Admin")+COUNTIFS($D$32:$D$82,$C5,$C$32:$C$82,"Down")+COUNTIFS($D$32:$D$82,$C5,$C$32:$C$82,"Super")+COUNTIFS($D$32:$D$82,$C5,$C$32:$C$82,"Model")</f>
         <v/>
       </c>
       <c r="J5" s="75">
-        <f>COUNTIFS($D$32:$D$45,$C5,$C$32:$C$45,"Vac")</f>
+        <f>COUNTIFS($D$32:$D$82,$C5,$C$32:$C$82,"Vac")</f>
         <v/>
       </c>
       <c r="K5" s="75">
-        <f>IFERROR(AVERAGEIFS($J$32:$J$45,$D$32:$D$45,$C5),"n/a")</f>
+        <f>IFERROR(AVERAGEIFS($J$32:$J$82,$D$32:$D$82,$C5),"n/a")</f>
         <v/>
       </c>
       <c r="L5" s="75">
-        <f>SUMIFS($J$32:$J$45,$D$32:$D$45,$C5)</f>
+        <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C5)</f>
         <v/>
       </c>
       <c r="M5" s="75">
-        <f>SUMIFS($J$32:$J$45,$D$32:$D$45,$C5,$C$32:$C$45,"Occ")+SUMIFS($J$32:$J$45,$D$32:$D$45,$C5,$C$32:$C$45,"Admin")+SUMIFS($J$32:$J$45,$D$32:$D$45,$C5,$C$32:$C$45,"Down")+SUMIFS($J$32:$J$45,$D$32:$D$45,$C5,$C$32:$C$45,"Super")+SUMIFS($J$32:$J$45,$D$32:$D$45,$C5,$C$32:$C$45,"Model")</f>
+        <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C5,$C$32:$C$82,"Occ")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C5,$C$32:$C$82,"Admin")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C5,$C$32:$C$82,"Down")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C5,$C$32:$C$82,"Super")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C5,$C$32:$C$82,"Model")</f>
         <v/>
       </c>
       <c r="N5" s="75">
-        <f>SUMIFS($J$32:$J$45,$D$32:$D$45,$C5,$C$32:$C$45,"Vac")</f>
+        <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C5,$C$32:$C$82,"Vac")</f>
         <v/>
       </c>
       <c r="O5" s="75">
-        <f>SUMIFS($L$32:$L$45,$D$32:$D$45,$C5)</f>
+        <f>SUMIFS($L$32:$L$82,$D$32:$D$82,$C5)</f>
         <v/>
       </c>
       <c r="P5" s="75">
-        <f>SUMIFS($M$32:$M$45,$D$32:$D$45,$C5)</f>
+        <f>SUMIFS($M$32:$M$82,$D$32:$D$82,$C5)</f>
         <v/>
       </c>
       <c r="Q5" s="75">
-        <f>SUMIFS($R$32:$R$45,$D$32:$D$45,$C5)</f>
+        <f>SUMIFS($R$32:$R$82,$D$32:$D$82,$C5)</f>
         <v/>
       </c>
       <c r="R5" s="75">
-        <f>SUMIFS($S$32:$S$45,$D$32:$D$45,$C5)</f>
+        <f>SUMIFS($S$32:$S$82,$D$32:$D$82,$C5)</f>
         <v/>
       </c>
       <c r="S5" s="75">
-        <f>SUMIFS($T$32:$T$45,$D$32:$D$45,$C5)</f>
+        <f>SUMIFS($T$32:$T$82,$D$32:$D$82,$C5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="C6" s="71" t="inlineStr">
         <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="D6" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="E6" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" s="75">
+        <f>COUNTIFS($D$32:$D$82,$C6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="75">
+        <f>COUNTIFS($D$32:$D$82,$C6,$C$32:$C$82,"Occ")+COUNTIFS($D$32:$D$82,$C6,$C$32:$C$82,"Admin")+COUNTIFS($D$32:$D$82,$C6,$C$32:$C$82,"Down")+COUNTIFS($D$32:$D$82,$C6,$C$32:$C$82,"Super")+COUNTIFS($D$32:$D$82,$C6,$C$32:$C$82,"Model")</f>
+        <v/>
+      </c>
+      <c r="J6" s="75">
+        <f>COUNTIFS($D$32:$D$82,$C6,$C$32:$C$82,"Vac")</f>
+        <v/>
+      </c>
+      <c r="K6" s="75">
+        <f>IFERROR(AVERAGEIFS($J$32:$J$82,$D$32:$D$82,$C6),"n/a")</f>
+        <v/>
+      </c>
+      <c r="L6" s="75">
+        <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="75">
+        <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C6,$C$32:$C$82,"Occ")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C6,$C$32:$C$82,"Admin")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C6,$C$32:$C$82,"Down")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C6,$C$32:$C$82,"Super")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C6,$C$32:$C$82,"Model")</f>
+        <v/>
+      </c>
+      <c r="N6" s="75">
+        <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C6,$C$32:$C$82,"Vac")</f>
+        <v/>
+      </c>
+      <c r="O6" s="75">
+        <f>SUMIFS($L$32:$L$82,$D$32:$D$82,$C6)</f>
+        <v/>
+      </c>
+      <c r="P6" s="75">
+        <f>SUMIFS($M$32:$M$82,$D$32:$D$82,$C6)</f>
+        <v/>
+      </c>
+      <c r="Q6" s="75">
+        <f>SUMIFS($R$32:$R$82,$D$32:$D$82,$C6)</f>
+        <v/>
+      </c>
+      <c r="R6" s="75">
+        <f>SUMIFS($S$32:$S$82,$D$32:$D$82,$C6)</f>
+        <v/>
+      </c>
+      <c r="S6" s="75">
+        <f>SUMIFS($T$32:$T$82,$D$32:$D$82,$C6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="71" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="D7" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="E7" s="73" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="75">
+        <f>COUNTIFS($D$32:$D$82,$C7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="75">
+        <f>COUNTIFS($D$32:$D$82,$C7,$C$32:$C$82,"Occ")+COUNTIFS($D$32:$D$82,$C7,$C$32:$C$82,"Admin")+COUNTIFS($D$32:$D$82,$C7,$C$32:$C$82,"Down")+COUNTIFS($D$32:$D$82,$C7,$C$32:$C$82,"Super")+COUNTIFS($D$32:$D$82,$C7,$C$32:$C$82,"Model")</f>
+        <v/>
+      </c>
+      <c r="J7" s="75">
+        <f>COUNTIFS($D$32:$D$82,$C7,$C$32:$C$82,"Vac")</f>
+        <v/>
+      </c>
+      <c r="K7" s="75">
+        <f>IFERROR(AVERAGEIFS($J$32:$J$82,$D$32:$D$82,$C7),"n/a")</f>
+        <v/>
+      </c>
+      <c r="L7" s="75">
+        <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="75">
+        <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C7,$C$32:$C$82,"Occ")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C7,$C$32:$C$82,"Admin")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C7,$C$32:$C$82,"Down")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C7,$C$32:$C$82,"Super")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C7,$C$32:$C$82,"Model")</f>
+        <v/>
+      </c>
+      <c r="N7" s="75">
+        <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C7,$C$32:$C$82,"Vac")</f>
+        <v/>
+      </c>
+      <c r="O7" s="75">
+        <f>SUMIFS($L$32:$L$82,$D$32:$D$82,$C7)</f>
+        <v/>
+      </c>
+      <c r="P7" s="75">
+        <f>SUMIFS($M$32:$M$82,$D$32:$D$82,$C7)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="75">
+        <f>SUMIFS($R$32:$R$82,$D$32:$D$82,$C7)</f>
+        <v/>
+      </c>
+      <c r="R7" s="75">
+        <f>SUMIFS($S$32:$S$82,$D$32:$D$82,$C7)</f>
+        <v/>
+      </c>
+      <c r="S7" s="75">
+        <f>SUMIFS($T$32:$T$82,$D$32:$D$82,$C7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="71" t="inlineStr">
+        <is>
           <t>2 BD / 2 BA</t>
         </is>
       </c>
-      <c r="D6" s="72" t="inlineStr">
+      <c r="D8" s="72" t="inlineStr">
         <is>
           <t>2x2B_C</t>
         </is>
       </c>
-      <c r="E6" s="73" t="n">
+      <c r="E8" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="74" t="n">
+      <c r="F8" s="74" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="73" t="inlineStr">
+      <c r="G8" s="73" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H6" s="75">
-        <f>COUNTIFS($D$32:$D$45,$C6)</f>
-        <v/>
-      </c>
-      <c r="I6" s="75">
-        <f>COUNTIFS($D$32:$D$45,$C6,$C$32:$C$45,"Occ")+COUNTIFS($D$32:$D$45,$C6,$C$32:$C$45,"Admin")+COUNTIFS($D$32:$D$45,$C6,$C$32:$C$45,"Down")+COUNTIFS($D$32:$D$45,$C6,$C$32:$C$45,"Super")+COUNTIFS($D$32:$D$45,$C6,$C$32:$C$45,"Model")</f>
-        <v/>
-      </c>
-      <c r="J6" s="75">
-        <f>COUNTIFS($D$32:$D$45,$C6,$C$32:$C$45,"Vac")</f>
-        <v/>
-      </c>
-      <c r="K6" s="75">
-        <f>IFERROR(AVERAGEIFS($J$32:$J$45,$D$32:$D$45,$C6),"n/a")</f>
-        <v/>
-      </c>
-      <c r="L6" s="75">
-        <f>SUMIFS($J$32:$J$45,$D$32:$D$45,$C6)</f>
-        <v/>
-      </c>
-      <c r="M6" s="75">
-        <f>SUMIFS($J$32:$J$45,$D$32:$D$45,$C6,$C$32:$C$45,"Occ")+SUMIFS($J$32:$J$45,$D$32:$D$45,$C6,$C$32:$C$45,"Admin")+SUMIFS($J$32:$J$45,$D$32:$D$45,$C6,$C$32:$C$45,"Down")+SUMIFS($J$32:$J$45,$D$32:$D$45,$C6,$C$32:$C$45,"Super")+SUMIFS($J$32:$J$45,$D$32:$D$45,$C6,$C$32:$C$45,"Model")</f>
-        <v/>
-      </c>
-      <c r="N6" s="75">
-        <f>SUMIFS($J$32:$J$45,$D$32:$D$45,$C6,$C$32:$C$45,"Vac")</f>
-        <v/>
-      </c>
-      <c r="O6" s="75">
-        <f>SUMIFS($L$32:$L$45,$D$32:$D$45,$C6)</f>
-        <v/>
-      </c>
-      <c r="P6" s="75">
-        <f>SUMIFS($M$32:$M$45,$D$32:$D$45,$C6)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="75">
-        <f>SUMIFS($R$32:$R$45,$D$32:$D$45,$C6)</f>
-        <v/>
-      </c>
-      <c r="R6" s="75">
-        <f>SUMIFS($S$32:$S$45,$D$32:$D$45,$C6)</f>
-        <v/>
-      </c>
-      <c r="S6" s="75">
-        <f>SUMIFS($T$32:$T$45,$D$32:$D$45,$C6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" s="68" t="inlineStr">
+      <c r="H8" s="75">
+        <f>COUNTIFS($D$32:$D$82,$C8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="75">
+        <f>COUNTIFS($D$32:$D$82,$C8,$C$32:$C$82,"Occ")+COUNTIFS($D$32:$D$82,$C8,$C$32:$C$82,"Admin")+COUNTIFS($D$32:$D$82,$C8,$C$32:$C$82,"Down")+COUNTIFS($D$32:$D$82,$C8,$C$32:$C$82,"Super")+COUNTIFS($D$32:$D$82,$C8,$C$32:$C$82,"Model")</f>
+        <v/>
+      </c>
+      <c r="J8" s="75">
+        <f>COUNTIFS($D$32:$D$82,$C8,$C$32:$C$82,"Vac")</f>
+        <v/>
+      </c>
+      <c r="K8" s="75">
+        <f>IFERROR(AVERAGEIFS($J$32:$J$82,$D$32:$D$82,$C8),"n/a")</f>
+        <v/>
+      </c>
+      <c r="L8" s="75">
+        <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="75">
+        <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C8,$C$32:$C$82,"Occ")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C8,$C$32:$C$82,"Admin")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C8,$C$32:$C$82,"Down")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C8,$C$32:$C$82,"Super")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C8,$C$32:$C$82,"Model")</f>
+        <v/>
+      </c>
+      <c r="N8" s="75">
+        <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C8,$C$32:$C$82,"Vac")</f>
+        <v/>
+      </c>
+      <c r="O8" s="75">
+        <f>SUMIFS($L$32:$L$82,$D$32:$D$82,$C8)</f>
+        <v/>
+      </c>
+      <c r="P8" s="75">
+        <f>SUMIFS($M$32:$M$82,$D$32:$D$82,$C8)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="75">
+        <f>SUMIFS($R$32:$R$82,$D$32:$D$82,$C8)</f>
+        <v/>
+      </c>
+      <c r="R8" s="75">
+        <f>SUMIFS($S$32:$S$82,$D$32:$D$82,$C8)</f>
+        <v/>
+      </c>
+      <c r="S8" s="75">
+        <f>SUMIFS($T$32:$T$82,$D$32:$D$82,$C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="68" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
-      <c r="H7" s="76">
-        <f>SUM(H5:H6)</f>
-        <v/>
-      </c>
-      <c r="I7" s="76">
-        <f>SUM(I5:I6)</f>
-        <v/>
-      </c>
-      <c r="J7" s="76">
-        <f>SUM(J5:J6)</f>
-        <v/>
-      </c>
-      <c r="L7" s="76">
-        <f>SUM(L5:L6)</f>
-        <v/>
-      </c>
-      <c r="M7" s="76">
-        <f>SUM(M5:M6)</f>
-        <v/>
-      </c>
-      <c r="N7" s="76">
-        <f>SUM(N5:N6)</f>
-        <v/>
-      </c>
-      <c r="O7" s="76">
-        <f>SUM(O5:O6)</f>
-        <v/>
-      </c>
-      <c r="P7" s="76">
-        <f>SUM(P5:P6)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="76">
-        <f>SUM(Q5:Q6)</f>
-        <v/>
-      </c>
-      <c r="R7" s="76">
-        <f>SUM(R5:R6)</f>
-        <v/>
-      </c>
-      <c r="S7" s="76">
-        <f>SUM(S5:S6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="68" t="inlineStr">
+      <c r="H9" s="76">
+        <f>SUM(H5:H8)</f>
+        <v/>
+      </c>
+      <c r="I9" s="76">
+        <f>SUM(I5:I8)</f>
+        <v/>
+      </c>
+      <c r="J9" s="76">
+        <f>SUM(J5:J8)</f>
+        <v/>
+      </c>
+      <c r="L9" s="76">
+        <f>SUM(L5:L8)</f>
+        <v/>
+      </c>
+      <c r="M9" s="76">
+        <f>SUM(M5:M8)</f>
+        <v/>
+      </c>
+      <c r="N9" s="76">
+        <f>SUM(N5:N8)</f>
+        <v/>
+      </c>
+      <c r="O9" s="76">
+        <f>SUM(O5:O8)</f>
+        <v/>
+      </c>
+      <c r="P9" s="76">
+        <f>SUM(P5:P8)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="76">
+        <f>SUM(Q5:Q8)</f>
+        <v/>
+      </c>
+      <c r="R9" s="76">
+        <f>SUM(R5:R8)</f>
+        <v/>
+      </c>
+      <c r="S9" s="76">
+        <f>SUM(S5:S8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" s="68" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="I8" s="77">
-        <f>I7/$H$7</f>
-        <v/>
-      </c>
-      <c r="J8" s="77">
-        <f>J7/$H$7</f>
-        <v/>
-      </c>
-      <c r="M8" s="77">
-        <f>IFERROR(M7/$L$7,"n/a")</f>
-        <v/>
-      </c>
-      <c r="N8" s="77">
-        <f>IFERROR(N7/$L$7,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="78" t="inlineStr">
-        <is>
-          <t>Notes:</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" s="78" t="inlineStr">
-        <is>
-          <t>1. Vacant units market rent is the per-unit market/asking rent from the source.</t>
-        </is>
+      <c r="I10" s="77">
+        <f>I9/$H$9</f>
+        <v/>
+      </c>
+      <c r="J10" s="77">
+        <f>J9/$H$9</f>
+        <v/>
+      </c>
+      <c r="M10" s="77">
+        <f>IFERROR(M9/$L$9,"n/a")</f>
+        <v/>
+      </c>
+      <c r="N10" s="77">
+        <f>IFERROR(N9/$L$9,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="78" t="inlineStr">
         <is>
+          <t>Notes:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="78" t="inlineStr">
+        <is>
+          <t>1. Vacant units market rent is the per-unit market/asking rent from the source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="78" t="inlineStr">
+        <is>
           <t>2. BD/BA count is from the Unit Type mapping above (edit the yellow cells to adjust).</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="C19" s="78" t="inlineStr">
+    <row r="21">
+      <c r="C21" s="78" t="inlineStr">
         <is>
           <t>Property Name</t>
         </is>
       </c>
-      <c r="D19" s="78" t="inlineStr">
+      <c r="D21" s="78" t="inlineStr">
         <is>
           <t>Maven @ 806</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="C20" s="78" t="inlineStr">
+    <row r="22">
+      <c r="C22" s="78" t="inlineStr">
         <is>
           <t>Rent Roll Date</t>
         </is>
       </c>
-      <c r="D20" s="79" t="n">
+      <c r="D22" s="79" t="n">
         <v>46157</v>
       </c>
     </row>
@@ -4036,7 +6652,7 @@
     </row>
     <row r="32">
       <c r="A32" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B32" s="72" t="n">
@@ -4047,19 +6663,19 @@
         <v/>
       </c>
       <c r="D32" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I32,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I32,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E32" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D32,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D32,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F32" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D32,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D32,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G32" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D32,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D32,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H32" s="72" t="inlineStr">
@@ -4114,7 +6730,7 @@
     </row>
     <row r="33">
       <c r="A33" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B33" s="72">
@@ -4126,19 +6742,19 @@
         <v/>
       </c>
       <c r="D33" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I33,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I33,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E33" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D33,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D33,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F33" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D33,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D33,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G33" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D33,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D33,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H33" s="72" t="inlineStr">
@@ -4193,7 +6809,7 @@
     </row>
     <row r="34">
       <c r="A34" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B34" s="72">
@@ -4205,19 +6821,19 @@
         <v/>
       </c>
       <c r="D34" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I34,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I34,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E34" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D34,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D34,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F34" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D34,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D34,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G34" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D34,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D34,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H34" s="72" t="inlineStr">
@@ -4272,7 +6888,7 @@
     </row>
     <row r="35">
       <c r="A35" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B35" s="72">
@@ -4284,19 +6900,19 @@
         <v/>
       </c>
       <c r="D35" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I35,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I35,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E35" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D35,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D35,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F35" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D35,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D35,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G35" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D35,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D35,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H35" s="72" t="inlineStr">
@@ -4351,7 +6967,7 @@
     </row>
     <row r="36">
       <c r="A36" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B36" s="72">
@@ -4363,19 +6979,19 @@
         <v/>
       </c>
       <c r="D36" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I36,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I36,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E36" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D36,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D36,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F36" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D36,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D36,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G36" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D36,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D36,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H36" s="72" t="inlineStr">
@@ -4430,7 +7046,7 @@
     </row>
     <row r="37">
       <c r="A37" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B37" s="72">
@@ -4442,19 +7058,19 @@
         <v/>
       </c>
       <c r="D37" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I37,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I37,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E37" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D37,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D37,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F37" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D37,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D37,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G37" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D37,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D37,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H37" s="72" t="inlineStr">
@@ -4509,7 +7125,7 @@
     </row>
     <row r="38">
       <c r="A38" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B38" s="72">
@@ -4521,19 +7137,19 @@
         <v/>
       </c>
       <c r="D38" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I38,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I38,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E38" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D38,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D38,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F38" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D38,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D38,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G38" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D38,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D38,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H38" s="72" t="inlineStr">
@@ -4579,7 +7195,7 @@
     </row>
     <row r="39">
       <c r="A39" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B39" s="72">
@@ -4591,19 +7207,19 @@
         <v/>
       </c>
       <c r="D39" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I39,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I39,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E39" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D39,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D39,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F39" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D39,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D39,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G39" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D39,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D39,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H39" s="72" t="inlineStr">
@@ -4658,7 +7274,7 @@
     </row>
     <row r="40">
       <c r="A40" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B40" s="72">
@@ -4670,19 +7286,19 @@
         <v/>
       </c>
       <c r="D40" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I40,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I40,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E40" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D40,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D40,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F40" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D40,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D40,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G40" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D40,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D40,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H40" s="72" t="inlineStr">
@@ -4740,7 +7356,7 @@
     </row>
     <row r="41">
       <c r="A41" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B41" s="72">
@@ -4752,19 +7368,19 @@
         <v/>
       </c>
       <c r="D41" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I41,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I41,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E41" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D41,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D41,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F41" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D41,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D41,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G41" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D41,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D41,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H41" s="72" t="inlineStr">
@@ -4819,7 +7435,7 @@
     </row>
     <row r="42">
       <c r="A42" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B42" s="72">
@@ -4831,19 +7447,19 @@
         <v/>
       </c>
       <c r="D42" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I42,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I42,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E42" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D42,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D42,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F42" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D42,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D42,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G42" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D42,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D42,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H42" s="72" t="inlineStr">
@@ -4889,7 +7505,7 @@
     </row>
     <row r="43">
       <c r="A43" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B43" s="72">
@@ -4901,19 +7517,19 @@
         <v/>
       </c>
       <c r="D43" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I43,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I43,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E43" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D43,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D43,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F43" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D43,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D43,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G43" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D43,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D43,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H43" s="72" t="inlineStr">
@@ -4968,7 +7584,7 @@
     </row>
     <row r="44">
       <c r="A44" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B44" s="72">
@@ -4980,19 +7596,19 @@
         <v/>
       </c>
       <c r="D44" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I44,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I44,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E44" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D44,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D44,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F44" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D44,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D44,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G44" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D44,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D44,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H44" s="72" t="inlineStr">
@@ -5038,7 +7654,7 @@
     </row>
     <row r="45">
       <c r="A45" s="72">
-        <f>$D$19</f>
+        <f>$D$21</f>
         <v/>
       </c>
       <c r="B45" s="72">
@@ -5050,19 +7666,19 @@
         <v/>
       </c>
       <c r="D45" s="72">
-        <f>INDEX($C$5:$C$6,MATCH(I45,$D$5:$D$6,0))</f>
+        <f>INDEX($C$5:$C$8,MATCH(I45,$D$5:$D$8,0))</f>
         <v/>
       </c>
       <c r="E45" s="72">
-        <f>INDEX($E$5:$E$6,MATCH(D45,$C$5:$C$6,0))</f>
+        <f>INDEX($E$5:$E$8,MATCH(D45,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="F45" s="72">
-        <f>INDEX($F$5:$F$6,MATCH(D45,$C$5:$C$6,0))</f>
+        <f>INDEX($F$5:$F$8,MATCH(D45,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="G45" s="72">
-        <f>INDEX($G$5:$G$6,MATCH(D45,$C$5:$C$6,0))</f>
+        <f>INDEX($G$5:$G$8,MATCH(D45,$C$5:$C$8,0))</f>
         <v/>
       </c>
       <c r="H45" s="72" t="inlineStr">
@@ -5104,6 +7720,2881 @@
       </c>
       <c r="Y45" s="81" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B46" s="72">
+        <f>B45+1</f>
+        <v/>
+      </c>
+      <c r="C46" s="72">
+        <f>IF(K46="Vacant","Vac",IF(K46="Model","Model",IF(K46="Admin","Admin",IF(K46="Down","Down",IF(K46="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D46" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I46,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E46" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D46,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F46" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D46,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G46" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D46,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H46" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-1</t>
+        </is>
+      </c>
+      <c r="I46" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J46" s="80" t="n">
+        <v>810</v>
+      </c>
+      <c r="K46" s="72" t="inlineStr">
+        <is>
+          <t>Collins, Nancy</t>
+        </is>
+      </c>
+      <c r="L46" s="81" t="n">
+        <v>1379</v>
+      </c>
+      <c r="M46" s="81">
+        <f>Y46</f>
+        <v/>
+      </c>
+      <c r="N46" s="82" t="n">
+        <v>44075</v>
+      </c>
+      <c r="O46" s="82" t="n">
+        <v>45901</v>
+      </c>
+      <c r="P46" s="82" t="n">
+        <v>46265</v>
+      </c>
+      <c r="R46" s="81">
+        <f>SUM(AB46:AK46)</f>
+        <v/>
+      </c>
+      <c r="S46" s="81">
+        <f>SUM(AM46:AQ46)</f>
+        <v/>
+      </c>
+      <c r="T46" s="81">
+        <f>SUM(AS46:AW46)</f>
+        <v/>
+      </c>
+      <c r="Y46" s="81" t="n">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B47" s="72">
+        <f>B46+1</f>
+        <v/>
+      </c>
+      <c r="C47" s="72">
+        <f>IF(K47="Vacant","Vac",IF(K47="Model","Model",IF(K47="Admin","Admin",IF(K47="Down","Down",IF(K47="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D47" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I47,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E47" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D47,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F47" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D47,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G47" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D47,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H47" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-2</t>
+        </is>
+      </c>
+      <c r="I47" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J47" s="80" t="n">
+        <v>935</v>
+      </c>
+      <c r="K47" s="72" t="inlineStr">
+        <is>
+          <t>Humphrey, Alyson</t>
+        </is>
+      </c>
+      <c r="L47" s="81" t="n">
+        <v>1379</v>
+      </c>
+      <c r="M47" s="81">
+        <f>Y47</f>
+        <v/>
+      </c>
+      <c r="N47" s="82" t="n">
+        <v>45551</v>
+      </c>
+      <c r="O47" s="82" t="n">
+        <v>45916</v>
+      </c>
+      <c r="P47" s="82" t="n">
+        <v>46280</v>
+      </c>
+      <c r="R47" s="81">
+        <f>SUM(AB47:AK47)</f>
+        <v/>
+      </c>
+      <c r="S47" s="81">
+        <f>SUM(AM47:AQ47)</f>
+        <v/>
+      </c>
+      <c r="T47" s="81">
+        <f>SUM(AS47:AW47)</f>
+        <v/>
+      </c>
+      <c r="Y47" s="81" t="n">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B48" s="72">
+        <f>B47+1</f>
+        <v/>
+      </c>
+      <c r="C48" s="72">
+        <f>IF(K48="Vacant","Vac",IF(K48="Model","Model",IF(K48="Admin","Admin",IF(K48="Down","Down",IF(K48="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D48" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I48,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E48" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D48,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F48" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D48,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G48" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D48,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H48" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-3</t>
+        </is>
+      </c>
+      <c r="I48" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J48" s="80" t="n">
+        <v>820</v>
+      </c>
+      <c r="K48" s="72" t="inlineStr">
+        <is>
+          <t>Waugh, Christopher</t>
+        </is>
+      </c>
+      <c r="L48" s="81" t="n">
+        <v>1404</v>
+      </c>
+      <c r="M48" s="81">
+        <f>Y48</f>
+        <v/>
+      </c>
+      <c r="N48" s="82" t="n">
+        <v>45121</v>
+      </c>
+      <c r="O48" s="82" t="n">
+        <v>45879</v>
+      </c>
+      <c r="P48" s="82" t="n">
+        <v>46243</v>
+      </c>
+      <c r="R48" s="81">
+        <f>SUM(AB48:AK48)</f>
+        <v/>
+      </c>
+      <c r="S48" s="81">
+        <f>SUM(AM48:AQ48)</f>
+        <v/>
+      </c>
+      <c r="T48" s="81">
+        <f>SUM(AS48:AW48)</f>
+        <v/>
+      </c>
+      <c r="Y48" s="81" t="n">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B49" s="72">
+        <f>B48+1</f>
+        <v/>
+      </c>
+      <c r="C49" s="72">
+        <f>IF(K49="Vacant","Vac",IF(K49="Model","Model",IF(K49="Admin","Admin",IF(K49="Down","Down",IF(K49="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D49" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I49,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E49" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D49,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F49" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D49,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G49" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D49,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H49" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-4</t>
+        </is>
+      </c>
+      <c r="I49" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J49" s="80" t="n">
+        <v>935</v>
+      </c>
+      <c r="K49" s="72" t="inlineStr">
+        <is>
+          <t>McClarty, Nicole</t>
+        </is>
+      </c>
+      <c r="L49" s="81" t="n">
+        <v>1404</v>
+      </c>
+      <c r="M49" s="81">
+        <f>Y49</f>
+        <v/>
+      </c>
+      <c r="N49" s="82" t="n">
+        <v>44241</v>
+      </c>
+      <c r="O49" s="82" t="n">
+        <v>45805</v>
+      </c>
+      <c r="P49" s="82" t="n">
+        <v>46261</v>
+      </c>
+      <c r="R49" s="81">
+        <f>SUM(AB49:AK49)</f>
+        <v/>
+      </c>
+      <c r="S49" s="81">
+        <f>SUM(AM49:AQ49)</f>
+        <v/>
+      </c>
+      <c r="T49" s="81">
+        <f>SUM(AS49:AW49)</f>
+        <v/>
+      </c>
+      <c r="Y49" s="81" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B50" s="72">
+        <f>B49+1</f>
+        <v/>
+      </c>
+      <c r="C50" s="72">
+        <f>IF(K50="Vacant","Vac",IF(K50="Model","Model",IF(K50="Admin","Admin",IF(K50="Down","Down",IF(K50="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D50" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I50,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E50" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D50,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F50" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D50,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G50" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D50,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H50" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-5</t>
+        </is>
+      </c>
+      <c r="I50" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J50" s="80" t="n">
+        <v>1066</v>
+      </c>
+      <c r="K50" s="72" t="inlineStr">
+        <is>
+          <t>Belcher, Keira</t>
+        </is>
+      </c>
+      <c r="L50" s="81" t="n">
+        <v>1349</v>
+      </c>
+      <c r="M50" s="81">
+        <f>Y50</f>
+        <v/>
+      </c>
+      <c r="N50" s="82" t="n">
+        <v>45495</v>
+      </c>
+      <c r="O50" s="82" t="n">
+        <v>45860</v>
+      </c>
+      <c r="P50" s="82" t="n">
+        <v>46224</v>
+      </c>
+      <c r="R50" s="81">
+        <f>SUM(AB50:AK50)</f>
+        <v/>
+      </c>
+      <c r="S50" s="81">
+        <f>SUM(AM50:AQ50)</f>
+        <v/>
+      </c>
+      <c r="T50" s="81">
+        <f>SUM(AS50:AW50)</f>
+        <v/>
+      </c>
+      <c r="Y50" s="81" t="n">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B51" s="72">
+        <f>B50+1</f>
+        <v/>
+      </c>
+      <c r="C51" s="72">
+        <f>IF(K51="Vacant","Vac",IF(K51="Model","Model",IF(K51="Admin","Admin",IF(K51="Down","Down",IF(K51="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D51" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I51,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E51" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D51,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F51" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D51,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G51" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D51,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H51" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-6</t>
+        </is>
+      </c>
+      <c r="I51" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J51" s="80" t="n">
+        <v>840</v>
+      </c>
+      <c r="K51" s="72" t="inlineStr">
+        <is>
+          <t>Harrison, Davis</t>
+        </is>
+      </c>
+      <c r="L51" s="81" t="n">
+        <v>1374</v>
+      </c>
+      <c r="M51" s="81">
+        <f>Y51</f>
+        <v/>
+      </c>
+      <c r="N51" s="82" t="n">
+        <v>45709</v>
+      </c>
+      <c r="O51" s="82" t="n">
+        <v>46074</v>
+      </c>
+      <c r="P51" s="82" t="n">
+        <v>46438</v>
+      </c>
+      <c r="R51" s="81">
+        <f>SUM(AB51:AK51)</f>
+        <v/>
+      </c>
+      <c r="S51" s="81">
+        <f>SUM(AM51:AQ51)</f>
+        <v/>
+      </c>
+      <c r="T51" s="81">
+        <f>SUM(AS51:AW51)</f>
+        <v/>
+      </c>
+      <c r="Y51" s="81" t="n">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B52" s="72">
+        <f>B51+1</f>
+        <v/>
+      </c>
+      <c r="C52" s="72">
+        <f>IF(K52="Vacant","Vac",IF(K52="Model","Model",IF(K52="Admin","Admin",IF(K52="Down","Down",IF(K52="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D52" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I52,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E52" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D52,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F52" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D52,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G52" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D52,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H52" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-7</t>
+        </is>
+      </c>
+      <c r="I52" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J52" s="80" t="n">
+        <v>965</v>
+      </c>
+      <c r="K52" s="72" t="inlineStr">
+        <is>
+          <t>Steele, Christopher</t>
+        </is>
+      </c>
+      <c r="L52" s="81" t="n">
+        <v>1374</v>
+      </c>
+      <c r="M52" s="81">
+        <f>Y52</f>
+        <v/>
+      </c>
+      <c r="N52" s="82" t="n">
+        <v>44281</v>
+      </c>
+      <c r="O52" s="82" t="n">
+        <v>45926</v>
+      </c>
+      <c r="P52" s="82" t="n">
+        <v>46290</v>
+      </c>
+      <c r="R52" s="81">
+        <f>SUM(AB52:AK52)</f>
+        <v/>
+      </c>
+      <c r="S52" s="81">
+        <f>SUM(AM52:AQ52)</f>
+        <v/>
+      </c>
+      <c r="T52" s="81">
+        <f>SUM(AS52:AW52)</f>
+        <v/>
+      </c>
+      <c r="Y52" s="81" t="n">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B53" s="72">
+        <f>B52+1</f>
+        <v/>
+      </c>
+      <c r="C53" s="72">
+        <f>IF(K53="Vacant","Vac",IF(K53="Model","Model",IF(K53="Admin","Admin",IF(K53="Down","Down",IF(K53="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D53" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I53,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E53" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D53,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F53" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D53,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G53" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D53,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H53" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-8</t>
+        </is>
+      </c>
+      <c r="I53" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J53" s="80" t="n">
+        <v>475</v>
+      </c>
+      <c r="K53" s="72" t="inlineStr">
+        <is>
+          <t>Rodriguez, Larissa</t>
+        </is>
+      </c>
+      <c r="L53" s="81" t="n">
+        <v>1049</v>
+      </c>
+      <c r="M53" s="81">
+        <f>Y53</f>
+        <v/>
+      </c>
+      <c r="N53" s="82" t="n">
+        <v>46042</v>
+      </c>
+      <c r="O53" s="82" t="n">
+        <v>46042</v>
+      </c>
+      <c r="P53" s="82" t="n">
+        <v>46496</v>
+      </c>
+      <c r="R53" s="81">
+        <f>SUM(AB53:AK53)</f>
+        <v/>
+      </c>
+      <c r="S53" s="81">
+        <f>SUM(AM53:AQ53)</f>
+        <v/>
+      </c>
+      <c r="T53" s="81">
+        <f>SUM(AS53:AW53)</f>
+        <v/>
+      </c>
+      <c r="Y53" s="81" t="n">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B54" s="72">
+        <f>B53+1</f>
+        <v/>
+      </c>
+      <c r="C54" s="72">
+        <f>IF(K54="Vacant","Vac",IF(K54="Model","Model",IF(K54="Admin","Admin",IF(K54="Down","Down",IF(K54="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D54" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I54,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E54" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D54,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F54" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D54,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G54" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D54,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H54" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-9</t>
+        </is>
+      </c>
+      <c r="I54" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J54" s="80" t="n">
+        <v>723</v>
+      </c>
+      <c r="K54" s="72" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="L54" s="81" t="n">
+        <v>1355</v>
+      </c>
+      <c r="M54" s="81">
+        <f>Y54</f>
+        <v/>
+      </c>
+      <c r="R54" s="81">
+        <f>SUM(AB54:AK54)</f>
+        <v/>
+      </c>
+      <c r="S54" s="81">
+        <f>SUM(AM54:AQ54)</f>
+        <v/>
+      </c>
+      <c r="T54" s="81">
+        <f>SUM(AS54:AW54)</f>
+        <v/>
+      </c>
+      <c r="Y54" s="81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B55" s="72">
+        <f>B54+1</f>
+        <v/>
+      </c>
+      <c r="C55" s="72">
+        <f>IF(K55="Vacant","Vac",IF(K55="Model","Model",IF(K55="Admin","Admin",IF(K55="Down","Down",IF(K55="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D55" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I55,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E55" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D55,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F55" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D55,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G55" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D55,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H55" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-10</t>
+        </is>
+      </c>
+      <c r="I55" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J55" s="80" t="n">
+        <v>744</v>
+      </c>
+      <c r="K55" s="72" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="L55" s="81" t="n">
+        <v>1355</v>
+      </c>
+      <c r="M55" s="81">
+        <f>Y55</f>
+        <v/>
+      </c>
+      <c r="R55" s="81">
+        <f>SUM(AB55:AK55)</f>
+        <v/>
+      </c>
+      <c r="S55" s="81">
+        <f>SUM(AM55:AQ55)</f>
+        <v/>
+      </c>
+      <c r="T55" s="81">
+        <f>SUM(AS55:AW55)</f>
+        <v/>
+      </c>
+      <c r="Y55" s="81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B56" s="72">
+        <f>B55+1</f>
+        <v/>
+      </c>
+      <c r="C56" s="72">
+        <f>IF(K56="Vacant","Vac",IF(K56="Model","Model",IF(K56="Admin","Admin",IF(K56="Down","Down",IF(K56="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D56" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I56,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E56" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D56,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F56" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D56,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G56" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D56,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H56" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-11</t>
+        </is>
+      </c>
+      <c r="I56" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J56" s="80" t="n">
+        <v>720</v>
+      </c>
+      <c r="K56" s="72" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="L56" s="81" t="n">
+        <v>990</v>
+      </c>
+      <c r="M56" s="81">
+        <f>Y56</f>
+        <v/>
+      </c>
+      <c r="R56" s="81">
+        <f>SUM(AB56:AK56)</f>
+        <v/>
+      </c>
+      <c r="S56" s="81">
+        <f>SUM(AM56:AQ56)</f>
+        <v/>
+      </c>
+      <c r="T56" s="81">
+        <f>SUM(AS56:AW56)</f>
+        <v/>
+      </c>
+      <c r="Y56" s="81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B57" s="72">
+        <f>B56+1</f>
+        <v/>
+      </c>
+      <c r="C57" s="72">
+        <f>IF(K57="Vacant","Vac",IF(K57="Model","Model",IF(K57="Admin","Admin",IF(K57="Down","Down",IF(K57="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D57" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I57,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E57" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D57,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F57" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D57,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G57" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D57,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H57" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-12</t>
+        </is>
+      </c>
+      <c r="I57" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J57" s="80" t="n">
+        <v>656</v>
+      </c>
+      <c r="K57" s="72" t="inlineStr">
+        <is>
+          <t>Montgomery-Lewis, Jaylynne</t>
+        </is>
+      </c>
+      <c r="L57" s="81" t="n">
+        <v>1139</v>
+      </c>
+      <c r="M57" s="81">
+        <f>Y57</f>
+        <v/>
+      </c>
+      <c r="N57" s="82" t="n">
+        <v>45863</v>
+      </c>
+      <c r="O57" s="82" t="n">
+        <v>45863</v>
+      </c>
+      <c r="P57" s="82" t="n">
+        <v>46227</v>
+      </c>
+      <c r="R57" s="81">
+        <f>SUM(AB57:AK57)</f>
+        <v/>
+      </c>
+      <c r="S57" s="81">
+        <f>SUM(AM57:AQ57)</f>
+        <v/>
+      </c>
+      <c r="T57" s="81">
+        <f>SUM(AS57:AW57)</f>
+        <v/>
+      </c>
+      <c r="Y57" s="81" t="n">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B58" s="72">
+        <f>B57+1</f>
+        <v/>
+      </c>
+      <c r="C58" s="72">
+        <f>IF(K58="Vacant","Vac",IF(K58="Model","Model",IF(K58="Admin","Admin",IF(K58="Down","Down",IF(K58="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D58" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I58,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E58" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D58,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F58" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D58,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G58" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D58,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H58" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-14</t>
+        </is>
+      </c>
+      <c r="I58" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J58" s="80" t="n">
+        <v>476</v>
+      </c>
+      <c r="K58" s="72" t="inlineStr">
+        <is>
+          <t>Von Hassell, Damontay</t>
+        </is>
+      </c>
+      <c r="L58" s="81" t="n">
+        <v>1049</v>
+      </c>
+      <c r="M58" s="81">
+        <f>Y58</f>
+        <v/>
+      </c>
+      <c r="N58" s="82" t="n">
+        <v>45831</v>
+      </c>
+      <c r="O58" s="82" t="n">
+        <v>45831</v>
+      </c>
+      <c r="P58" s="82" t="n">
+        <v>46195</v>
+      </c>
+      <c r="R58" s="81">
+        <f>SUM(AB58:AK58)</f>
+        <v/>
+      </c>
+      <c r="S58" s="81">
+        <f>SUM(AM58:AQ58)</f>
+        <v/>
+      </c>
+      <c r="T58" s="81">
+        <f>SUM(AS58:AW58)</f>
+        <v/>
+      </c>
+      <c r="Y58" s="81" t="n">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B59" s="72">
+        <f>B58+1</f>
+        <v/>
+      </c>
+      <c r="C59" s="72">
+        <f>IF(K59="Vacant","Vac",IF(K59="Model","Model",IF(K59="Admin","Admin",IF(K59="Down","Down",IF(K59="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D59" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I59,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E59" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D59,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F59" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D59,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G59" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D59,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H59" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-15</t>
+        </is>
+      </c>
+      <c r="I59" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J59" s="80" t="n">
+        <v>723</v>
+      </c>
+      <c r="K59" s="72" t="inlineStr">
+        <is>
+          <t>Sorrells, Kashon</t>
+        </is>
+      </c>
+      <c r="L59" s="81" t="n">
+        <v>1164</v>
+      </c>
+      <c r="M59" s="81">
+        <f>Y59</f>
+        <v/>
+      </c>
+      <c r="N59" s="82" t="n">
+        <v>44250</v>
+      </c>
+      <c r="O59" s="82" t="n">
+        <v>46113</v>
+      </c>
+      <c r="R59" s="81">
+        <f>SUM(AB59:AK59)</f>
+        <v/>
+      </c>
+      <c r="S59" s="81">
+        <f>SUM(AM59:AQ59)</f>
+        <v/>
+      </c>
+      <c r="T59" s="81">
+        <f>SUM(AS59:AW59)</f>
+        <v/>
+      </c>
+      <c r="Y59" s="81" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B60" s="72">
+        <f>B59+1</f>
+        <v/>
+      </c>
+      <c r="C60" s="72">
+        <f>IF(K60="Vacant","Vac",IF(K60="Model","Model",IF(K60="Admin","Admin",IF(K60="Down","Down",IF(K60="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D60" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I60,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E60" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D60,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F60" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D60,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G60" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D60,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H60" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-16</t>
+        </is>
+      </c>
+      <c r="I60" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J60" s="80" t="n">
+        <v>516</v>
+      </c>
+      <c r="K60" s="72" t="inlineStr">
+        <is>
+          <t>Pitvorec, Jeremy</t>
+        </is>
+      </c>
+      <c r="L60" s="81" t="n">
+        <v>1149</v>
+      </c>
+      <c r="M60" s="81">
+        <f>Y60</f>
+        <v/>
+      </c>
+      <c r="N60" s="82" t="n">
+        <v>44621</v>
+      </c>
+      <c r="O60" s="82" t="n">
+        <v>46082</v>
+      </c>
+      <c r="P60" s="82" t="n">
+        <v>46538</v>
+      </c>
+      <c r="R60" s="81">
+        <f>SUM(AB60:AK60)</f>
+        <v/>
+      </c>
+      <c r="S60" s="81">
+        <f>SUM(AM60:AQ60)</f>
+        <v/>
+      </c>
+      <c r="T60" s="81">
+        <f>SUM(AS60:AW60)</f>
+        <v/>
+      </c>
+      <c r="Y60" s="81" t="n">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B61" s="72">
+        <f>B60+1</f>
+        <v/>
+      </c>
+      <c r="C61" s="72">
+        <f>IF(K61="Vacant","Vac",IF(K61="Model","Model",IF(K61="Admin","Admin",IF(K61="Down","Down",IF(K61="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D61" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I61,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E61" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D61,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F61" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D61,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G61" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D61,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H61" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-17</t>
+        </is>
+      </c>
+      <c r="I61" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J61" s="80" t="n">
+        <v>765</v>
+      </c>
+      <c r="K61" s="72" t="inlineStr">
+        <is>
+          <t>Quiroz, Espie</t>
+        </is>
+      </c>
+      <c r="L61" s="81" t="n">
+        <v>1179</v>
+      </c>
+      <c r="M61" s="81">
+        <f>Y61</f>
+        <v/>
+      </c>
+      <c r="N61" s="82" t="n">
+        <v>45971</v>
+      </c>
+      <c r="O61" s="82" t="n">
+        <v>45971</v>
+      </c>
+      <c r="P61" s="82" t="n">
+        <v>46335</v>
+      </c>
+      <c r="R61" s="81">
+        <f>SUM(AB61:AK61)</f>
+        <v/>
+      </c>
+      <c r="S61" s="81">
+        <f>SUM(AM61:AQ61)</f>
+        <v/>
+      </c>
+      <c r="T61" s="81">
+        <f>SUM(AS61:AW61)</f>
+        <v/>
+      </c>
+      <c r="Y61" s="81" t="n">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B62" s="72">
+        <f>B61+1</f>
+        <v/>
+      </c>
+      <c r="C62" s="72">
+        <f>IF(K62="Vacant","Vac",IF(K62="Model","Model",IF(K62="Admin","Admin",IF(K62="Down","Down",IF(K62="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D62" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I62,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E62" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D62,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F62" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D62,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G62" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D62,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H62" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-18</t>
+        </is>
+      </c>
+      <c r="I62" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J62" s="80" t="n">
+        <v>765</v>
+      </c>
+      <c r="K62" s="72" t="inlineStr">
+        <is>
+          <t>Ostrander, Bradley</t>
+        </is>
+      </c>
+      <c r="L62" s="81" t="n">
+        <v>1124</v>
+      </c>
+      <c r="M62" s="81">
+        <f>Y62</f>
+        <v/>
+      </c>
+      <c r="N62" s="82" t="n">
+        <v>45946</v>
+      </c>
+      <c r="O62" s="82" t="n">
+        <v>45946</v>
+      </c>
+      <c r="P62" s="82" t="n">
+        <v>46310</v>
+      </c>
+      <c r="R62" s="81">
+        <f>SUM(AB62:AK62)</f>
+        <v/>
+      </c>
+      <c r="S62" s="81">
+        <f>SUM(AM62:AQ62)</f>
+        <v/>
+      </c>
+      <c r="T62" s="81">
+        <f>SUM(AS62:AW62)</f>
+        <v/>
+      </c>
+      <c r="Y62" s="81" t="n">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B63" s="72">
+        <f>B62+1</f>
+        <v/>
+      </c>
+      <c r="C63" s="72">
+        <f>IF(K63="Vacant","Vac",IF(K63="Model","Model",IF(K63="Admin","Admin",IF(K63="Down","Down",IF(K63="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D63" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I63,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E63" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D63,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F63" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D63,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G63" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D63,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H63" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-19</t>
+        </is>
+      </c>
+      <c r="I63" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J63" s="80" t="n">
+        <v>781</v>
+      </c>
+      <c r="K63" s="72" t="inlineStr">
+        <is>
+          <t>Webb, Kennetha</t>
+        </is>
+      </c>
+      <c r="L63" s="81" t="n">
+        <v>1324</v>
+      </c>
+      <c r="M63" s="81">
+        <f>Y63</f>
+        <v/>
+      </c>
+      <c r="N63" s="82" t="n">
+        <v>45926</v>
+      </c>
+      <c r="O63" s="82" t="n">
+        <v>45926</v>
+      </c>
+      <c r="P63" s="82" t="n">
+        <v>46381</v>
+      </c>
+      <c r="R63" s="81">
+        <f>SUM(AB63:AK63)</f>
+        <v/>
+      </c>
+      <c r="S63" s="81">
+        <f>SUM(AM63:AQ63)</f>
+        <v/>
+      </c>
+      <c r="T63" s="81">
+        <f>SUM(AS63:AW63)</f>
+        <v/>
+      </c>
+      <c r="Y63" s="81" t="n">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B64" s="72">
+        <f>B63+1</f>
+        <v/>
+      </c>
+      <c r="C64" s="72">
+        <f>IF(K64="Vacant","Vac",IF(K64="Model","Model",IF(K64="Admin","Admin",IF(K64="Down","Down",IF(K64="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D64" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I64,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E64" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D64,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F64" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D64,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G64" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D64,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H64" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-20</t>
+        </is>
+      </c>
+      <c r="I64" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J64" s="80" t="n">
+        <v>515</v>
+      </c>
+      <c r="K64" s="72" t="inlineStr">
+        <is>
+          <t>Keaton, Aniya</t>
+        </is>
+      </c>
+      <c r="L64" s="81" t="n">
+        <v>1114</v>
+      </c>
+      <c r="M64" s="81">
+        <f>Y64</f>
+        <v/>
+      </c>
+      <c r="N64" s="82" t="n">
+        <v>45836</v>
+      </c>
+      <c r="O64" s="82" t="n">
+        <v>45836</v>
+      </c>
+      <c r="P64" s="82" t="n">
+        <v>46200</v>
+      </c>
+      <c r="R64" s="81">
+        <f>SUM(AB64:AK64)</f>
+        <v/>
+      </c>
+      <c r="S64" s="81">
+        <f>SUM(AM64:AQ64)</f>
+        <v/>
+      </c>
+      <c r="T64" s="81">
+        <f>SUM(AS64:AW64)</f>
+        <v/>
+      </c>
+      <c r="Y64" s="81" t="n">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B65" s="72">
+        <f>B64+1</f>
+        <v/>
+      </c>
+      <c r="C65" s="72">
+        <f>IF(K65="Vacant","Vac",IF(K65="Model","Model",IF(K65="Admin","Admin",IF(K65="Down","Down",IF(K65="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D65" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I65,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E65" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D65,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F65" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D65,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G65" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D65,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H65" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-21</t>
+        </is>
+      </c>
+      <c r="I65" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J65" s="80" t="n">
+        <v>515</v>
+      </c>
+      <c r="K65" s="72" t="inlineStr">
+        <is>
+          <t>Sanchez Hernandez, Jose Adolfo</t>
+        </is>
+      </c>
+      <c r="L65" s="81" t="n">
+        <v>1169</v>
+      </c>
+      <c r="M65" s="81">
+        <f>Y65</f>
+        <v/>
+      </c>
+      <c r="N65" s="82" t="n">
+        <v>45623</v>
+      </c>
+      <c r="O65" s="82" t="n">
+        <v>45988</v>
+      </c>
+      <c r="P65" s="82" t="n">
+        <v>46352</v>
+      </c>
+      <c r="R65" s="81">
+        <f>SUM(AB65:AK65)</f>
+        <v/>
+      </c>
+      <c r="S65" s="81">
+        <f>SUM(AM65:AQ65)</f>
+        <v/>
+      </c>
+      <c r="T65" s="81">
+        <f>SUM(AS65:AW65)</f>
+        <v/>
+      </c>
+      <c r="Y65" s="81" t="n">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B66" s="72">
+        <f>B65+1</f>
+        <v/>
+      </c>
+      <c r="C66" s="72">
+        <f>IF(K66="Vacant","Vac",IF(K66="Model","Model",IF(K66="Admin","Admin",IF(K66="Down","Down",IF(K66="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D66" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I66,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E66" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D66,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F66" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D66,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G66" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D66,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H66" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-22</t>
+        </is>
+      </c>
+      <c r="I66" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J66" s="80" t="n">
+        <v>748</v>
+      </c>
+      <c r="K66" s="72" t="inlineStr">
+        <is>
+          <t>Sablas, Mary</t>
+        </is>
+      </c>
+      <c r="L66" s="81" t="n">
+        <v>1109</v>
+      </c>
+      <c r="M66" s="81">
+        <f>Y66</f>
+        <v/>
+      </c>
+      <c r="N66" s="82" t="n">
+        <v>45308</v>
+      </c>
+      <c r="O66" s="82" t="n">
+        <v>46039</v>
+      </c>
+      <c r="P66" s="82" t="n">
+        <v>46493</v>
+      </c>
+      <c r="R66" s="81">
+        <f>SUM(AB66:AK66)</f>
+        <v/>
+      </c>
+      <c r="S66" s="81">
+        <f>SUM(AM66:AQ66)</f>
+        <v/>
+      </c>
+      <c r="T66" s="81">
+        <f>SUM(AS66:AW66)</f>
+        <v/>
+      </c>
+      <c r="Y66" s="81" t="n">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B67" s="72">
+        <f>B66+1</f>
+        <v/>
+      </c>
+      <c r="C67" s="72">
+        <f>IF(K67="Vacant","Vac",IF(K67="Model","Model",IF(K67="Admin","Admin",IF(K67="Down","Down",IF(K67="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D67" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I67,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E67" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D67,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F67" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D67,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G67" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D67,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H67" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-23</t>
+        </is>
+      </c>
+      <c r="I67" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J67" s="80" t="n">
+        <v>888</v>
+      </c>
+      <c r="K67" s="72" t="inlineStr">
+        <is>
+          <t>Sell, Miranda</t>
+        </is>
+      </c>
+      <c r="L67" s="81" t="n">
+        <v>1384</v>
+      </c>
+      <c r="M67" s="81">
+        <f>Y67</f>
+        <v/>
+      </c>
+      <c r="N67" s="82" t="n">
+        <v>45990</v>
+      </c>
+      <c r="O67" s="82" t="n">
+        <v>45990</v>
+      </c>
+      <c r="P67" s="82" t="n">
+        <v>46354</v>
+      </c>
+      <c r="R67" s="81">
+        <f>SUM(AB67:AK67)</f>
+        <v/>
+      </c>
+      <c r="S67" s="81">
+        <f>SUM(AM67:AQ67)</f>
+        <v/>
+      </c>
+      <c r="T67" s="81">
+        <f>SUM(AS67:AW67)</f>
+        <v/>
+      </c>
+      <c r="Y67" s="81" t="n">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B68" s="72">
+        <f>B67+1</f>
+        <v/>
+      </c>
+      <c r="C68" s="72">
+        <f>IF(K68="Vacant","Vac",IF(K68="Model","Model",IF(K68="Admin","Admin",IF(K68="Down","Down",IF(K68="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D68" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I68,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E68" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D68,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F68" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D68,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G68" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D68,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H68" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-24</t>
+        </is>
+      </c>
+      <c r="I68" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J68" s="80" t="n">
+        <v>683</v>
+      </c>
+      <c r="K68" s="72" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="L68" s="81" t="n">
+        <v>1355</v>
+      </c>
+      <c r="M68" s="81">
+        <f>Y68</f>
+        <v/>
+      </c>
+      <c r="R68" s="81">
+        <f>SUM(AB68:AK68)</f>
+        <v/>
+      </c>
+      <c r="S68" s="81">
+        <f>SUM(AM68:AQ68)</f>
+        <v/>
+      </c>
+      <c r="T68" s="81">
+        <f>SUM(AS68:AW68)</f>
+        <v/>
+      </c>
+      <c r="Y68" s="81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B69" s="72">
+        <f>B68+1</f>
+        <v/>
+      </c>
+      <c r="C69" s="72">
+        <f>IF(K69="Vacant","Vac",IF(K69="Model","Model",IF(K69="Admin","Admin",IF(K69="Down","Down",IF(K69="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D69" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I69,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E69" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D69,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F69" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D69,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G69" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D69,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H69" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-25</t>
+        </is>
+      </c>
+      <c r="I69" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J69" s="80" t="n">
+        <v>781</v>
+      </c>
+      <c r="K69" s="72" t="inlineStr">
+        <is>
+          <t>Williams, Andre</t>
+        </is>
+      </c>
+      <c r="L69" s="81" t="n">
+        <v>1314</v>
+      </c>
+      <c r="M69" s="81">
+        <f>Y69</f>
+        <v/>
+      </c>
+      <c r="N69" s="82" t="n">
+        <v>45717</v>
+      </c>
+      <c r="O69" s="82" t="n">
+        <v>46082</v>
+      </c>
+      <c r="P69" s="82" t="n">
+        <v>46446</v>
+      </c>
+      <c r="R69" s="81">
+        <f>SUM(AB69:AK69)</f>
+        <v/>
+      </c>
+      <c r="S69" s="81">
+        <f>SUM(AM69:AQ69)</f>
+        <v/>
+      </c>
+      <c r="T69" s="81">
+        <f>SUM(AS69:AW69)</f>
+        <v/>
+      </c>
+      <c r="Y69" s="81" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B70" s="72">
+        <f>B69+1</f>
+        <v/>
+      </c>
+      <c r="C70" s="72">
+        <f>IF(K70="Vacant","Vac",IF(K70="Model","Model",IF(K70="Admin","Admin",IF(K70="Down","Down",IF(K70="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D70" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I70,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E70" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D70,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F70" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D70,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G70" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D70,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H70" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-26</t>
+        </is>
+      </c>
+      <c r="I70" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J70" s="80" t="n">
+        <v>685</v>
+      </c>
+      <c r="K70" s="72" t="inlineStr">
+        <is>
+          <t>Hausley, Isaiah</t>
+        </is>
+      </c>
+      <c r="L70" s="81" t="n">
+        <v>1364</v>
+      </c>
+      <c r="M70" s="81">
+        <f>Y70</f>
+        <v/>
+      </c>
+      <c r="N70" s="82" t="n">
+        <v>44909</v>
+      </c>
+      <c r="O70" s="82" t="n">
+        <v>46039</v>
+      </c>
+      <c r="P70" s="82" t="n">
+        <v>46403</v>
+      </c>
+      <c r="R70" s="81">
+        <f>SUM(AB70:AK70)</f>
+        <v/>
+      </c>
+      <c r="S70" s="81">
+        <f>SUM(AM70:AQ70)</f>
+        <v/>
+      </c>
+      <c r="T70" s="81">
+        <f>SUM(AS70:AW70)</f>
+        <v/>
+      </c>
+      <c r="Y70" s="81" t="n">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B71" s="72">
+        <f>B70+1</f>
+        <v/>
+      </c>
+      <c r="C71" s="72">
+        <f>IF(K71="Vacant","Vac",IF(K71="Model","Model",IF(K71="Admin","Admin",IF(K71="Down","Down",IF(K71="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D71" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I71,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E71" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D71,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F71" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D71,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G71" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D71,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H71" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-27</t>
+        </is>
+      </c>
+      <c r="I71" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J71" s="80" t="n">
+        <v>516</v>
+      </c>
+      <c r="K71" s="72" t="inlineStr">
+        <is>
+          <t>West, Brayden</t>
+        </is>
+      </c>
+      <c r="L71" s="81" t="n">
+        <v>1149</v>
+      </c>
+      <c r="M71" s="81">
+        <f>Y71</f>
+        <v/>
+      </c>
+      <c r="N71" s="82" t="n">
+        <v>45869</v>
+      </c>
+      <c r="O71" s="82" t="n">
+        <v>45869</v>
+      </c>
+      <c r="P71" s="82" t="n">
+        <v>46233</v>
+      </c>
+      <c r="R71" s="81">
+        <f>SUM(AB71:AK71)</f>
+        <v/>
+      </c>
+      <c r="S71" s="81">
+        <f>SUM(AM71:AQ71)</f>
+        <v/>
+      </c>
+      <c r="T71" s="81">
+        <f>SUM(AS71:AW71)</f>
+        <v/>
+      </c>
+      <c r="Y71" s="81" t="n">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B72" s="72">
+        <f>B71+1</f>
+        <v/>
+      </c>
+      <c r="C72" s="72">
+        <f>IF(K72="Vacant","Vac",IF(K72="Model","Model",IF(K72="Admin","Admin",IF(K72="Down","Down",IF(K72="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D72" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I72,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E72" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D72,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F72" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D72,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G72" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D72,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H72" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-28</t>
+        </is>
+      </c>
+      <c r="I72" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J72" s="80" t="n">
+        <v>775</v>
+      </c>
+      <c r="K72" s="72" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="L72" s="81" t="n">
+        <v>1355</v>
+      </c>
+      <c r="M72" s="81">
+        <f>Y72</f>
+        <v/>
+      </c>
+      <c r="R72" s="81">
+        <f>SUM(AB72:AK72)</f>
+        <v/>
+      </c>
+      <c r="S72" s="81">
+        <f>SUM(AM72:AQ72)</f>
+        <v/>
+      </c>
+      <c r="T72" s="81">
+        <f>SUM(AS72:AW72)</f>
+        <v/>
+      </c>
+      <c r="Y72" s="81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B73" s="72">
+        <f>B72+1</f>
+        <v/>
+      </c>
+      <c r="C73" s="72">
+        <f>IF(K73="Vacant","Vac",IF(K73="Model","Model",IF(K73="Admin","Admin",IF(K73="Down","Down",IF(K73="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D73" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I73,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E73" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D73,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F73" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D73,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G73" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D73,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H73" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-29</t>
+        </is>
+      </c>
+      <c r="I73" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J73" s="80" t="n">
+        <v>712</v>
+      </c>
+      <c r="K73" s="72" t="inlineStr">
+        <is>
+          <t>Ndiaye, Omar</t>
+        </is>
+      </c>
+      <c r="L73" s="81" t="n">
+        <v>1349</v>
+      </c>
+      <c r="M73" s="81">
+        <f>Y73</f>
+        <v/>
+      </c>
+      <c r="N73" s="82" t="n">
+        <v>45120</v>
+      </c>
+      <c r="O73" s="82" t="n">
+        <v>45851</v>
+      </c>
+      <c r="P73" s="82" t="n">
+        <v>46215</v>
+      </c>
+      <c r="R73" s="81">
+        <f>SUM(AB73:AK73)</f>
+        <v/>
+      </c>
+      <c r="S73" s="81">
+        <f>SUM(AM73:AQ73)</f>
+        <v/>
+      </c>
+      <c r="T73" s="81">
+        <f>SUM(AS73:AW73)</f>
+        <v/>
+      </c>
+      <c r="Y73" s="81" t="n">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B74" s="72">
+        <f>B73+1</f>
+        <v/>
+      </c>
+      <c r="C74" s="72">
+        <f>IF(K74="Vacant","Vac",IF(K74="Model","Model",IF(K74="Admin","Admin",IF(K74="Down","Down",IF(K74="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D74" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I74,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E74" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D74,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F74" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D74,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G74" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D74,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H74" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-30</t>
+        </is>
+      </c>
+      <c r="I74" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J74" s="80" t="n">
+        <v>712</v>
+      </c>
+      <c r="K74" s="72" t="inlineStr">
+        <is>
+          <t>Ogundipe, Eniola</t>
+        </is>
+      </c>
+      <c r="L74" s="81" t="n">
+        <v>1124</v>
+      </c>
+      <c r="M74" s="81">
+        <f>Y74</f>
+        <v/>
+      </c>
+      <c r="N74" s="82" t="n">
+        <v>45077</v>
+      </c>
+      <c r="O74" s="82" t="n">
+        <v>45808</v>
+      </c>
+      <c r="P74" s="82" t="n">
+        <v>46172</v>
+      </c>
+      <c r="R74" s="81">
+        <f>SUM(AB74:AK74)</f>
+        <v/>
+      </c>
+      <c r="S74" s="81">
+        <f>SUM(AM74:AQ74)</f>
+        <v/>
+      </c>
+      <c r="T74" s="81">
+        <f>SUM(AS74:AW74)</f>
+        <v/>
+      </c>
+      <c r="Y74" s="81" t="n">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B75" s="72">
+        <f>B74+1</f>
+        <v/>
+      </c>
+      <c r="C75" s="72">
+        <f>IF(K75="Vacant","Vac",IF(K75="Model","Model",IF(K75="Admin","Admin",IF(K75="Down","Down",IF(K75="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D75" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I75,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E75" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D75,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F75" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D75,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G75" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D75,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H75" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-31</t>
+        </is>
+      </c>
+      <c r="I75" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J75" s="80" t="n">
+        <v>781</v>
+      </c>
+      <c r="K75" s="72" t="inlineStr">
+        <is>
+          <t>HUTZELL, LILLIAN</t>
+        </is>
+      </c>
+      <c r="L75" s="81" t="n">
+        <v>1349</v>
+      </c>
+      <c r="M75" s="81">
+        <f>Y75</f>
+        <v/>
+      </c>
+      <c r="N75" s="82" t="n">
+        <v>44678</v>
+      </c>
+      <c r="O75" s="82" t="n">
+        <v>46139</v>
+      </c>
+      <c r="P75" s="82" t="n">
+        <v>46503</v>
+      </c>
+      <c r="R75" s="81">
+        <f>SUM(AB75:AK75)</f>
+        <v/>
+      </c>
+      <c r="S75" s="81">
+        <f>SUM(AM75:AQ75)</f>
+        <v/>
+      </c>
+      <c r="T75" s="81">
+        <f>SUM(AS75:AW75)</f>
+        <v/>
+      </c>
+      <c r="Y75" s="81" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B76" s="72">
+        <f>B75+1</f>
+        <v/>
+      </c>
+      <c r="C76" s="72">
+        <f>IF(K76="Vacant","Vac",IF(K76="Model","Model",IF(K76="Admin","Admin",IF(K76="Down","Down",IF(K76="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D76" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I76,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E76" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D76,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F76" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D76,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G76" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D76,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H76" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-32</t>
+        </is>
+      </c>
+      <c r="I76" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J76" s="80" t="n">
+        <v>686</v>
+      </c>
+      <c r="K76" s="72" t="inlineStr">
+        <is>
+          <t>La Flower, Michael</t>
+        </is>
+      </c>
+      <c r="L76" s="81" t="n">
+        <v>1334</v>
+      </c>
+      <c r="M76" s="81">
+        <f>Y76</f>
+        <v/>
+      </c>
+      <c r="N76" s="82" t="n">
+        <v>45898</v>
+      </c>
+      <c r="O76" s="82" t="n">
+        <v>45898</v>
+      </c>
+      <c r="P76" s="82" t="n">
+        <v>46262</v>
+      </c>
+      <c r="R76" s="81">
+        <f>SUM(AB76:AK76)</f>
+        <v/>
+      </c>
+      <c r="S76" s="81">
+        <f>SUM(AM76:AQ76)</f>
+        <v/>
+      </c>
+      <c r="T76" s="81">
+        <f>SUM(AS76:AW76)</f>
+        <v/>
+      </c>
+      <c r="Y76" s="81" t="n">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B77" s="72">
+        <f>B76+1</f>
+        <v/>
+      </c>
+      <c r="C77" s="72">
+        <f>IF(K77="Vacant","Vac",IF(K77="Model","Model",IF(K77="Admin","Admin",IF(K77="Down","Down",IF(K77="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D77" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I77,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E77" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D77,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F77" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D77,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G77" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D77,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H77" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-33</t>
+        </is>
+      </c>
+      <c r="I77" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J77" s="80" t="n">
+        <v>516</v>
+      </c>
+      <c r="K77" s="72" t="inlineStr">
+        <is>
+          <t>Bowman, Katherine</t>
+        </is>
+      </c>
+      <c r="L77" s="81" t="n">
+        <v>1124</v>
+      </c>
+      <c r="M77" s="81">
+        <f>Y77</f>
+        <v/>
+      </c>
+      <c r="N77" s="82" t="n">
+        <v>45821</v>
+      </c>
+      <c r="O77" s="82" t="n">
+        <v>45821</v>
+      </c>
+      <c r="P77" s="82" t="n">
+        <v>46186</v>
+      </c>
+      <c r="R77" s="81">
+        <f>SUM(AB77:AK77)</f>
+        <v/>
+      </c>
+      <c r="S77" s="81">
+        <f>SUM(AM77:AQ77)</f>
+        <v/>
+      </c>
+      <c r="T77" s="81">
+        <f>SUM(AS77:AW77)</f>
+        <v/>
+      </c>
+      <c r="Y77" s="81" t="n">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B78" s="72">
+        <f>B77+1</f>
+        <v/>
+      </c>
+      <c r="C78" s="72">
+        <f>IF(K78="Vacant","Vac",IF(K78="Model","Model",IF(K78="Admin","Admin",IF(K78="Down","Down",IF(K78="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D78" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I78,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E78" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D78,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F78" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D78,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G78" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D78,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H78" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-34</t>
+        </is>
+      </c>
+      <c r="I78" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J78" s="80" t="n">
+        <v>748</v>
+      </c>
+      <c r="K78" s="72" t="inlineStr">
+        <is>
+          <t>Asher, Derrick</t>
+        </is>
+      </c>
+      <c r="L78" s="81" t="n">
+        <v>1334</v>
+      </c>
+      <c r="M78" s="81">
+        <f>Y78</f>
+        <v/>
+      </c>
+      <c r="N78" s="82" t="n">
+        <v>45855</v>
+      </c>
+      <c r="O78" s="82" t="n">
+        <v>45855</v>
+      </c>
+      <c r="P78" s="82" t="n">
+        <v>46219</v>
+      </c>
+      <c r="R78" s="81">
+        <f>SUM(AB78:AK78)</f>
+        <v/>
+      </c>
+      <c r="S78" s="81">
+        <f>SUM(AM78:AQ78)</f>
+        <v/>
+      </c>
+      <c r="T78" s="81">
+        <f>SUM(AS78:AW78)</f>
+        <v/>
+      </c>
+      <c r="Y78" s="81" t="n">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B79" s="72">
+        <f>B78+1</f>
+        <v/>
+      </c>
+      <c r="C79" s="72">
+        <f>IF(K79="Vacant","Vac",IF(K79="Model","Model",IF(K79="Admin","Admin",IF(K79="Down","Down",IF(K79="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D79" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I79,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E79" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D79,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F79" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D79,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G79" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D79,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H79" s="72" t="inlineStr">
+        <is>
+          <t>CL - 806-35</t>
+        </is>
+      </c>
+      <c r="I79" s="72" t="inlineStr">
+        <is>
+          <t>2x1A_C</t>
+        </is>
+      </c>
+      <c r="J79" s="80" t="n">
+        <v>1078</v>
+      </c>
+      <c r="K79" s="72" t="inlineStr">
+        <is>
+          <t>Mack, Morgan</t>
+        </is>
+      </c>
+      <c r="L79" s="81" t="n">
+        <v>1394</v>
+      </c>
+      <c r="M79" s="81">
+        <f>Y79</f>
+        <v/>
+      </c>
+      <c r="N79" s="82" t="n">
+        <v>46112</v>
+      </c>
+      <c r="O79" s="82" t="n">
+        <v>46112</v>
+      </c>
+      <c r="P79" s="82" t="n">
+        <v>46476</v>
+      </c>
+      <c r="R79" s="81">
+        <f>SUM(AB79:AK79)</f>
+        <v/>
+      </c>
+      <c r="S79" s="81">
+        <f>SUM(AM79:AQ79)</f>
+        <v/>
+      </c>
+      <c r="T79" s="81">
+        <f>SUM(AS79:AW79)</f>
+        <v/>
+      </c>
+      <c r="Y79" s="81" t="n">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B80" s="72">
+        <f>B79+1</f>
+        <v/>
+      </c>
+      <c r="C80" s="72">
+        <f>IF(K80="Vacant","Vac",IF(K80="Model","Model",IF(K80="Admin","Admin",IF(K80="Down","Down",IF(K80="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D80" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I80,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E80" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D80,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F80" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D80,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G80" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D80,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H80" s="72" t="inlineStr">
+        <is>
+          <t>CL - 816-1</t>
+        </is>
+      </c>
+      <c r="I80" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J80" s="80" t="n">
+        <v>540</v>
+      </c>
+      <c r="K80" s="72" t="inlineStr">
+        <is>
+          <t>Miller, Brian</t>
+        </is>
+      </c>
+      <c r="L80" s="81" t="n">
+        <v>1189</v>
+      </c>
+      <c r="M80" s="81">
+        <f>Y80</f>
+        <v/>
+      </c>
+      <c r="N80" s="82" t="n">
+        <v>45595</v>
+      </c>
+      <c r="O80" s="82" t="n">
+        <v>45960</v>
+      </c>
+      <c r="P80" s="82" t="n">
+        <v>46416</v>
+      </c>
+      <c r="R80" s="81">
+        <f>SUM(AB80:AK80)</f>
+        <v/>
+      </c>
+      <c r="S80" s="81">
+        <f>SUM(AM80:AQ80)</f>
+        <v/>
+      </c>
+      <c r="T80" s="81">
+        <f>SUM(AS80:AW80)</f>
+        <v/>
+      </c>
+      <c r="Y80" s="81" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B81" s="72">
+        <f>B80+1</f>
+        <v/>
+      </c>
+      <c r="C81" s="72">
+        <f>IF(K81="Vacant","Vac",IF(K81="Model","Model",IF(K81="Admin","Admin",IF(K81="Down","Down",IF(K81="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D81" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I81,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E81" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D81,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F81" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D81,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G81" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D81,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H81" s="72" t="inlineStr">
+        <is>
+          <t>CL - 816-2</t>
+        </is>
+      </c>
+      <c r="I81" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J81" s="80" t="n">
+        <v>775</v>
+      </c>
+      <c r="K81" s="72" t="inlineStr">
+        <is>
+          <t>Holbrook, Kendrick</t>
+        </is>
+      </c>
+      <c r="L81" s="81" t="n">
+        <v>1189</v>
+      </c>
+      <c r="M81" s="81">
+        <f>Y81</f>
+        <v/>
+      </c>
+      <c r="N81" s="82" t="n">
+        <v>45456</v>
+      </c>
+      <c r="O81" s="82" t="n">
+        <v>45821</v>
+      </c>
+      <c r="P81" s="82" t="n">
+        <v>46185</v>
+      </c>
+      <c r="R81" s="81">
+        <f>SUM(AB81:AK81)</f>
+        <v/>
+      </c>
+      <c r="S81" s="81">
+        <f>SUM(AM81:AQ81)</f>
+        <v/>
+      </c>
+      <c r="T81" s="81">
+        <f>SUM(AS81:AW81)</f>
+        <v/>
+      </c>
+      <c r="Y81" s="81" t="n">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="72">
+        <f>$D$21</f>
+        <v/>
+      </c>
+      <c r="B82" s="72">
+        <f>B81+1</f>
+        <v/>
+      </c>
+      <c r="C82" s="72">
+        <f>IF(K82="Vacant","Vac",IF(K82="Model","Model",IF(K82="Admin","Admin",IF(K82="Down","Down",IF(K82="Super","Super","Occ")))))</f>
+        <v/>
+      </c>
+      <c r="D82" s="72">
+        <f>INDEX($C$5:$C$8,MATCH(I82,$D$5:$D$8,0))</f>
+        <v/>
+      </c>
+      <c r="E82" s="72">
+        <f>INDEX($E$5:$E$8,MATCH(D82,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="F82" s="72">
+        <f>INDEX($F$5:$F$8,MATCH(D82,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="G82" s="72">
+        <f>INDEX($G$5:$G$8,MATCH(D82,$C$5:$C$8,0))</f>
+        <v/>
+      </c>
+      <c r="H82" s="72" t="inlineStr">
+        <is>
+          <t>CL - 816-3</t>
+        </is>
+      </c>
+      <c r="I82" s="72" t="inlineStr">
+        <is>
+          <t>1x1A_C</t>
+        </is>
+      </c>
+      <c r="J82" s="80" t="n">
+        <v>775</v>
+      </c>
+      <c r="K82" s="72" t="inlineStr">
+        <is>
+          <t>Bariff, Mae</t>
+        </is>
+      </c>
+      <c r="L82" s="81" t="n">
+        <v>1189</v>
+      </c>
+      <c r="M82" s="81">
+        <f>Y82</f>
+        <v/>
+      </c>
+      <c r="N82" s="82" t="n">
+        <v>45838</v>
+      </c>
+      <c r="O82" s="82" t="n">
+        <v>45838</v>
+      </c>
+      <c r="P82" s="82" t="n">
+        <v>46232</v>
+      </c>
+      <c r="R82" s="81">
+        <f>SUM(AB82:AK82)</f>
+        <v/>
+      </c>
+      <c r="S82" s="81">
+        <f>SUM(AM82:AQ82)</f>
+        <v/>
+      </c>
+      <c r="T82" s="81">
+        <f>SUM(AS82:AW82)</f>
+        <v/>
+      </c>
+      <c r="Y82" s="81" t="n">
+        <v>1189</v>
       </c>
     </row>
   </sheetData>

--- a/examples/outputs/Birgo RR Exhibits - Maven @ 806v07.01.26.xlsx
+++ b/examples/outputs/Birgo RR Exhibits - Maven @ 806v07.01.26.xlsx
@@ -5971,7 +5971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:AS82"/>
+  <dimension ref="A3:AK82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.6" customWidth="1" min="1" max="1"/>
@@ -5994,6 +5994,15 @@
     <col width="12.1" customWidth="1" min="20" max="20"/>
     <col width="24" customWidth="1" min="22" max="22"/>
     <col width="12.1" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -6502,14 +6511,9 @@
           <t>Other Income</t>
         </is>
       </c>
-      <c r="AM30" s="67" t="inlineStr">
+      <c r="AK30" s="67" t="inlineStr">
         <is>
           <t>Concessions</t>
-        </is>
-      </c>
-      <c r="AS30" s="67" t="inlineStr">
-        <is>
-          <t>Employee Discounts</t>
         </is>
       </c>
     </row>
@@ -6631,22 +6635,47 @@
       </c>
       <c r="AB31" s="67" t="inlineStr">
         <is>
-          <t>Pet Fee</t>
+          <t>Building Protection Policy</t>
         </is>
       </c>
       <c r="AC31" s="67" t="inlineStr">
         <is>
-          <t>Laundry Income</t>
-        </is>
-      </c>
-      <c r="AM31" s="67" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="AS31" s="67" t="inlineStr">
-        <is>
-          <t>Employee Rent Credit</t>
+          <t>Pet Rent</t>
+        </is>
+      </c>
+      <c r="AD31" s="67" t="inlineStr">
+        <is>
+          <t>Resident Pest Control</t>
+        </is>
+      </c>
+      <c r="AE31" s="67" t="inlineStr">
+        <is>
+          <t>Resident Trash Charge</t>
+        </is>
+      </c>
+      <c r="AF31" s="67" t="inlineStr">
+        <is>
+          <t>Resident Water Charge</t>
+        </is>
+      </c>
+      <c r="AG31" s="67" t="inlineStr">
+        <is>
+          <t>WiFi/Cable Rent</t>
+        </is>
+      </c>
+      <c r="AH31" s="67" t="inlineStr">
+        <is>
+          <t>MTM Fee</t>
+        </is>
+      </c>
+      <c r="AI31" s="67" t="inlineStr">
+        <is>
+          <t>Resident Utilities (Rubs) Charge</t>
+        </is>
+      </c>
+      <c r="AK31" s="67" t="inlineStr">
+        <is>
+          <t>Concession</t>
         </is>
       </c>
     </row>
@@ -6713,19 +6742,36 @@
         <v>46474</v>
       </c>
       <c r="R32" s="81">
-        <f>SUM(AB32:AK32)</f>
+        <f>SUM(AB32:AI32)</f>
         <v/>
       </c>
       <c r="S32" s="81">
-        <f>SUM(AM32:AQ32)</f>
-        <v/>
-      </c>
-      <c r="T32" s="81">
-        <f>SUM(AS32:AW32)</f>
-        <v/>
+        <f>AK32</f>
+        <v/>
+      </c>
+      <c r="T32" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y32" s="81" t="n">
         <v>1285</v>
+      </c>
+      <c r="AB32" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC32" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD32" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG32" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="33">
@@ -6792,19 +6838,33 @@
         <v>46248</v>
       </c>
       <c r="R33" s="81">
-        <f>SUM(AB33:AK33)</f>
+        <f>SUM(AB33:AI33)</f>
         <v/>
       </c>
       <c r="S33" s="81">
-        <f>SUM(AM33:AQ33)</f>
-        <v/>
-      </c>
-      <c r="T33" s="81">
-        <f>SUM(AS33:AW33)</f>
-        <v/>
+        <f>AK33</f>
+        <v/>
+      </c>
+      <c r="T33" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y33" s="81" t="n">
         <v>1229</v>
+      </c>
+      <c r="AB33" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD33" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE33" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF33" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG33" s="81" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="34">
@@ -6871,19 +6931,33 @@
         <v>46507</v>
       </c>
       <c r="R34" s="81">
-        <f>SUM(AB34:AK34)</f>
+        <f>SUM(AB34:AI34)</f>
         <v/>
       </c>
       <c r="S34" s="81">
-        <f>SUM(AM34:AQ34)</f>
-        <v/>
-      </c>
-      <c r="T34" s="81">
-        <f>SUM(AS34:AW34)</f>
-        <v/>
+        <f>AK34</f>
+        <v/>
+      </c>
+      <c r="T34" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y34" s="81" t="n">
         <v>1249</v>
+      </c>
+      <c r="AB34" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD34" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE34" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF34" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG34" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="35">
@@ -6950,19 +7024,33 @@
         <v>46328</v>
       </c>
       <c r="R35" s="81">
-        <f>SUM(AB35:AK35)</f>
+        <f>SUM(AB35:AI35)</f>
         <v/>
       </c>
       <c r="S35" s="81">
-        <f>SUM(AM35:AQ35)</f>
-        <v/>
-      </c>
-      <c r="T35" s="81">
-        <f>SUM(AS35:AW35)</f>
-        <v/>
+        <f>AK35</f>
+        <v/>
+      </c>
+      <c r="T35" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y35" s="81" t="n">
         <v>1239</v>
+      </c>
+      <c r="AB35" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD35" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE35" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF35" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG35" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="36">
@@ -7029,19 +7117,33 @@
         <v>46507</v>
       </c>
       <c r="R36" s="81">
-        <f>SUM(AB36:AK36)</f>
+        <f>SUM(AB36:AI36)</f>
         <v/>
       </c>
       <c r="S36" s="81">
-        <f>SUM(AM36:AQ36)</f>
-        <v/>
-      </c>
-      <c r="T36" s="81">
-        <f>SUM(AS36:AW36)</f>
-        <v/>
+        <f>AK36</f>
+        <v/>
+      </c>
+      <c r="T36" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y36" s="81" t="n">
         <v>1220</v>
+      </c>
+      <c r="AB36" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD36" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE36" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF36" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG36" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="37">
@@ -7108,19 +7210,33 @@
         <v>46319</v>
       </c>
       <c r="R37" s="81">
-        <f>SUM(AB37:AK37)</f>
+        <f>SUM(AB37:AI37)</f>
         <v/>
       </c>
       <c r="S37" s="81">
-        <f>SUM(AM37:AQ37)</f>
-        <v/>
-      </c>
-      <c r="T37" s="81">
-        <f>SUM(AS37:AW37)</f>
-        <v/>
+        <f>AK37</f>
+        <v/>
+      </c>
+      <c r="T37" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y37" s="81" t="n">
         <v>1234</v>
+      </c>
+      <c r="AB37" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD37" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE37" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF37" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG37" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="38">
@@ -7178,16 +7294,15 @@
         <v/>
       </c>
       <c r="R38" s="81">
-        <f>SUM(AB38:AK38)</f>
+        <f>SUM(AB38:AI38)</f>
         <v/>
       </c>
       <c r="S38" s="81">
-        <f>SUM(AM38:AQ38)</f>
-        <v/>
-      </c>
-      <c r="T38" s="81">
-        <f>SUM(AS38:AW38)</f>
-        <v/>
+        <f>AK38</f>
+        <v/>
+      </c>
+      <c r="T38" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y38" s="81" t="n">
         <v>0</v>
@@ -7257,19 +7372,33 @@
         <v>46242</v>
       </c>
       <c r="R39" s="81">
-        <f>SUM(AB39:AK39)</f>
+        <f>SUM(AB39:AI39)</f>
         <v/>
       </c>
       <c r="S39" s="81">
-        <f>SUM(AM39:AQ39)</f>
-        <v/>
-      </c>
-      <c r="T39" s="81">
-        <f>SUM(AS39:AW39)</f>
-        <v/>
+        <f>AK39</f>
+        <v/>
+      </c>
+      <c r="T39" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y39" s="81" t="n">
         <v>1230</v>
+      </c>
+      <c r="AB39" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD39" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE39" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF39" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG39" s="81" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="40">
@@ -7336,21 +7465,35 @@
         <v>46472</v>
       </c>
       <c r="R40" s="81">
-        <f>SUM(AB40:AK40)</f>
+        <f>SUM(AB40:AI40)</f>
         <v/>
       </c>
       <c r="S40" s="81">
-        <f>SUM(AM40:AQ40)</f>
-        <v/>
-      </c>
-      <c r="T40" s="81">
-        <f>SUM(AS40:AW40)</f>
-        <v/>
+        <f>AK40</f>
+        <v/>
+      </c>
+      <c r="T40" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y40" s="81" t="n">
         <v>1249</v>
       </c>
-      <c r="AM40" s="81" t="n">
+      <c r="AB40" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD40" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE40" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF40" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG40" s="81" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK40" s="81" t="n">
         <v>-374.7</v>
       </c>
     </row>
@@ -7418,19 +7561,36 @@
         <v>46244</v>
       </c>
       <c r="R41" s="81">
-        <f>SUM(AB41:AK41)</f>
+        <f>SUM(AB41:AI41)</f>
         <v/>
       </c>
       <c r="S41" s="81">
-        <f>SUM(AM41:AQ41)</f>
-        <v/>
-      </c>
-      <c r="T41" s="81">
-        <f>SUM(AS41:AW41)</f>
-        <v/>
+        <f>AK41</f>
+        <v/>
+      </c>
+      <c r="T41" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y41" s="81" t="n">
         <v>1325</v>
+      </c>
+      <c r="AB41" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC41" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD41" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE41" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF41" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG41" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="42">
@@ -7488,16 +7648,15 @@
         <v/>
       </c>
       <c r="R42" s="81">
-        <f>SUM(AB42:AK42)</f>
+        <f>SUM(AB42:AI42)</f>
         <v/>
       </c>
       <c r="S42" s="81">
-        <f>SUM(AM42:AQ42)</f>
-        <v/>
-      </c>
-      <c r="T42" s="81">
-        <f>SUM(AS42:AW42)</f>
-        <v/>
+        <f>AK42</f>
+        <v/>
+      </c>
+      <c r="T42" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y42" s="81" t="n">
         <v>0</v>
@@ -7567,19 +7726,33 @@
         <v>46396</v>
       </c>
       <c r="R43" s="81">
-        <f>SUM(AB43:AK43)</f>
+        <f>SUM(AB43:AI43)</f>
         <v/>
       </c>
       <c r="S43" s="81">
-        <f>SUM(AM43:AQ43)</f>
-        <v/>
-      </c>
-      <c r="T43" s="81">
-        <f>SUM(AS43:AW43)</f>
-        <v/>
+        <f>AK43</f>
+        <v/>
+      </c>
+      <c r="T43" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y43" s="81" t="n">
         <v>1799</v>
+      </c>
+      <c r="AB43" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD43" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF43" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG43" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="44">
@@ -7637,16 +7810,15 @@
         <v/>
       </c>
       <c r="R44" s="81">
-        <f>SUM(AB44:AK44)</f>
+        <f>SUM(AB44:AI44)</f>
         <v/>
       </c>
       <c r="S44" s="81">
-        <f>SUM(AM44:AQ44)</f>
-        <v/>
-      </c>
-      <c r="T44" s="81">
-        <f>SUM(AS44:AW44)</f>
-        <v/>
+        <f>AK44</f>
+        <v/>
+      </c>
+      <c r="T44" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y44" s="81" t="n">
         <v>0</v>
@@ -7707,16 +7879,15 @@
         <v/>
       </c>
       <c r="R45" s="81">
-        <f>SUM(AB45:AK45)</f>
+        <f>SUM(AB45:AI45)</f>
         <v/>
       </c>
       <c r="S45" s="81">
-        <f>SUM(AM45:AQ45)</f>
-        <v/>
-      </c>
-      <c r="T45" s="81">
-        <f>SUM(AS45:AW45)</f>
-        <v/>
+        <f>AK45</f>
+        <v/>
+      </c>
+      <c r="T45" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y45" s="81" t="n">
         <v>0</v>
@@ -7786,19 +7957,33 @@
         <v>46265</v>
       </c>
       <c r="R46" s="81">
-        <f>SUM(AB46:AK46)</f>
+        <f>SUM(AB46:AI46)</f>
         <v/>
       </c>
       <c r="S46" s="81">
-        <f>SUM(AM46:AQ46)</f>
-        <v/>
-      </c>
-      <c r="T46" s="81">
-        <f>SUM(AS46:AW46)</f>
-        <v/>
+        <f>AK46</f>
+        <v/>
+      </c>
+      <c r="T46" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y46" s="81" t="n">
         <v>1249</v>
+      </c>
+      <c r="AB46" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD46" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE46" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF46" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG46" s="81" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="47">
@@ -7865,19 +8050,33 @@
         <v>46280</v>
       </c>
       <c r="R47" s="81">
-        <f>SUM(AB47:AK47)</f>
+        <f>SUM(AB47:AI47)</f>
         <v/>
       </c>
       <c r="S47" s="81">
-        <f>SUM(AM47:AQ47)</f>
-        <v/>
-      </c>
-      <c r="T47" s="81">
-        <f>SUM(AS47:AW47)</f>
-        <v/>
+        <f>AK47</f>
+        <v/>
+      </c>
+      <c r="T47" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y47" s="81" t="n">
         <v>1249</v>
+      </c>
+      <c r="AB47" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD47" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF47" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG47" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="48">
@@ -7944,19 +8143,33 @@
         <v>46243</v>
       </c>
       <c r="R48" s="81">
-        <f>SUM(AB48:AK48)</f>
+        <f>SUM(AB48:AI48)</f>
         <v/>
       </c>
       <c r="S48" s="81">
-        <f>SUM(AM48:AQ48)</f>
-        <v/>
-      </c>
-      <c r="T48" s="81">
-        <f>SUM(AS48:AW48)</f>
-        <v/>
+        <f>AK48</f>
+        <v/>
+      </c>
+      <c r="T48" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y48" s="81" t="n">
         <v>1245</v>
+      </c>
+      <c r="AB48" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD48" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF48" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG48" s="81" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="49">
@@ -8023,19 +8236,36 @@
         <v>46261</v>
       </c>
       <c r="R49" s="81">
-        <f>SUM(AB49:AK49)</f>
+        <f>SUM(AB49:AI49)</f>
         <v/>
       </c>
       <c r="S49" s="81">
-        <f>SUM(AM49:AQ49)</f>
-        <v/>
-      </c>
-      <c r="T49" s="81">
-        <f>SUM(AS49:AW49)</f>
-        <v/>
+        <f>AK49</f>
+        <v/>
+      </c>
+      <c r="T49" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y49" s="81" t="n">
         <v>1215</v>
+      </c>
+      <c r="AB49" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC49" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD49" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE49" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF49" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG49" s="81" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="50">
@@ -8102,19 +8332,36 @@
         <v>46224</v>
       </c>
       <c r="R50" s="81">
-        <f>SUM(AB50:AK50)</f>
+        <f>SUM(AB50:AI50)</f>
         <v/>
       </c>
       <c r="S50" s="81">
-        <f>SUM(AM50:AQ50)</f>
-        <v/>
-      </c>
-      <c r="T50" s="81">
-        <f>SUM(AS50:AW50)</f>
-        <v/>
+        <f>AK50</f>
+        <v/>
+      </c>
+      <c r="T50" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y50" s="81" t="n">
         <v>1345</v>
+      </c>
+      <c r="AB50" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC50" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD50" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE50" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF50" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG50" s="81" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="51">
@@ -8181,19 +8428,33 @@
         <v>46438</v>
       </c>
       <c r="R51" s="81">
-        <f>SUM(AB51:AK51)</f>
+        <f>SUM(AB51:AI51)</f>
         <v/>
       </c>
       <c r="S51" s="81">
-        <f>SUM(AM51:AQ51)</f>
-        <v/>
-      </c>
-      <c r="T51" s="81">
-        <f>SUM(AS51:AW51)</f>
-        <v/>
+        <f>AK51</f>
+        <v/>
+      </c>
+      <c r="T51" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y51" s="81" t="n">
         <v>1244</v>
+      </c>
+      <c r="AB51" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD51" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE51" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF51" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG51" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="52">
@@ -8260,19 +8521,36 @@
         <v>46290</v>
       </c>
       <c r="R52" s="81">
-        <f>SUM(AB52:AK52)</f>
+        <f>SUM(AB52:AI52)</f>
         <v/>
       </c>
       <c r="S52" s="81">
-        <f>SUM(AM52:AQ52)</f>
-        <v/>
-      </c>
-      <c r="T52" s="81">
-        <f>SUM(AS52:AW52)</f>
-        <v/>
+        <f>AK52</f>
+        <v/>
+      </c>
+      <c r="T52" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y52" s="81" t="n">
         <v>1320</v>
+      </c>
+      <c r="AB52" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC52" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD52" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF52" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG52" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="53">
@@ -8339,19 +8617,33 @@
         <v>46496</v>
       </c>
       <c r="R53" s="81">
-        <f>SUM(AB53:AK53)</f>
+        <f>SUM(AB53:AI53)</f>
         <v/>
       </c>
       <c r="S53" s="81">
-        <f>SUM(AM53:AQ53)</f>
-        <v/>
-      </c>
-      <c r="T53" s="81">
-        <f>SUM(AS53:AW53)</f>
-        <v/>
+        <f>AK53</f>
+        <v/>
+      </c>
+      <c r="T53" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y53" s="81" t="n">
         <v>1049</v>
+      </c>
+      <c r="AB53" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD53" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE53" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF53" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG53" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="54">
@@ -8409,16 +8701,15 @@
         <v/>
       </c>
       <c r="R54" s="81">
-        <f>SUM(AB54:AK54)</f>
+        <f>SUM(AB54:AI54)</f>
         <v/>
       </c>
       <c r="S54" s="81">
-        <f>SUM(AM54:AQ54)</f>
-        <v/>
-      </c>
-      <c r="T54" s="81">
-        <f>SUM(AS54:AW54)</f>
-        <v/>
+        <f>AK54</f>
+        <v/>
+      </c>
+      <c r="T54" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y54" s="81" t="n">
         <v>0</v>
@@ -8479,16 +8770,15 @@
         <v/>
       </c>
       <c r="R55" s="81">
-        <f>SUM(AB55:AK55)</f>
+        <f>SUM(AB55:AI55)</f>
         <v/>
       </c>
       <c r="S55" s="81">
-        <f>SUM(AM55:AQ55)</f>
-        <v/>
-      </c>
-      <c r="T55" s="81">
-        <f>SUM(AS55:AW55)</f>
-        <v/>
+        <f>AK55</f>
+        <v/>
+      </c>
+      <c r="T55" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y55" s="81" t="n">
         <v>0</v>
@@ -8549,16 +8839,15 @@
         <v/>
       </c>
       <c r="R56" s="81">
-        <f>SUM(AB56:AK56)</f>
+        <f>SUM(AB56:AI56)</f>
         <v/>
       </c>
       <c r="S56" s="81">
-        <f>SUM(AM56:AQ56)</f>
-        <v/>
-      </c>
-      <c r="T56" s="81">
-        <f>SUM(AS56:AW56)</f>
-        <v/>
+        <f>AK56</f>
+        <v/>
+      </c>
+      <c r="T56" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y56" s="81" t="n">
         <v>0</v>
@@ -8628,19 +8917,33 @@
         <v>46227</v>
       </c>
       <c r="R57" s="81">
-        <f>SUM(AB57:AK57)</f>
+        <f>SUM(AB57:AI57)</f>
         <v/>
       </c>
       <c r="S57" s="81">
-        <f>SUM(AM57:AQ57)</f>
-        <v/>
-      </c>
-      <c r="T57" s="81">
-        <f>SUM(AS57:AW57)</f>
-        <v/>
+        <f>AK57</f>
+        <v/>
+      </c>
+      <c r="T57" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y57" s="81" t="n">
         <v>1139</v>
+      </c>
+      <c r="AB57" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD57" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG57" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="58">
@@ -8707,19 +9010,33 @@
         <v>46195</v>
       </c>
       <c r="R58" s="81">
-        <f>SUM(AB58:AK58)</f>
+        <f>SUM(AB58:AI58)</f>
         <v/>
       </c>
       <c r="S58" s="81">
-        <f>SUM(AM58:AQ58)</f>
-        <v/>
-      </c>
-      <c r="T58" s="81">
-        <f>SUM(AS58:AW58)</f>
-        <v/>
+        <f>AK58</f>
+        <v/>
+      </c>
+      <c r="T58" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y58" s="81" t="n">
         <v>1099</v>
+      </c>
+      <c r="AB58" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD58" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF58" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG58" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="59">
@@ -8783,19 +9100,36 @@
         <v>46113</v>
       </c>
       <c r="R59" s="81">
-        <f>SUM(AB59:AK59)</f>
+        <f>SUM(AB59:AI59)</f>
         <v/>
       </c>
       <c r="S59" s="81">
-        <f>SUM(AM59:AQ59)</f>
-        <v/>
-      </c>
-      <c r="T59" s="81">
-        <f>SUM(AS59:AW59)</f>
-        <v/>
+        <f>AK59</f>
+        <v/>
+      </c>
+      <c r="T59" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y59" s="81" t="n">
         <v>990</v>
+      </c>
+      <c r="AB59" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD59" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE59" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG59" s="81" t="n">
+        <v>65</v>
+      </c>
+      <c r="AH59" s="81" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="60">
@@ -8862,19 +9196,33 @@
         <v>46538</v>
       </c>
       <c r="R60" s="81">
-        <f>SUM(AB60:AK60)</f>
+        <f>SUM(AB60:AI60)</f>
         <v/>
       </c>
       <c r="S60" s="81">
-        <f>SUM(AM60:AQ60)</f>
-        <v/>
-      </c>
-      <c r="T60" s="81">
-        <f>SUM(AS60:AW60)</f>
-        <v/>
+        <f>AK60</f>
+        <v/>
+      </c>
+      <c r="T60" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y60" s="81" t="n">
         <v>1125</v>
+      </c>
+      <c r="AB60" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD60" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE60" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF60" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG60" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="61">
@@ -8941,19 +9289,33 @@
         <v>46335</v>
       </c>
       <c r="R61" s="81">
-        <f>SUM(AB61:AK61)</f>
+        <f>SUM(AB61:AI61)</f>
         <v/>
       </c>
       <c r="S61" s="81">
-        <f>SUM(AM61:AQ61)</f>
-        <v/>
-      </c>
-      <c r="T61" s="81">
-        <f>SUM(AS61:AW61)</f>
-        <v/>
+        <f>AK61</f>
+        <v/>
+      </c>
+      <c r="T61" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y61" s="81" t="n">
         <v>1179</v>
+      </c>
+      <c r="AB61" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD61" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE61" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF61" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG61" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="62">
@@ -9020,19 +9382,33 @@
         <v>46310</v>
       </c>
       <c r="R62" s="81">
-        <f>SUM(AB62:AK62)</f>
+        <f>SUM(AB62:AI62)</f>
         <v/>
       </c>
       <c r="S62" s="81">
-        <f>SUM(AM62:AQ62)</f>
-        <v/>
-      </c>
-      <c r="T62" s="81">
-        <f>SUM(AS62:AW62)</f>
-        <v/>
+        <f>AK62</f>
+        <v/>
+      </c>
+      <c r="T62" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y62" s="81" t="n">
         <v>1124</v>
+      </c>
+      <c r="AB62" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD62" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE62" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF62" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG62" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="63">
@@ -9099,19 +9475,36 @@
         <v>46381</v>
       </c>
       <c r="R63" s="81">
-        <f>SUM(AB63:AK63)</f>
+        <f>SUM(AB63:AI63)</f>
         <v/>
       </c>
       <c r="S63" s="81">
-        <f>SUM(AM63:AQ63)</f>
-        <v/>
-      </c>
-      <c r="T63" s="81">
-        <f>SUM(AS63:AW63)</f>
-        <v/>
+        <f>AK63</f>
+        <v/>
+      </c>
+      <c r="T63" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y63" s="81" t="n">
         <v>1324</v>
+      </c>
+      <c r="AB63" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC63" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD63" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE63" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF63" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG63" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="64">
@@ -9178,19 +9571,33 @@
         <v>46200</v>
       </c>
       <c r="R64" s="81">
-        <f>SUM(AB64:AK64)</f>
+        <f>SUM(AB64:AI64)</f>
         <v/>
       </c>
       <c r="S64" s="81">
-        <f>SUM(AM64:AQ64)</f>
-        <v/>
-      </c>
-      <c r="T64" s="81">
-        <f>SUM(AS64:AW64)</f>
-        <v/>
+        <f>AK64</f>
+        <v/>
+      </c>
+      <c r="T64" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y64" s="81" t="n">
         <v>1114</v>
+      </c>
+      <c r="AB64" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD64" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE64" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF64" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG64" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="65">
@@ -9257,19 +9664,33 @@
         <v>46352</v>
       </c>
       <c r="R65" s="81">
-        <f>SUM(AB65:AK65)</f>
+        <f>SUM(AB65:AI65)</f>
         <v/>
       </c>
       <c r="S65" s="81">
-        <f>SUM(AM65:AQ65)</f>
-        <v/>
-      </c>
-      <c r="T65" s="81">
-        <f>SUM(AS65:AW65)</f>
-        <v/>
+        <f>AK65</f>
+        <v/>
+      </c>
+      <c r="T65" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y65" s="81" t="n">
         <v>1245</v>
+      </c>
+      <c r="AB65" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD65" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE65" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF65" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG65" s="81" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="66">
@@ -9336,19 +9757,33 @@
         <v>46493</v>
       </c>
       <c r="R66" s="81">
-        <f>SUM(AB66:AK66)</f>
+        <f>SUM(AB66:AI66)</f>
         <v/>
       </c>
       <c r="S66" s="81">
-        <f>SUM(AM66:AQ66)</f>
-        <v/>
-      </c>
-      <c r="T66" s="81">
-        <f>SUM(AS66:AW66)</f>
-        <v/>
+        <f>AK66</f>
+        <v/>
+      </c>
+      <c r="T66" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y66" s="81" t="n">
         <v>1059</v>
+      </c>
+      <c r="AB66" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD66" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF66" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG66" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="67">
@@ -9415,19 +9850,33 @@
         <v>46354</v>
       </c>
       <c r="R67" s="81">
-        <f>SUM(AB67:AK67)</f>
+        <f>SUM(AB67:AI67)</f>
         <v/>
       </c>
       <c r="S67" s="81">
-        <f>SUM(AM67:AQ67)</f>
-        <v/>
-      </c>
-      <c r="T67" s="81">
-        <f>SUM(AS67:AW67)</f>
-        <v/>
+        <f>AK67</f>
+        <v/>
+      </c>
+      <c r="T67" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y67" s="81" t="n">
         <v>1384</v>
+      </c>
+      <c r="AB67" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD67" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE67" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF67" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG67" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="68">
@@ -9485,16 +9934,15 @@
         <v/>
       </c>
       <c r="R68" s="81">
-        <f>SUM(AB68:AK68)</f>
+        <f>SUM(AB68:AI68)</f>
         <v/>
       </c>
       <c r="S68" s="81">
-        <f>SUM(AM68:AQ68)</f>
-        <v/>
-      </c>
-      <c r="T68" s="81">
-        <f>SUM(AS68:AW68)</f>
-        <v/>
+        <f>AK68</f>
+        <v/>
+      </c>
+      <c r="T68" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y68" s="81" t="n">
         <v>0</v>
@@ -9564,19 +10012,36 @@
         <v>46446</v>
       </c>
       <c r="R69" s="81">
-        <f>SUM(AB69:AK69)</f>
+        <f>SUM(AB69:AI69)</f>
         <v/>
       </c>
       <c r="S69" s="81">
-        <f>SUM(AM69:AQ69)</f>
-        <v/>
-      </c>
-      <c r="T69" s="81">
-        <f>SUM(AS69:AW69)</f>
-        <v/>
+        <f>AK69</f>
+        <v/>
+      </c>
+      <c r="T69" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y69" s="81" t="n">
         <v>1184</v>
+      </c>
+      <c r="AB69" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC69" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD69" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE69" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF69" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG69" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="70">
@@ -9643,19 +10108,33 @@
         <v>46403</v>
       </c>
       <c r="R70" s="81">
-        <f>SUM(AB70:AK70)</f>
+        <f>SUM(AB70:AI70)</f>
         <v/>
       </c>
       <c r="S70" s="81">
-        <f>SUM(AM70:AQ70)</f>
-        <v/>
-      </c>
-      <c r="T70" s="81">
-        <f>SUM(AS70:AW70)</f>
-        <v/>
+        <f>AK70</f>
+        <v/>
+      </c>
+      <c r="T70" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y70" s="81" t="n">
         <v>1255</v>
+      </c>
+      <c r="AB70" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD70" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE70" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF70" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG70" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="71">
@@ -9722,19 +10201,33 @@
         <v>46233</v>
       </c>
       <c r="R71" s="81">
-        <f>SUM(AB71:AK71)</f>
+        <f>SUM(AB71:AI71)</f>
         <v/>
       </c>
       <c r="S71" s="81">
-        <f>SUM(AM71:AQ71)</f>
-        <v/>
-      </c>
-      <c r="T71" s="81">
-        <f>SUM(AS71:AW71)</f>
-        <v/>
+        <f>AK71</f>
+        <v/>
+      </c>
+      <c r="T71" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y71" s="81" t="n">
         <v>1149</v>
+      </c>
+      <c r="AB71" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD71" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE71" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF71" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG71" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="72">
@@ -9792,16 +10285,15 @@
         <v/>
       </c>
       <c r="R72" s="81">
-        <f>SUM(AB72:AK72)</f>
+        <f>SUM(AB72:AI72)</f>
         <v/>
       </c>
       <c r="S72" s="81">
-        <f>SUM(AM72:AQ72)</f>
-        <v/>
-      </c>
-      <c r="T72" s="81">
-        <f>SUM(AS72:AW72)</f>
-        <v/>
+        <f>AK72</f>
+        <v/>
+      </c>
+      <c r="T72" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y72" s="81" t="n">
         <v>0</v>
@@ -9871,19 +10363,33 @@
         <v>46215</v>
       </c>
       <c r="R73" s="81">
-        <f>SUM(AB73:AK73)</f>
+        <f>SUM(AB73:AI73)</f>
         <v/>
       </c>
       <c r="S73" s="81">
-        <f>SUM(AM73:AQ73)</f>
-        <v/>
-      </c>
-      <c r="T73" s="81">
-        <f>SUM(AS73:AW73)</f>
-        <v/>
+        <f>AK73</f>
+        <v/>
+      </c>
+      <c r="T73" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y73" s="81" t="n">
         <v>1330</v>
+      </c>
+      <c r="AB73" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD73" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE73" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF73" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG73" s="81" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="74">
@@ -9950,19 +10456,36 @@
         <v>46172</v>
       </c>
       <c r="R74" s="81">
-        <f>SUM(AB74:AK74)</f>
+        <f>SUM(AB74:AI74)</f>
         <v/>
       </c>
       <c r="S74" s="81">
-        <f>SUM(AM74:AQ74)</f>
-        <v/>
-      </c>
-      <c r="T74" s="81">
-        <f>SUM(AS74:AW74)</f>
-        <v/>
+        <f>AK74</f>
+        <v/>
+      </c>
+      <c r="T74" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y74" s="81" t="n">
         <v>1185</v>
+      </c>
+      <c r="AB74" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC74" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD74" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE74" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF74" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG74" s="81" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="75">
@@ -10029,19 +10552,36 @@
         <v>46503</v>
       </c>
       <c r="R75" s="81">
-        <f>SUM(AB75:AK75)</f>
+        <f>SUM(AB75:AI75)</f>
         <v/>
       </c>
       <c r="S75" s="81">
-        <f>SUM(AM75:AQ75)</f>
-        <v/>
-      </c>
-      <c r="T75" s="81">
-        <f>SUM(AS75:AW75)</f>
-        <v/>
+        <f>AK75</f>
+        <v/>
+      </c>
+      <c r="T75" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y75" s="81" t="n">
         <v>1355</v>
+      </c>
+      <c r="AB75" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC75" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD75" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE75" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF75" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG75" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="76">
@@ -10108,19 +10648,33 @@
         <v>46262</v>
       </c>
       <c r="R76" s="81">
-        <f>SUM(AB76:AK76)</f>
+        <f>SUM(AB76:AI76)</f>
         <v/>
       </c>
       <c r="S76" s="81">
-        <f>SUM(AM76:AQ76)</f>
-        <v/>
-      </c>
-      <c r="T76" s="81">
-        <f>SUM(AS76:AW76)</f>
-        <v/>
+        <f>AK76</f>
+        <v/>
+      </c>
+      <c r="T76" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y76" s="81" t="n">
         <v>1334</v>
+      </c>
+      <c r="AB76" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD76" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE76" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF76" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG76" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="77">
@@ -10187,19 +10741,33 @@
         <v>46186</v>
       </c>
       <c r="R77" s="81">
-        <f>SUM(AB77:AK77)</f>
+        <f>SUM(AB77:AI77)</f>
         <v/>
       </c>
       <c r="S77" s="81">
-        <f>SUM(AM77:AQ77)</f>
-        <v/>
-      </c>
-      <c r="T77" s="81">
-        <f>SUM(AS77:AW77)</f>
-        <v/>
+        <f>AK77</f>
+        <v/>
+      </c>
+      <c r="T77" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y77" s="81" t="n">
         <v>1124</v>
+      </c>
+      <c r="AB77" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD77" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE77" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF77" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG77" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="78">
@@ -10266,19 +10834,33 @@
         <v>46219</v>
       </c>
       <c r="R78" s="81">
-        <f>SUM(AB78:AK78)</f>
+        <f>SUM(AB78:AI78)</f>
         <v/>
       </c>
       <c r="S78" s="81">
-        <f>SUM(AM78:AQ78)</f>
-        <v/>
-      </c>
-      <c r="T78" s="81">
-        <f>SUM(AS78:AW78)</f>
-        <v/>
+        <f>AK78</f>
+        <v/>
+      </c>
+      <c r="T78" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y78" s="81" t="n">
         <v>1334</v>
+      </c>
+      <c r="AB78" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD78" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE78" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF78" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG78" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="79">
@@ -10345,19 +10927,33 @@
         <v>46476</v>
       </c>
       <c r="R79" s="81">
-        <f>SUM(AB79:AK79)</f>
+        <f>SUM(AB79:AI79)</f>
         <v/>
       </c>
       <c r="S79" s="81">
-        <f>SUM(AM79:AQ79)</f>
-        <v/>
-      </c>
-      <c r="T79" s="81">
-        <f>SUM(AS79:AW79)</f>
-        <v/>
+        <f>AK79</f>
+        <v/>
+      </c>
+      <c r="T79" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y79" s="81" t="n">
         <v>1394</v>
+      </c>
+      <c r="AB79" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD79" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE79" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF79" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG79" s="81" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="80">
@@ -10424,19 +11020,36 @@
         <v>46416</v>
       </c>
       <c r="R80" s="81">
-        <f>SUM(AB80:AK80)</f>
+        <f>SUM(AB80:AI80)</f>
         <v/>
       </c>
       <c r="S80" s="81">
-        <f>SUM(AM80:AQ80)</f>
-        <v/>
-      </c>
-      <c r="T80" s="81">
-        <f>SUM(AS80:AW80)</f>
-        <v/>
+        <f>AK80</f>
+        <v/>
+      </c>
+      <c r="T80" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y80" s="81" t="n">
         <v>1300</v>
+      </c>
+      <c r="AB80" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD80" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE80" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF80" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG80" s="81" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI80" s="81" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="81">
@@ -10503,19 +11116,39 @@
         <v>46185</v>
       </c>
       <c r="R81" s="81">
-        <f>SUM(AB81:AK81)</f>
+        <f>SUM(AB81:AI81)</f>
         <v/>
       </c>
       <c r="S81" s="81">
-        <f>SUM(AM81:AQ81)</f>
-        <v/>
-      </c>
-      <c r="T81" s="81">
-        <f>SUM(AS81:AW81)</f>
-        <v/>
+        <f>AK81</f>
+        <v/>
+      </c>
+      <c r="T81" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y81" s="81" t="n">
         <v>1145</v>
+      </c>
+      <c r="AB81" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC81" s="81" t="n">
+        <v>65</v>
+      </c>
+      <c r="AD81" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE81" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF81" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG81" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI81" s="81" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="82">
@@ -10582,19 +11215,36 @@
         <v>46232</v>
       </c>
       <c r="R82" s="81">
-        <f>SUM(AB82:AK82)</f>
+        <f>SUM(AB82:AI82)</f>
         <v/>
       </c>
       <c r="S82" s="81">
-        <f>SUM(AM82:AQ82)</f>
-        <v/>
-      </c>
-      <c r="T82" s="81">
-        <f>SUM(AS82:AW82)</f>
-        <v/>
+        <f>AK82</f>
+        <v/>
+      </c>
+      <c r="T82" s="81" t="n">
+        <v>0</v>
       </c>
       <c r="Y82" s="81" t="n">
         <v>1189</v>
+      </c>
+      <c r="AB82" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD82" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE82" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF82" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG82" s="81" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI82" s="81" t="n">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/examples/outputs/Birgo RR Exhibits - Maven @ 806v07.01.26.xlsx
+++ b/examples/outputs/Birgo RR Exhibits - Maven @ 806v07.01.26.xlsx
@@ -84,14 +84,14 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -153,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -318,25 +318,6 @@
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="174" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -356,48 +337,56 @@
     <xf numFmtId="10" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="177" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="178" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3088,76 +3077,60 @@
       </c>
     </row>
     <row r="14">
-      <c r="D14" s="60" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>Maven @ 806</t>
         </is>
       </c>
-      <c r="E14" s="61" t="inlineStr">
+      <c r="E14" s="54" t="inlineStr">
         <is>
           <t>800-2A</t>
         </is>
       </c>
-      <c r="F14" s="61" t="inlineStr">
+      <c r="F14" s="54" t="inlineStr">
         <is>
           <t>2x2B_C</t>
         </is>
       </c>
-      <c r="G14" s="61" t="inlineStr">
+      <c r="G14" s="54" t="inlineStr">
         <is>
           <t>2 BD / 2 BA</t>
         </is>
       </c>
-      <c r="H14" s="62" t="n"/>
-      <c r="I14" s="62" t="n"/>
-      <c r="J14" s="62" t="n"/>
-      <c r="K14" s="60" t="inlineStr">
+      <c r="K14" s="36" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L14" s="63" t="n">
+      <c r="L14" s="55" t="n">
         <v>1253</v>
       </c>
-      <c r="M14" s="64" t="n">
+      <c r="M14" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="N14" s="64" t="n">
+      <c r="N14" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="O14" s="62" t="n"/>
-      <c r="P14" s="62" t="n"/>
-      <c r="Q14" s="65" t="inlineStr">
+      <c r="Q14" s="57" t="inlineStr">
         <is>
           <t>Vac</t>
         </is>
       </c>
-      <c r="R14" s="62" t="n"/>
-      <c r="S14" s="62" t="n"/>
-      <c r="T14" s="62" t="n"/>
-      <c r="U14" s="66" t="n">
+      <c r="U14" s="58" t="n">
         <v>1799</v>
       </c>
-      <c r="V14" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="62" t="n"/>
-      <c r="AA14" s="62" t="n"/>
-      <c r="AB14" s="62" t="n"/>
-      <c r="AC14" s="62" t="n"/>
-      <c r="AD14" s="62" t="n"/>
-      <c r="AE14" s="62" t="n"/>
-      <c r="AF14" s="62" t="n"/>
-      <c r="AG14" s="62" t="n"/>
+      <c r="V14" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="D15" s="36" t="inlineStr">
@@ -3355,76 +3328,60 @@
       </c>
     </row>
     <row r="18">
-      <c r="D18" s="60" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>Maven @ 806</t>
         </is>
       </c>
-      <c r="E18" s="61" t="inlineStr">
+      <c r="E18" s="54" t="inlineStr">
         <is>
           <t>800-3A</t>
         </is>
       </c>
-      <c r="F18" s="61" t="inlineStr">
+      <c r="F18" s="54" t="inlineStr">
         <is>
           <t>2x2B_C</t>
         </is>
       </c>
-      <c r="G18" s="61" t="inlineStr">
+      <c r="G18" s="54" t="inlineStr">
         <is>
           <t>2 BD / 2 BA</t>
         </is>
       </c>
-      <c r="H18" s="62" t="n"/>
-      <c r="I18" s="62" t="n"/>
-      <c r="J18" s="62" t="n"/>
-      <c r="K18" s="60" t="inlineStr">
+      <c r="K18" s="36" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L18" s="63" t="n">
+      <c r="L18" s="55" t="n">
         <v>1153</v>
       </c>
-      <c r="M18" s="64" t="n">
+      <c r="M18" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="N18" s="64" t="n">
+      <c r="N18" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="O18" s="62" t="n"/>
-      <c r="P18" s="62" t="n"/>
-      <c r="Q18" s="65" t="inlineStr">
+      <c r="Q18" s="57" t="inlineStr">
         <is>
           <t>Vac</t>
         </is>
       </c>
-      <c r="R18" s="62" t="n"/>
-      <c r="S18" s="62" t="n"/>
-      <c r="T18" s="62" t="n"/>
-      <c r="U18" s="66" t="n">
+      <c r="U18" s="58" t="n">
         <v>1799</v>
       </c>
-      <c r="V18" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="62" t="n"/>
-      <c r="AA18" s="62" t="n"/>
-      <c r="AB18" s="62" t="n"/>
-      <c r="AC18" s="62" t="n"/>
-      <c r="AD18" s="62" t="n"/>
-      <c r="AE18" s="62" t="n"/>
-      <c r="AF18" s="62" t="n"/>
-      <c r="AG18" s="62" t="n"/>
+      <c r="V18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="D19" s="36" t="inlineStr">
@@ -3492,148 +3449,116 @@
       </c>
     </row>
     <row r="20">
-      <c r="D20" s="60" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>Maven @ 806</t>
         </is>
       </c>
-      <c r="E20" s="61" t="inlineStr">
+      <c r="E20" s="54" t="inlineStr">
         <is>
           <t>800-3C</t>
         </is>
       </c>
-      <c r="F20" s="61" t="inlineStr">
+      <c r="F20" s="54" t="inlineStr">
         <is>
           <t>2x2B_C</t>
         </is>
       </c>
-      <c r="G20" s="61" t="inlineStr">
+      <c r="G20" s="54" t="inlineStr">
         <is>
           <t>2 BD / 2 BA</t>
         </is>
       </c>
-      <c r="H20" s="62" t="n"/>
-      <c r="I20" s="62" t="n"/>
-      <c r="J20" s="62" t="n"/>
-      <c r="K20" s="60" t="inlineStr">
+      <c r="K20" s="36" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L20" s="63" t="n">
+      <c r="L20" s="55" t="n">
         <v>972</v>
       </c>
-      <c r="M20" s="64" t="n">
+      <c r="M20" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="N20" s="64" t="n">
+      <c r="N20" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="O20" s="62" t="n"/>
-      <c r="P20" s="62" t="n"/>
-      <c r="Q20" s="65" t="inlineStr">
+      <c r="Q20" s="57" t="inlineStr">
         <is>
           <t>Vac</t>
         </is>
       </c>
-      <c r="R20" s="62" t="n"/>
-      <c r="S20" s="62" t="n"/>
-      <c r="T20" s="62" t="n"/>
-      <c r="U20" s="66" t="n">
+      <c r="U20" s="58" t="n">
         <v>1799</v>
       </c>
-      <c r="V20" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="62" t="n"/>
-      <c r="AA20" s="62" t="n"/>
-      <c r="AB20" s="62" t="n"/>
-      <c r="AC20" s="62" t="n"/>
-      <c r="AD20" s="62" t="n"/>
-      <c r="AE20" s="62" t="n"/>
-      <c r="AF20" s="62" t="n"/>
-      <c r="AG20" s="62" t="n"/>
+      <c r="V20" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
-      <c r="D21" s="60" t="inlineStr">
+      <c r="D21" s="36" t="inlineStr">
         <is>
           <t>Maven @ 806</t>
         </is>
       </c>
-      <c r="E21" s="61" t="inlineStr">
+      <c r="E21" s="54" t="inlineStr">
         <is>
           <t>800-3D</t>
         </is>
       </c>
-      <c r="F21" s="61" t="inlineStr">
+      <c r="F21" s="54" t="inlineStr">
         <is>
           <t>2x2B_C</t>
         </is>
       </c>
-      <c r="G21" s="61" t="inlineStr">
+      <c r="G21" s="54" t="inlineStr">
         <is>
           <t>2 BD / 2 BA</t>
         </is>
       </c>
-      <c r="H21" s="62" t="n"/>
-      <c r="I21" s="62" t="n"/>
-      <c r="J21" s="62" t="n"/>
-      <c r="K21" s="60" t="inlineStr">
+      <c r="K21" s="36" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L21" s="63" t="n">
+      <c r="L21" s="55" t="n">
         <v>972</v>
       </c>
-      <c r="M21" s="64" t="n">
+      <c r="M21" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="N21" s="64" t="n">
+      <c r="N21" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="O21" s="62" t="n"/>
-      <c r="P21" s="62" t="n"/>
-      <c r="Q21" s="65" t="inlineStr">
+      <c r="Q21" s="57" t="inlineStr">
         <is>
           <t>Vac</t>
         </is>
       </c>
-      <c r="R21" s="62" t="n"/>
-      <c r="S21" s="62" t="n"/>
-      <c r="T21" s="62" t="n"/>
-      <c r="U21" s="66" t="n">
+      <c r="U21" s="58" t="n">
         <v>1799</v>
       </c>
-      <c r="V21" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="62" t="n"/>
-      <c r="AA21" s="62" t="n"/>
-      <c r="AB21" s="62" t="n"/>
-      <c r="AC21" s="62" t="n"/>
-      <c r="AD21" s="62" t="n"/>
-      <c r="AE21" s="62" t="n"/>
-      <c r="AF21" s="62" t="n"/>
-      <c r="AG21" s="62" t="n"/>
+      <c r="V21" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="D22" s="36" t="inlineStr">
@@ -4156,220 +4081,172 @@
       </c>
     </row>
     <row r="30">
-      <c r="D30" s="60" t="inlineStr">
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>Maven @ 806</t>
         </is>
       </c>
-      <c r="E30" s="61" t="inlineStr">
+      <c r="E30" s="54" t="inlineStr">
         <is>
           <t>CL - 806-9</t>
         </is>
       </c>
-      <c r="F30" s="61" t="inlineStr">
+      <c r="F30" s="54" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="G30" s="61" t="inlineStr">
+      <c r="G30" s="54" t="inlineStr">
         <is>
           <t>2 BD / 1 BA</t>
         </is>
       </c>
-      <c r="H30" s="62" t="n"/>
-      <c r="I30" s="62" t="n"/>
-      <c r="J30" s="62" t="n"/>
-      <c r="K30" s="60" t="inlineStr">
+      <c r="K30" s="36" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L30" s="63" t="n">
+      <c r="L30" s="55" t="n">
         <v>723</v>
       </c>
-      <c r="M30" s="64" t="n">
+      <c r="M30" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="64" t="n">
+      <c r="N30" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="O30" s="62" t="n"/>
-      <c r="P30" s="62" t="n"/>
-      <c r="Q30" s="65" t="inlineStr">
+      <c r="Q30" s="57" t="inlineStr">
         <is>
           <t>Vac</t>
         </is>
       </c>
-      <c r="R30" s="62" t="n"/>
-      <c r="S30" s="62" t="n"/>
-      <c r="T30" s="62" t="n"/>
-      <c r="U30" s="66" t="n">
+      <c r="U30" s="58" t="n">
         <v>1355</v>
       </c>
-      <c r="V30" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="62" t="n"/>
-      <c r="AA30" s="62" t="n"/>
-      <c r="AB30" s="62" t="n"/>
-      <c r="AC30" s="62" t="n"/>
-      <c r="AD30" s="62" t="n"/>
-      <c r="AE30" s="62" t="n"/>
-      <c r="AF30" s="62" t="n"/>
-      <c r="AG30" s="62" t="n"/>
+      <c r="V30" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
-      <c r="D31" s="60" t="inlineStr">
+      <c r="D31" s="36" t="inlineStr">
         <is>
           <t>Maven @ 806</t>
         </is>
       </c>
-      <c r="E31" s="61" t="inlineStr">
+      <c r="E31" s="54" t="inlineStr">
         <is>
           <t>CL - 806-10</t>
         </is>
       </c>
-      <c r="F31" s="61" t="inlineStr">
+      <c r="F31" s="54" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="G31" s="61" t="inlineStr">
+      <c r="G31" s="54" t="inlineStr">
         <is>
           <t>2 BD / 1 BA</t>
         </is>
       </c>
-      <c r="H31" s="62" t="n"/>
-      <c r="I31" s="62" t="n"/>
-      <c r="J31" s="62" t="n"/>
-      <c r="K31" s="60" t="inlineStr">
+      <c r="K31" s="36" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L31" s="63" t="n">
+      <c r="L31" s="55" t="n">
         <v>744</v>
       </c>
-      <c r="M31" s="64" t="n">
+      <c r="M31" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="N31" s="64" t="n">
+      <c r="N31" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="O31" s="62" t="n"/>
-      <c r="P31" s="62" t="n"/>
-      <c r="Q31" s="65" t="inlineStr">
+      <c r="Q31" s="57" t="inlineStr">
         <is>
           <t>Vac</t>
         </is>
       </c>
-      <c r="R31" s="62" t="n"/>
-      <c r="S31" s="62" t="n"/>
-      <c r="T31" s="62" t="n"/>
-      <c r="U31" s="66" t="n">
+      <c r="U31" s="58" t="n">
         <v>1355</v>
       </c>
-      <c r="V31" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="62" t="n"/>
-      <c r="AA31" s="62" t="n"/>
-      <c r="AB31" s="62" t="n"/>
-      <c r="AC31" s="62" t="n"/>
-      <c r="AD31" s="62" t="n"/>
-      <c r="AE31" s="62" t="n"/>
-      <c r="AF31" s="62" t="n"/>
-      <c r="AG31" s="62" t="n"/>
+      <c r="V31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
-      <c r="D32" s="60" t="inlineStr">
+      <c r="D32" s="36" t="inlineStr">
         <is>
           <t>Maven @ 806</t>
         </is>
       </c>
-      <c r="E32" s="61" t="inlineStr">
+      <c r="E32" s="54" t="inlineStr">
         <is>
           <t>CL - 806-11</t>
         </is>
       </c>
-      <c r="F32" s="61" t="inlineStr">
+      <c r="F32" s="54" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="G32" s="61" t="inlineStr">
+      <c r="G32" s="54" t="inlineStr">
         <is>
           <t>1 BD / 1 BA</t>
         </is>
       </c>
-      <c r="H32" s="62" t="n"/>
-      <c r="I32" s="62" t="n"/>
-      <c r="J32" s="62" t="n"/>
-      <c r="K32" s="60" t="inlineStr">
+      <c r="K32" s="36" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L32" s="63" t="n">
+      <c r="L32" s="55" t="n">
         <v>720</v>
       </c>
-      <c r="M32" s="64" t="n">
+      <c r="M32" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="64" t="n">
+      <c r="N32" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="O32" s="62" t="n"/>
-      <c r="P32" s="62" t="n"/>
-      <c r="Q32" s="65" t="inlineStr">
+      <c r="Q32" s="57" t="inlineStr">
         <is>
           <t>Vac</t>
         </is>
       </c>
-      <c r="R32" s="62" t="n"/>
-      <c r="S32" s="62" t="n"/>
-      <c r="T32" s="62" t="n"/>
-      <c r="U32" s="66" t="n">
+      <c r="U32" s="58" t="n">
         <v>990</v>
       </c>
-      <c r="V32" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="62" t="n"/>
-      <c r="AA32" s="62" t="n"/>
-      <c r="AB32" s="62" t="n"/>
-      <c r="AC32" s="62" t="n"/>
-      <c r="AD32" s="62" t="n"/>
-      <c r="AE32" s="62" t="n"/>
-      <c r="AF32" s="62" t="n"/>
-      <c r="AG32" s="62" t="n"/>
+      <c r="V32" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="D33" s="36" t="inlineStr">
@@ -5084,76 +4961,60 @@
       </c>
     </row>
     <row r="44">
-      <c r="D44" s="60" t="inlineStr">
+      <c r="D44" s="36" t="inlineStr">
         <is>
           <t>Maven @ 806</t>
         </is>
       </c>
-      <c r="E44" s="61" t="inlineStr">
+      <c r="E44" s="54" t="inlineStr">
         <is>
           <t>CL - 806-24</t>
         </is>
       </c>
-      <c r="F44" s="61" t="inlineStr">
+      <c r="F44" s="54" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="G44" s="61" t="inlineStr">
+      <c r="G44" s="54" t="inlineStr">
         <is>
           <t>2 BD / 1 BA</t>
         </is>
       </c>
-      <c r="H44" s="62" t="n"/>
-      <c r="I44" s="62" t="n"/>
-      <c r="J44" s="62" t="n"/>
-      <c r="K44" s="60" t="inlineStr">
+      <c r="K44" s="36" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L44" s="63" t="n">
+      <c r="L44" s="55" t="n">
         <v>683</v>
       </c>
-      <c r="M44" s="64" t="n">
+      <c r="M44" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="N44" s="64" t="n">
+      <c r="N44" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="O44" s="62" t="n"/>
-      <c r="P44" s="62" t="n"/>
-      <c r="Q44" s="65" t="inlineStr">
+      <c r="Q44" s="57" t="inlineStr">
         <is>
           <t>Vac</t>
         </is>
       </c>
-      <c r="R44" s="62" t="n"/>
-      <c r="S44" s="62" t="n"/>
-      <c r="T44" s="62" t="n"/>
-      <c r="U44" s="66" t="n">
+      <c r="U44" s="58" t="n">
         <v>1355</v>
       </c>
-      <c r="V44" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="62" t="n"/>
-      <c r="AA44" s="62" t="n"/>
-      <c r="AB44" s="62" t="n"/>
-      <c r="AC44" s="62" t="n"/>
-      <c r="AD44" s="62" t="n"/>
-      <c r="AE44" s="62" t="n"/>
-      <c r="AF44" s="62" t="n"/>
-      <c r="AG44" s="62" t="n"/>
+      <c r="V44" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="D45" s="36" t="inlineStr">
@@ -5351,76 +5212,60 @@
       </c>
     </row>
     <row r="48">
-      <c r="D48" s="60" t="inlineStr">
+      <c r="D48" s="36" t="inlineStr">
         <is>
           <t>Maven @ 806</t>
         </is>
       </c>
-      <c r="E48" s="61" t="inlineStr">
+      <c r="E48" s="54" t="inlineStr">
         <is>
           <t>CL - 806-28</t>
         </is>
       </c>
-      <c r="F48" s="61" t="inlineStr">
+      <c r="F48" s="54" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="G48" s="61" t="inlineStr">
+      <c r="G48" s="54" t="inlineStr">
         <is>
           <t>2 BD / 1 BA</t>
         </is>
       </c>
-      <c r="H48" s="62" t="n"/>
-      <c r="I48" s="62" t="n"/>
-      <c r="J48" s="62" t="n"/>
-      <c r="K48" s="60" t="inlineStr">
+      <c r="K48" s="36" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L48" s="63" t="n">
+      <c r="L48" s="55" t="n">
         <v>775</v>
       </c>
-      <c r="M48" s="64" t="n">
+      <c r="M48" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="N48" s="64" t="n">
+      <c r="N48" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="O48" s="62" t="n"/>
-      <c r="P48" s="62" t="n"/>
-      <c r="Q48" s="65" t="inlineStr">
+      <c r="Q48" s="57" t="inlineStr">
         <is>
           <t>Vac</t>
         </is>
       </c>
-      <c r="R48" s="62" t="n"/>
-      <c r="S48" s="62" t="n"/>
-      <c r="T48" s="62" t="n"/>
-      <c r="U48" s="66" t="n">
+      <c r="U48" s="58" t="n">
         <v>1355</v>
       </c>
-      <c r="V48" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="62" t="n"/>
-      <c r="AA48" s="62" t="n"/>
-      <c r="AB48" s="62" t="n"/>
-      <c r="AC48" s="62" t="n"/>
-      <c r="AD48" s="62" t="n"/>
-      <c r="AE48" s="62" t="n"/>
-      <c r="AF48" s="62" t="n"/>
-      <c r="AG48" s="62" t="n"/>
+      <c r="V48" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="D49" s="36" t="inlineStr">
@@ -6073,59 +5918,59 @@
       </c>
     </row>
     <row r="59">
-      <c r="C59" s="67" t="inlineStr">
+      <c r="C59" s="60" t="inlineStr">
         <is>
           <t>Total / Wtd. Average</t>
         </is>
       </c>
-      <c r="D59" s="68" t="n"/>
-      <c r="E59" s="68" t="n"/>
-      <c r="F59" s="68" t="n"/>
-      <c r="G59" s="69" t="n">
+      <c r="D59" s="61" t="n"/>
+      <c r="E59" s="61" t="n"/>
+      <c r="F59" s="61" t="n"/>
+      <c r="G59" s="62" t="n">
         <v>51</v>
       </c>
-      <c r="H59" s="68" t="n"/>
-      <c r="I59" s="68" t="n"/>
-      <c r="J59" s="68" t="n"/>
-      <c r="K59" s="68" t="n"/>
-      <c r="L59" s="70" t="n">
+      <c r="H59" s="61" t="n"/>
+      <c r="I59" s="61" t="n"/>
+      <c r="J59" s="61" t="n"/>
+      <c r="K59" s="61" t="n"/>
+      <c r="L59" s="63" t="n">
         <v>38376</v>
       </c>
-      <c r="M59" s="68" t="n"/>
-      <c r="N59" s="68" t="n"/>
-      <c r="O59" s="68" t="n"/>
-      <c r="P59" s="68" t="n"/>
-      <c r="Q59" s="68" t="n"/>
-      <c r="R59" s="68" t="n"/>
-      <c r="S59" s="68" t="n"/>
-      <c r="T59" s="68" t="n"/>
-      <c r="U59" s="71" t="n">
+      <c r="M59" s="61" t="n"/>
+      <c r="N59" s="61" t="n"/>
+      <c r="O59" s="61" t="n"/>
+      <c r="P59" s="61" t="n"/>
+      <c r="Q59" s="61" t="n"/>
+      <c r="R59" s="61" t="n"/>
+      <c r="S59" s="61" t="n"/>
+      <c r="T59" s="61" t="n"/>
+      <c r="U59" s="64" t="n">
         <v>66209</v>
       </c>
-      <c r="V59" s="71" t="n">
+      <c r="V59" s="64" t="n">
         <v>51660.3</v>
       </c>
-      <c r="W59" s="71" t="n">
+      <c r="W59" s="64" t="n">
         <v>-374.7</v>
       </c>
-      <c r="X59" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="71" t="n">
+      <c r="X59" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="64" t="n">
         <v>6361</v>
       </c>
-      <c r="Z59" s="68" t="n"/>
-      <c r="AA59" s="68" t="n"/>
-      <c r="AB59" s="68" t="n"/>
-      <c r="AC59" s="68" t="n"/>
-      <c r="AD59" s="68" t="n"/>
-      <c r="AE59" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" s="73" t="n"/>
+      <c r="Z59" s="61" t="n"/>
+      <c r="AA59" s="61" t="n"/>
+      <c r="AB59" s="61" t="n"/>
+      <c r="AC59" s="61" t="n"/>
+      <c r="AD59" s="61" t="n"/>
+      <c r="AE59" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="66" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6173,5244 +6018,5424 @@
   </cols>
   <sheetData>
     <row r="3">
-      <c r="C3" s="74" t="inlineStr">
+      <c r="C3" s="67" t="inlineStr">
         <is>
           <t>Checking:</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="75" t="inlineStr">
+      <c r="C4" s="68" t="inlineStr">
         <is>
           <t>Floor Plan</t>
         </is>
       </c>
-      <c r="D4" s="75" t="inlineStr">
+      <c r="D4" s="68" t="inlineStr">
         <is>
           <t>Unit Type</t>
         </is>
       </c>
-      <c r="E4" s="76" t="inlineStr">
+      <c r="E4" s="69" t="inlineStr">
         <is>
           <t>BD</t>
         </is>
       </c>
-      <c r="F4" s="76" t="inlineStr">
+      <c r="F4" s="69" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="G4" s="76" t="inlineStr">
+      <c r="G4" s="69" t="inlineStr">
         <is>
           <t>Renovated</t>
         </is>
       </c>
-      <c r="H4" s="77" t="inlineStr">
+      <c r="H4" s="70" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="I4" s="77" t="inlineStr">
+      <c r="I4" s="70" t="inlineStr">
         <is>
           <t># Occ</t>
         </is>
       </c>
-      <c r="J4" s="77" t="inlineStr">
+      <c r="J4" s="70" t="inlineStr">
         <is>
           <t>#Vac</t>
         </is>
       </c>
-      <c r="K4" s="77" t="inlineStr">
+      <c r="K4" s="70" t="inlineStr">
         <is>
           <t>Avg SF</t>
         </is>
       </c>
-      <c r="L4" s="77" t="inlineStr">
+      <c r="L4" s="70" t="inlineStr">
         <is>
           <t>Total SF</t>
         </is>
       </c>
-      <c r="M4" s="77" t="inlineStr">
+      <c r="M4" s="70" t="inlineStr">
         <is>
           <t>Occ SF</t>
         </is>
       </c>
-      <c r="N4" s="77" t="inlineStr">
+      <c r="N4" s="70" t="inlineStr">
         <is>
           <t>Vac SF</t>
         </is>
       </c>
-      <c r="O4" s="77" t="inlineStr">
+      <c r="O4" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">Market Rent </t>
         </is>
       </c>
-      <c r="P4" s="77" t="inlineStr">
+      <c r="P4" s="70" t="inlineStr">
         <is>
           <t>Rent</t>
         </is>
       </c>
-      <c r="Q4" s="77" t="inlineStr">
+      <c r="Q4" s="70" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="R4" s="77" t="inlineStr">
+      <c r="R4" s="70" t="inlineStr">
         <is>
           <t>Concessions</t>
         </is>
       </c>
-      <c r="S4" s="77" t="inlineStr">
+      <c r="S4" s="70" t="inlineStr">
         <is>
           <t>Emp Discounts</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="78" t="inlineStr">
+      <c r="C5" s="71" t="inlineStr">
         <is>
           <t>1 BD / 1 BA</t>
         </is>
       </c>
-      <c r="D5" s="79" t="inlineStr">
+      <c r="D5" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="E5" s="80" t="n">
+      <c r="E5" s="73" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="81" t="n">
+      <c r="F5" s="74" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="80" t="inlineStr">
+      <c r="G5" s="73" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H5" s="82">
+      <c r="H5" s="75">
         <f>COUNTIFS($D$32:$D$82,$C5)</f>
         <v/>
       </c>
-      <c r="I5" s="82">
+      <c r="I5" s="75">
         <f>COUNTIFS($D$32:$D$82,$C5,$C$32:$C$82,"Occ")+COUNTIFS($D$32:$D$82,$C5,$C$32:$C$82,"Admin")+COUNTIFS($D$32:$D$82,$C5,$C$32:$C$82,"Down")+COUNTIFS($D$32:$D$82,$C5,$C$32:$C$82,"Super")+COUNTIFS($D$32:$D$82,$C5,$C$32:$C$82,"Model")</f>
         <v/>
       </c>
-      <c r="J5" s="82">
+      <c r="J5" s="75">
         <f>COUNTIFS($D$32:$D$82,$C5,$C$32:$C$82,"Vac")</f>
         <v/>
       </c>
-      <c r="K5" s="82">
+      <c r="K5" s="75">
         <f>IFERROR(AVERAGEIFS($J$32:$J$82,$D$32:$D$82,$C5),"n/a")</f>
         <v/>
       </c>
-      <c r="L5" s="82">
+      <c r="L5" s="75">
         <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C5)</f>
         <v/>
       </c>
-      <c r="M5" s="82">
+      <c r="M5" s="75">
         <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C5,$C$32:$C$82,"Occ")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C5,$C$32:$C$82,"Admin")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C5,$C$32:$C$82,"Down")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C5,$C$32:$C$82,"Super")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C5,$C$32:$C$82,"Model")</f>
         <v/>
       </c>
-      <c r="N5" s="82">
+      <c r="N5" s="75">
         <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C5,$C$32:$C$82,"Vac")</f>
         <v/>
       </c>
-      <c r="O5" s="82">
+      <c r="O5" s="75">
         <f>SUMIFS($L$32:$L$82,$D$32:$D$82,$C5)</f>
         <v/>
       </c>
-      <c r="P5" s="82">
+      <c r="P5" s="75">
         <f>SUMIFS($M$32:$M$82,$D$32:$D$82,$C5)</f>
         <v/>
       </c>
-      <c r="Q5" s="82">
+      <c r="Q5" s="75">
         <f>SUMIFS($R$32:$R$82,$D$32:$D$82,$C5)</f>
         <v/>
       </c>
-      <c r="R5" s="82">
+      <c r="R5" s="75">
         <f>SUMIFS($S$32:$S$82,$D$32:$D$82,$C5)</f>
         <v/>
       </c>
-      <c r="S5" s="82">
+      <c r="S5" s="75">
         <f>SUMIFS($T$32:$T$82,$D$32:$D$82,$C5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="78" t="inlineStr">
+      <c r="C6" s="71" t="inlineStr">
         <is>
           <t>1 BD / 1 BA</t>
         </is>
       </c>
-      <c r="D6" s="79" t="inlineStr">
+      <c r="D6" s="72" t="inlineStr">
         <is>
           <t>1x1B_C</t>
         </is>
       </c>
-      <c r="E6" s="80" t="n">
+      <c r="E6" s="73" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="81" t="n">
+      <c r="F6" s="74" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="80" t="inlineStr">
+      <c r="G6" s="73" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H6" s="82">
+      <c r="H6" s="75">
         <f>COUNTIFS($D$32:$D$82,$C6)</f>
         <v/>
       </c>
-      <c r="I6" s="82">
+      <c r="I6" s="75">
         <f>COUNTIFS($D$32:$D$82,$C6,$C$32:$C$82,"Occ")+COUNTIFS($D$32:$D$82,$C6,$C$32:$C$82,"Admin")+COUNTIFS($D$32:$D$82,$C6,$C$32:$C$82,"Down")+COUNTIFS($D$32:$D$82,$C6,$C$32:$C$82,"Super")+COUNTIFS($D$32:$D$82,$C6,$C$32:$C$82,"Model")</f>
         <v/>
       </c>
-      <c r="J6" s="82">
+      <c r="J6" s="75">
         <f>COUNTIFS($D$32:$D$82,$C6,$C$32:$C$82,"Vac")</f>
         <v/>
       </c>
-      <c r="K6" s="82">
+      <c r="K6" s="75">
         <f>IFERROR(AVERAGEIFS($J$32:$J$82,$D$32:$D$82,$C6),"n/a")</f>
         <v/>
       </c>
-      <c r="L6" s="82">
+      <c r="L6" s="75">
         <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C6)</f>
         <v/>
       </c>
-      <c r="M6" s="82">
+      <c r="M6" s="75">
         <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C6,$C$32:$C$82,"Occ")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C6,$C$32:$C$82,"Admin")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C6,$C$32:$C$82,"Down")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C6,$C$32:$C$82,"Super")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C6,$C$32:$C$82,"Model")</f>
         <v/>
       </c>
-      <c r="N6" s="82">
+      <c r="N6" s="75">
         <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C6,$C$32:$C$82,"Vac")</f>
         <v/>
       </c>
-      <c r="O6" s="82">
+      <c r="O6" s="75">
         <f>SUMIFS($L$32:$L$82,$D$32:$D$82,$C6)</f>
         <v/>
       </c>
-      <c r="P6" s="82">
+      <c r="P6" s="75">
         <f>SUMIFS($M$32:$M$82,$D$32:$D$82,$C6)</f>
         <v/>
       </c>
-      <c r="Q6" s="82">
+      <c r="Q6" s="75">
         <f>SUMIFS($R$32:$R$82,$D$32:$D$82,$C6)</f>
         <v/>
       </c>
-      <c r="R6" s="82">
+      <c r="R6" s="75">
         <f>SUMIFS($S$32:$S$82,$D$32:$D$82,$C6)</f>
         <v/>
       </c>
-      <c r="S6" s="82">
+      <c r="S6" s="75">
         <f>SUMIFS($T$32:$T$82,$D$32:$D$82,$C6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="78" t="inlineStr">
+      <c r="C7" s="71" t="inlineStr">
         <is>
           <t>2 BD / 1 BA</t>
         </is>
       </c>
-      <c r="D7" s="79" t="inlineStr">
+      <c r="D7" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="E7" s="80" t="n">
+      <c r="E7" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="81" t="n">
+      <c r="F7" s="74" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="80" t="inlineStr">
+      <c r="G7" s="73" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H7" s="82">
+      <c r="H7" s="75">
         <f>COUNTIFS($D$32:$D$82,$C7)</f>
         <v/>
       </c>
-      <c r="I7" s="82">
+      <c r="I7" s="75">
         <f>COUNTIFS($D$32:$D$82,$C7,$C$32:$C$82,"Occ")+COUNTIFS($D$32:$D$82,$C7,$C$32:$C$82,"Admin")+COUNTIFS($D$32:$D$82,$C7,$C$32:$C$82,"Down")+COUNTIFS($D$32:$D$82,$C7,$C$32:$C$82,"Super")+COUNTIFS($D$32:$D$82,$C7,$C$32:$C$82,"Model")</f>
         <v/>
       </c>
-      <c r="J7" s="82">
+      <c r="J7" s="75">
         <f>COUNTIFS($D$32:$D$82,$C7,$C$32:$C$82,"Vac")</f>
         <v/>
       </c>
-      <c r="K7" s="82">
+      <c r="K7" s="75">
         <f>IFERROR(AVERAGEIFS($J$32:$J$82,$D$32:$D$82,$C7),"n/a")</f>
         <v/>
       </c>
-      <c r="L7" s="82">
+      <c r="L7" s="75">
         <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C7)</f>
         <v/>
       </c>
-      <c r="M7" s="82">
+      <c r="M7" s="75">
         <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C7,$C$32:$C$82,"Occ")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C7,$C$32:$C$82,"Admin")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C7,$C$32:$C$82,"Down")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C7,$C$32:$C$82,"Super")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C7,$C$32:$C$82,"Model")</f>
         <v/>
       </c>
-      <c r="N7" s="82">
+      <c r="N7" s="75">
         <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C7,$C$32:$C$82,"Vac")</f>
         <v/>
       </c>
-      <c r="O7" s="82">
+      <c r="O7" s="75">
         <f>SUMIFS($L$32:$L$82,$D$32:$D$82,$C7)</f>
         <v/>
       </c>
-      <c r="P7" s="82">
+      <c r="P7" s="75">
         <f>SUMIFS($M$32:$M$82,$D$32:$D$82,$C7)</f>
         <v/>
       </c>
-      <c r="Q7" s="82">
+      <c r="Q7" s="75">
         <f>SUMIFS($R$32:$R$82,$D$32:$D$82,$C7)</f>
         <v/>
       </c>
-      <c r="R7" s="82">
+      <c r="R7" s="75">
         <f>SUMIFS($S$32:$S$82,$D$32:$D$82,$C7)</f>
         <v/>
       </c>
-      <c r="S7" s="82">
+      <c r="S7" s="75">
         <f>SUMIFS($T$32:$T$82,$D$32:$D$82,$C7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="78" t="inlineStr">
+      <c r="C8" s="71" t="inlineStr">
         <is>
           <t>2 BD / 2 BA</t>
         </is>
       </c>
-      <c r="D8" s="79" t="inlineStr">
+      <c r="D8" s="72" t="inlineStr">
         <is>
           <t>2x2B_C</t>
         </is>
       </c>
-      <c r="E8" s="80" t="n">
+      <c r="E8" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="81" t="n">
+      <c r="F8" s="74" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="80" t="inlineStr">
+      <c r="G8" s="73" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H8" s="82">
+      <c r="H8" s="75">
         <f>COUNTIFS($D$32:$D$82,$C8)</f>
         <v/>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="75">
         <f>COUNTIFS($D$32:$D$82,$C8,$C$32:$C$82,"Occ")+COUNTIFS($D$32:$D$82,$C8,$C$32:$C$82,"Admin")+COUNTIFS($D$32:$D$82,$C8,$C$32:$C$82,"Down")+COUNTIFS($D$32:$D$82,$C8,$C$32:$C$82,"Super")+COUNTIFS($D$32:$D$82,$C8,$C$32:$C$82,"Model")</f>
         <v/>
       </c>
-      <c r="J8" s="82">
+      <c r="J8" s="75">
         <f>COUNTIFS($D$32:$D$82,$C8,$C$32:$C$82,"Vac")</f>
         <v/>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="75">
         <f>IFERROR(AVERAGEIFS($J$32:$J$82,$D$32:$D$82,$C8),"n/a")</f>
         <v/>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="75">
         <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C8)</f>
         <v/>
       </c>
-      <c r="M8" s="82">
+      <c r="M8" s="75">
         <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C8,$C$32:$C$82,"Occ")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C8,$C$32:$C$82,"Admin")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C8,$C$32:$C$82,"Down")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C8,$C$32:$C$82,"Super")+SUMIFS($J$32:$J$82,$D$32:$D$82,$C8,$C$32:$C$82,"Model")</f>
         <v/>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="75">
         <f>SUMIFS($J$32:$J$82,$D$32:$D$82,$C8,$C$32:$C$82,"Vac")</f>
         <v/>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="75">
         <f>SUMIFS($L$32:$L$82,$D$32:$D$82,$C8)</f>
         <v/>
       </c>
-      <c r="P8" s="82">
+      <c r="P8" s="75">
         <f>SUMIFS($M$32:$M$82,$D$32:$D$82,$C8)</f>
         <v/>
       </c>
-      <c r="Q8" s="82">
+      <c r="Q8" s="75">
         <f>SUMIFS($R$32:$R$82,$D$32:$D$82,$C8)</f>
         <v/>
       </c>
-      <c r="R8" s="82">
+      <c r="R8" s="75">
         <f>SUMIFS($S$32:$S$82,$D$32:$D$82,$C8)</f>
         <v/>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="75">
         <f>SUMIFS($T$32:$T$82,$D$32:$D$82,$C8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="75" t="inlineStr">
+      <c r="C9" s="68" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
-      <c r="H9" s="83">
+      <c r="H9" s="76">
         <f>SUM(H5:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="83">
+      <c r="I9" s="76">
         <f>SUM(I5:I8)</f>
         <v/>
       </c>
-      <c r="J9" s="83">
+      <c r="J9" s="76">
         <f>SUM(J5:J8)</f>
         <v/>
       </c>
-      <c r="L9" s="83">
+      <c r="L9" s="76">
         <f>SUM(L5:L8)</f>
         <v/>
       </c>
-      <c r="M9" s="83">
+      <c r="M9" s="76">
         <f>SUM(M5:M8)</f>
         <v/>
       </c>
-      <c r="N9" s="83">
+      <c r="N9" s="76">
         <f>SUM(N5:N8)</f>
         <v/>
       </c>
-      <c r="O9" s="83">
+      <c r="O9" s="76">
         <f>SUM(O5:O8)</f>
         <v/>
       </c>
-      <c r="P9" s="83">
+      <c r="P9" s="76">
         <f>SUM(P5:P8)</f>
         <v/>
       </c>
-      <c r="Q9" s="83">
+      <c r="Q9" s="76">
         <f>SUM(Q5:Q8)</f>
         <v/>
       </c>
-      <c r="R9" s="83">
+      <c r="R9" s="76">
         <f>SUM(R5:R8)</f>
         <v/>
       </c>
-      <c r="S9" s="83">
+      <c r="S9" s="76">
         <f>SUM(S5:S8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="75" t="inlineStr">
+      <c r="C10" s="68" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="I10" s="84">
+      <c r="I10" s="77">
         <f>I9/$H$9</f>
         <v/>
       </c>
-      <c r="J10" s="84">
+      <c r="J10" s="77">
         <f>J9/$H$9</f>
         <v/>
       </c>
-      <c r="M10" s="84">
+      <c r="M10" s="77">
         <f>IFERROR(M9/$L$9,"n/a")</f>
         <v/>
       </c>
-      <c r="N10" s="84">
+      <c r="N10" s="77">
         <f>IFERROR(N9/$L$9,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="85" t="inlineStr">
+      <c r="C14" s="78" t="inlineStr">
         <is>
           <t>Notes:</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="85" t="inlineStr">
+      <c r="C15" s="78" t="inlineStr">
         <is>
           <t>1. Vacant units market rent is the per-unit market/asking rent from the source.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="85" t="inlineStr">
+      <c r="C16" s="78" t="inlineStr">
         <is>
           <t>2. BD/BA count is from the Unit Type mapping above (edit the yellow cells to adjust).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="85" t="inlineStr">
+      <c r="C21" s="78" t="inlineStr">
         <is>
           <t>Property Name</t>
         </is>
       </c>
-      <c r="D21" s="85" t="inlineStr">
+      <c r="D21" s="78" t="inlineStr">
         <is>
           <t>Maven @ 806</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="85" t="inlineStr">
+      <c r="C22" s="78" t="inlineStr">
         <is>
           <t>Rent Roll Date</t>
         </is>
       </c>
-      <c r="D22" s="86" t="n">
+      <c r="D22" s="79" t="n">
         <v>46157</v>
       </c>
     </row>
     <row r="30">
-      <c r="Y30" s="74" t="inlineStr">
+      <c r="Y30" s="67" t="inlineStr">
         <is>
           <t>Rent</t>
         </is>
       </c>
-      <c r="AB30" s="74" t="inlineStr">
+      <c r="AB30" s="67" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="AK30" s="74" t="inlineStr">
+      <c r="AK30" s="67" t="inlineStr">
         <is>
           <t>Concessions</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="74" t="inlineStr">
+      <c r="A31" s="67" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B31" s="74" t="inlineStr">
+      <c r="B31" s="67" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C31" s="74" t="inlineStr">
+      <c r="C31" s="67" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="D31" s="74" t="inlineStr">
+      <c r="D31" s="67" t="inlineStr">
         <is>
           <t>Floorplan</t>
         </is>
       </c>
-      <c r="E31" s="74" t="inlineStr">
+      <c r="E31" s="67" t="inlineStr">
         <is>
           <t>Bd</t>
         </is>
       </c>
-      <c r="F31" s="74" t="inlineStr">
+      <c r="F31" s="67" t="inlineStr">
         <is>
           <t>Ba</t>
         </is>
       </c>
-      <c r="G31" s="74" t="inlineStr">
+      <c r="G31" s="67" t="inlineStr">
         <is>
           <t>Renovated</t>
         </is>
       </c>
-      <c r="H31" s="74" t="inlineStr">
+      <c r="H31" s="67" t="inlineStr">
         <is>
           <t>Unit #</t>
         </is>
       </c>
-      <c r="I31" s="74" t="inlineStr">
+      <c r="I31" s="67" t="inlineStr">
         <is>
           <t>Unit Type</t>
         </is>
       </c>
-      <c r="J31" s="74" t="inlineStr">
+      <c r="J31" s="67" t="inlineStr">
         <is>
           <t>Unit Sq Ft</t>
         </is>
       </c>
-      <c r="K31" s="74" t="inlineStr">
+      <c r="K31" s="67" t="inlineStr">
         <is>
           <t>Resident/Tenant Name</t>
         </is>
       </c>
-      <c r="L31" s="74" t="inlineStr">
+      <c r="L31" s="67" t="inlineStr">
         <is>
           <t>Market Rent</t>
         </is>
       </c>
-      <c r="M31" s="74" t="inlineStr">
+      <c r="M31" s="67" t="inlineStr">
         <is>
           <t>Rent</t>
         </is>
       </c>
-      <c r="N31" s="74" t="inlineStr">
+      <c r="N31" s="67" t="inlineStr">
         <is>
           <t>Move in</t>
         </is>
       </c>
-      <c r="O31" s="74" t="inlineStr">
+      <c r="O31" s="67" t="inlineStr">
         <is>
           <t>Lease Start</t>
         </is>
       </c>
-      <c r="P31" s="74" t="inlineStr">
+      <c r="P31" s="67" t="inlineStr">
         <is>
           <t>Lease End</t>
         </is>
       </c>
-      <c r="Q31" s="74" t="inlineStr">
+      <c r="Q31" s="67" t="inlineStr">
         <is>
           <t>Move Out</t>
         </is>
       </c>
-      <c r="R31" s="74" t="inlineStr">
+      <c r="R31" s="67" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="S31" s="74" t="inlineStr">
+      <c r="S31" s="67" t="inlineStr">
         <is>
           <t>Concessions</t>
         </is>
       </c>
-      <c r="T31" s="74" t="inlineStr">
+      <c r="T31" s="67" t="inlineStr">
         <is>
           <t>Employee Discounts</t>
         </is>
       </c>
-      <c r="V31" s="74" t="inlineStr">
+      <c r="V31" s="67" t="inlineStr">
         <is>
           <t>Unit Type (Manual)</t>
         </is>
       </c>
-      <c r="W31" s="74" t="inlineStr">
+      <c r="W31" s="67" t="inlineStr">
         <is>
           <t>Unit Type (Manual) - Updated</t>
         </is>
       </c>
-      <c r="Y31" s="74" t="inlineStr">
+      <c r="Y31" s="67" t="inlineStr">
         <is>
           <t>RENT</t>
         </is>
       </c>
-      <c r="AB31" s="74" t="inlineStr">
+      <c r="AB31" s="67" t="inlineStr">
         <is>
           <t>Building Protection Policy</t>
         </is>
       </c>
-      <c r="AC31" s="74" t="inlineStr">
+      <c r="AC31" s="67" t="inlineStr">
         <is>
           <t>Pet Rent</t>
         </is>
       </c>
-      <c r="AD31" s="74" t="inlineStr">
+      <c r="AD31" s="67" t="inlineStr">
         <is>
           <t>Resident Pest Control</t>
         </is>
       </c>
-      <c r="AE31" s="74" t="inlineStr">
+      <c r="AE31" s="67" t="inlineStr">
         <is>
           <t>Resident Trash Charge</t>
         </is>
       </c>
-      <c r="AF31" s="74" t="inlineStr">
+      <c r="AF31" s="67" t="inlineStr">
         <is>
           <t>Resident Water Charge</t>
         </is>
       </c>
-      <c r="AG31" s="74" t="inlineStr">
+      <c r="AG31" s="67" t="inlineStr">
         <is>
           <t>WiFi/Cable Rent</t>
         </is>
       </c>
-      <c r="AH31" s="74" t="inlineStr">
+      <c r="AH31" s="67" t="inlineStr">
         <is>
           <t>MTM Fee</t>
         </is>
       </c>
-      <c r="AI31" s="74" t="inlineStr">
+      <c r="AI31" s="67" t="inlineStr">
         <is>
           <t>Resident Utilities (Rubs) Charge</t>
         </is>
       </c>
-      <c r="AK31" s="74" t="inlineStr">
+      <c r="AK31" s="67" t="inlineStr">
         <is>
           <t>Concession</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="79">
+      <c r="A32" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B32" s="79" t="n">
+      <c r="B32" s="72" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="79">
+      <c r="C32" s="72">
         <f>IF(K32="Vacant","Vac",IF(K32="Model","Model",IF(K32="Admin","Admin",IF(K32="Down","Down",IF(K32="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D32" s="79">
+      <c r="D32" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I32,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E32" s="79">
+      <c r="E32" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D32,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F32" s="79">
+      <c r="F32" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D32,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G32" s="79">
+      <c r="G32" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D32,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H32" s="79" t="inlineStr">
+      <c r="H32" s="72" t="inlineStr">
         <is>
           <t>800-1A</t>
         </is>
       </c>
-      <c r="I32" s="79" t="inlineStr">
+      <c r="I32" s="72" t="inlineStr">
         <is>
           <t>1x1B_C</t>
         </is>
       </c>
-      <c r="J32" s="87" t="n">
+      <c r="J32" s="80" t="n">
         <v>817</v>
       </c>
-      <c r="K32" s="79" t="inlineStr">
+      <c r="K32" s="72" t="inlineStr">
         <is>
           <t>HiSmith, Darwin</t>
         </is>
       </c>
-      <c r="L32" s="88" t="n">
+      <c r="L32" s="81" t="n">
         <v>1234</v>
       </c>
-      <c r="M32" s="88">
+      <c r="M32" s="81">
         <f>Y32</f>
         <v/>
       </c>
-      <c r="N32" s="89" t="n">
+      <c r="N32" s="82" t="n">
         <v>45380</v>
       </c>
-      <c r="O32" s="89" t="n">
+      <c r="O32" s="82" t="n">
         <v>46110</v>
       </c>
-      <c r="P32" s="89" t="n">
+      <c r="P32" s="82" t="n">
         <v>46474</v>
       </c>
-      <c r="R32" s="88">
+      <c r="R32" s="81">
         <f>SUM(AB32:AI32)</f>
         <v/>
       </c>
-      <c r="S32" s="88">
+      <c r="S32" s="81">
         <f>AK32</f>
         <v/>
       </c>
-      <c r="T32" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="88" t="n">
+      <c r="T32" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="81" t="n">
         <v>1285</v>
       </c>
-      <c r="AB32" s="88" t="n">
+      <c r="AB32" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AC32" s="88" t="n">
+      <c r="AC32" s="81" t="n">
         <v>35</v>
       </c>
-      <c r="AD32" s="88" t="n">
+      <c r="AD32" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE32" s="88" t="n">
+      <c r="AE32" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF32" s="88" t="n">
+      <c r="AF32" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG32" s="88" t="n">
+      <c r="AG32" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="79">
+      <c r="A33" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B33" s="79">
+      <c r="B33" s="72">
         <f>B32+1</f>
         <v/>
       </c>
-      <c r="C33" s="79">
+      <c r="C33" s="72">
         <f>IF(K33="Vacant","Vac",IF(K33="Model","Model",IF(K33="Admin","Admin",IF(K33="Down","Down",IF(K33="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D33" s="79">
+      <c r="D33" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I33,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E33" s="79">
+      <c r="E33" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D33,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F33" s="79">
+      <c r="F33" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D33,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G33" s="79">
+      <c r="G33" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D33,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H33" s="79" t="inlineStr">
+      <c r="H33" s="72" t="inlineStr">
         <is>
           <t>800-1AU</t>
         </is>
       </c>
-      <c r="I33" s="79" t="inlineStr">
+      <c r="I33" s="72" t="inlineStr">
         <is>
           <t>1x1B_C</t>
         </is>
       </c>
-      <c r="J33" s="87" t="n">
+      <c r="J33" s="80" t="n">
         <v>745</v>
       </c>
-      <c r="K33" s="79" t="inlineStr">
+      <c r="K33" s="72" t="inlineStr">
         <is>
           <t>Rental, Meraki Rentals</t>
         </is>
       </c>
-      <c r="L33" s="88" t="n">
+      <c r="L33" s="81" t="n">
         <v>1159</v>
       </c>
-      <c r="M33" s="88">
+      <c r="M33" s="81">
         <f>Y33</f>
         <v/>
       </c>
-      <c r="N33" s="89" t="n">
+      <c r="N33" s="82" t="n">
         <v>45000</v>
       </c>
-      <c r="O33" s="89" t="n">
+      <c r="O33" s="82" t="n">
         <v>45792</v>
       </c>
-      <c r="P33" s="89" t="n">
+      <c r="P33" s="82" t="n">
         <v>46248</v>
       </c>
-      <c r="R33" s="88">
+      <c r="R33" s="81">
         <f>SUM(AB33:AI33)</f>
         <v/>
       </c>
-      <c r="S33" s="88">
+      <c r="S33" s="81">
         <f>AK33</f>
         <v/>
       </c>
-      <c r="T33" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="88" t="n">
+      <c r="T33" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="81" t="n">
         <v>1229</v>
       </c>
-      <c r="AB33" s="88" t="n">
+      <c r="AB33" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AD33" s="88" t="n">
+      <c r="AD33" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE33" s="88" t="n">
+      <c r="AE33" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF33" s="88" t="n">
+      <c r="AF33" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG33" s="88" t="n">
+      <c r="AG33" s="81" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="79">
+      <c r="A34" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B34" s="79">
+      <c r="B34" s="72">
         <f>B33+1</f>
         <v/>
       </c>
-      <c r="C34" s="79">
+      <c r="C34" s="72">
         <f>IF(K34="Vacant","Vac",IF(K34="Model","Model",IF(K34="Admin","Admin",IF(K34="Down","Down",IF(K34="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D34" s="79">
+      <c r="D34" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I34,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E34" s="79">
+      <c r="E34" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D34,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F34" s="79">
+      <c r="F34" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D34,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G34" s="79">
+      <c r="G34" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D34,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H34" s="79" t="inlineStr">
+      <c r="H34" s="72" t="inlineStr">
         <is>
           <t>800-1B</t>
         </is>
       </c>
-      <c r="I34" s="79" t="inlineStr">
+      <c r="I34" s="72" t="inlineStr">
         <is>
           <t>1x1B_C</t>
         </is>
       </c>
-      <c r="J34" s="87" t="n">
+      <c r="J34" s="80" t="n">
         <v>745</v>
       </c>
-      <c r="K34" s="79" t="inlineStr">
+      <c r="K34" s="72" t="inlineStr">
         <is>
           <t>Bhutia, Tshering</t>
         </is>
       </c>
-      <c r="L34" s="88" t="n">
+      <c r="L34" s="81" t="n">
         <v>1249</v>
       </c>
-      <c r="M34" s="88">
+      <c r="M34" s="81">
         <f>Y34</f>
         <v/>
       </c>
-      <c r="N34" s="89" t="n">
+      <c r="N34" s="82" t="n">
         <v>46143</v>
       </c>
-      <c r="O34" s="89" t="n">
+      <c r="O34" s="82" t="n">
         <v>46143</v>
       </c>
-      <c r="P34" s="89" t="n">
+      <c r="P34" s="82" t="n">
         <v>46507</v>
       </c>
-      <c r="R34" s="88">
+      <c r="R34" s="81">
         <f>SUM(AB34:AI34)</f>
         <v/>
       </c>
-      <c r="S34" s="88">
+      <c r="S34" s="81">
         <f>AK34</f>
         <v/>
       </c>
-      <c r="T34" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="88" t="n">
+      <c r="T34" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="81" t="n">
         <v>1249</v>
       </c>
-      <c r="AB34" s="88" t="n">
+      <c r="AB34" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD34" s="88" t="n">
+      <c r="AD34" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE34" s="88" t="n">
+      <c r="AE34" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF34" s="88" t="n">
+      <c r="AF34" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG34" s="88" t="n">
+      <c r="AG34" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="79">
+      <c r="A35" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B35" s="79">
+      <c r="B35" s="72">
         <f>B34+1</f>
         <v/>
       </c>
-      <c r="C35" s="79">
+      <c r="C35" s="72">
         <f>IF(K35="Vacant","Vac",IF(K35="Model","Model",IF(K35="Admin","Admin",IF(K35="Down","Down",IF(K35="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D35" s="79">
+      <c r="D35" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I35,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E35" s="79">
+      <c r="E35" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D35,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F35" s="79">
+      <c r="F35" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D35,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G35" s="79">
+      <c r="G35" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D35,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H35" s="79" t="inlineStr">
+      <c r="H35" s="72" t="inlineStr">
         <is>
           <t>800-1BU</t>
         </is>
       </c>
-      <c r="I35" s="79" t="inlineStr">
+      <c r="I35" s="72" t="inlineStr">
         <is>
           <t>1x1B_C</t>
         </is>
       </c>
-      <c r="J35" s="87" t="n">
+      <c r="J35" s="80" t="n">
         <v>641</v>
       </c>
-      <c r="K35" s="79" t="inlineStr">
+      <c r="K35" s="72" t="inlineStr">
         <is>
           <t>Brooks, Heidi</t>
         </is>
       </c>
-      <c r="L35" s="88" t="n">
+      <c r="L35" s="81" t="n">
         <v>1159</v>
       </c>
-      <c r="M35" s="88">
+      <c r="M35" s="81">
         <f>Y35</f>
         <v/>
       </c>
-      <c r="N35" s="89" t="n">
+      <c r="N35" s="82" t="n">
         <v>46115</v>
       </c>
-      <c r="O35" s="89" t="n">
+      <c r="O35" s="82" t="n">
         <v>46115</v>
       </c>
-      <c r="P35" s="89" t="n">
+      <c r="P35" s="82" t="n">
         <v>46328</v>
       </c>
-      <c r="R35" s="88">
+      <c r="R35" s="81">
         <f>SUM(AB35:AI35)</f>
         <v/>
       </c>
-      <c r="S35" s="88">
+      <c r="S35" s="81">
         <f>AK35</f>
         <v/>
       </c>
-      <c r="T35" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="88" t="n">
+      <c r="T35" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="81" t="n">
         <v>1239</v>
       </c>
-      <c r="AB35" s="88" t="n">
+      <c r="AB35" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD35" s="88" t="n">
+      <c r="AD35" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE35" s="88" t="n">
+      <c r="AE35" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF35" s="88" t="n">
+      <c r="AF35" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG35" s="88" t="n">
+      <c r="AG35" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="79">
+      <c r="A36" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B36" s="79">
+      <c r="B36" s="72">
         <f>B35+1</f>
         <v/>
       </c>
-      <c r="C36" s="79">
+      <c r="C36" s="72">
         <f>IF(K36="Vacant","Vac",IF(K36="Model","Model",IF(K36="Admin","Admin",IF(K36="Down","Down",IF(K36="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D36" s="79">
+      <c r="D36" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I36,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E36" s="79">
+      <c r="E36" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D36,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F36" s="79">
+      <c r="F36" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D36,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G36" s="79">
+      <c r="G36" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D36,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H36" s="79" t="inlineStr">
+      <c r="H36" s="72" t="inlineStr">
         <is>
           <t>800-1C</t>
         </is>
       </c>
-      <c r="I36" s="79" t="inlineStr">
+      <c r="I36" s="72" t="inlineStr">
         <is>
           <t>1x1B_C</t>
         </is>
       </c>
-      <c r="J36" s="87" t="n">
+      <c r="J36" s="80" t="n">
         <v>622</v>
       </c>
-      <c r="K36" s="79" t="inlineStr">
+      <c r="K36" s="72" t="inlineStr">
         <is>
           <t>Olmstead, Emma</t>
         </is>
       </c>
-      <c r="L36" s="88" t="n">
+      <c r="L36" s="81" t="n">
         <v>1234</v>
       </c>
-      <c r="M36" s="88">
+      <c r="M36" s="81">
         <f>Y36</f>
         <v/>
       </c>
-      <c r="N36" s="89" t="n">
+      <c r="N36" s="82" t="n">
         <v>45047</v>
       </c>
-      <c r="O36" s="89" t="n">
+      <c r="O36" s="82" t="n">
         <v>46143</v>
       </c>
-      <c r="P36" s="89" t="n">
+      <c r="P36" s="82" t="n">
         <v>46507</v>
       </c>
-      <c r="R36" s="88">
+      <c r="R36" s="81">
         <f>SUM(AB36:AI36)</f>
         <v/>
       </c>
-      <c r="S36" s="88">
+      <c r="S36" s="81">
         <f>AK36</f>
         <v/>
       </c>
-      <c r="T36" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="88" t="n">
+      <c r="T36" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="81" t="n">
         <v>1220</v>
       </c>
-      <c r="AB36" s="88" t="n">
+      <c r="AB36" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD36" s="88" t="n">
+      <c r="AD36" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE36" s="88" t="n">
+      <c r="AE36" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF36" s="88" t="n">
+      <c r="AF36" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG36" s="88" t="n">
+      <c r="AG36" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="79">
+      <c r="A37" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B37" s="79">
+      <c r="B37" s="72">
         <f>B36+1</f>
         <v/>
       </c>
-      <c r="C37" s="79">
+      <c r="C37" s="72">
         <f>IF(K37="Vacant","Vac",IF(K37="Model","Model",IF(K37="Admin","Admin",IF(K37="Down","Down",IF(K37="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D37" s="79">
+      <c r="D37" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I37,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E37" s="79">
+      <c r="E37" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D37,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F37" s="79">
+      <c r="F37" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D37,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G37" s="79">
+      <c r="G37" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D37,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H37" s="79" t="inlineStr">
+      <c r="H37" s="72" t="inlineStr">
         <is>
           <t>800-1D</t>
         </is>
       </c>
-      <c r="I37" s="79" t="inlineStr">
+      <c r="I37" s="72" t="inlineStr">
         <is>
           <t>1x1B_C</t>
         </is>
       </c>
-      <c r="J37" s="87" t="n">
+      <c r="J37" s="80" t="n">
         <v>622</v>
       </c>
-      <c r="K37" s="79" t="inlineStr">
+      <c r="K37" s="72" t="inlineStr">
         <is>
           <t>Calvert, Savannah</t>
         </is>
       </c>
-      <c r="L37" s="88" t="n">
+      <c r="L37" s="81" t="n">
         <v>1234</v>
       </c>
-      <c r="M37" s="88">
+      <c r="M37" s="81">
         <f>Y37</f>
         <v/>
       </c>
-      <c r="N37" s="89" t="n">
+      <c r="N37" s="82" t="n">
         <v>45863</v>
       </c>
-      <c r="O37" s="89" t="n">
+      <c r="O37" s="82" t="n">
         <v>45863</v>
       </c>
-      <c r="P37" s="89" t="n">
+      <c r="P37" s="82" t="n">
         <v>46319</v>
       </c>
-      <c r="R37" s="88">
+      <c r="R37" s="81">
         <f>SUM(AB37:AI37)</f>
         <v/>
       </c>
-      <c r="S37" s="88">
+      <c r="S37" s="81">
         <f>AK37</f>
         <v/>
       </c>
-      <c r="T37" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="88" t="n">
+      <c r="T37" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="81" t="n">
         <v>1234</v>
       </c>
-      <c r="AB37" s="88" t="n">
+      <c r="AB37" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD37" s="88" t="n">
+      <c r="AD37" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE37" s="88" t="n">
+      <c r="AE37" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF37" s="88" t="n">
+      <c r="AF37" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG37" s="88" t="n">
+      <c r="AG37" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="79">
+      <c r="A38" s="83">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B38" s="79">
+      <c r="B38" s="83">
         <f>B37+1</f>
         <v/>
       </c>
-      <c r="C38" s="79">
+      <c r="C38" s="83">
         <f>IF(K38="Vacant","Vac",IF(K38="Model","Model",IF(K38="Admin","Admin",IF(K38="Down","Down",IF(K38="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D38" s="79">
+      <c r="D38" s="83">
         <f>INDEX($C$5:$C$8,MATCH(I38,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E38" s="79">
+      <c r="E38" s="83">
         <f>INDEX($E$5:$E$8,MATCH(D38,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F38" s="79">
+      <c r="F38" s="83">
         <f>INDEX($F$5:$F$8,MATCH(D38,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G38" s="79">
+      <c r="G38" s="83">
         <f>INDEX($G$5:$G$8,MATCH(D38,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H38" s="79" t="inlineStr">
+      <c r="H38" s="83" t="inlineStr">
         <is>
           <t>800-2A</t>
         </is>
       </c>
-      <c r="I38" s="79" t="inlineStr">
+      <c r="I38" s="83" t="inlineStr">
         <is>
           <t>2x2B_C</t>
         </is>
       </c>
-      <c r="J38" s="87" t="n">
+      <c r="J38" s="84" t="n">
         <v>1253</v>
       </c>
-      <c r="K38" s="79" t="inlineStr">
+      <c r="K38" s="83" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L38" s="88" t="n">
+      <c r="L38" s="85" t="n">
         <v>1799</v>
       </c>
-      <c r="M38" s="88">
+      <c r="M38" s="85">
         <f>Y38</f>
         <v/>
       </c>
-      <c r="R38" s="88">
+      <c r="N38" s="86" t="n"/>
+      <c r="O38" s="86" t="n"/>
+      <c r="P38" s="86" t="n"/>
+      <c r="Q38" s="86" t="n"/>
+      <c r="R38" s="85">
         <f>SUM(AB38:AI38)</f>
         <v/>
       </c>
-      <c r="S38" s="88">
+      <c r="S38" s="85">
         <f>AK38</f>
         <v/>
       </c>
-      <c r="T38" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="88" t="n">
-        <v>0</v>
-      </c>
+      <c r="T38" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="86" t="n"/>
+      <c r="V38" s="86" t="n"/>
+      <c r="W38" s="86" t="n"/>
+      <c r="X38" s="86" t="n"/>
+      <c r="Y38" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="86" t="n"/>
+      <c r="AA38" s="86" t="n"/>
+      <c r="AB38" s="86" t="n"/>
+      <c r="AC38" s="86" t="n"/>
+      <c r="AD38" s="86" t="n"/>
+      <c r="AE38" s="86" t="n"/>
+      <c r="AF38" s="86" t="n"/>
+      <c r="AG38" s="86" t="n"/>
+      <c r="AH38" s="86" t="n"/>
+      <c r="AI38" s="86" t="n"/>
+      <c r="AJ38" s="86" t="n"/>
+      <c r="AK38" s="86" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="79">
+      <c r="A39" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B39" s="79">
+      <c r="B39" s="72">
         <f>B38+1</f>
         <v/>
       </c>
-      <c r="C39" s="79">
+      <c r="C39" s="72">
         <f>IF(K39="Vacant","Vac",IF(K39="Model","Model",IF(K39="Admin","Admin",IF(K39="Down","Down",IF(K39="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D39" s="79">
+      <c r="D39" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I39,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E39" s="79">
+      <c r="E39" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D39,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F39" s="79">
+      <c r="F39" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D39,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G39" s="79">
+      <c r="G39" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D39,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H39" s="79" t="inlineStr">
+      <c r="H39" s="72" t="inlineStr">
         <is>
           <t>800-2B</t>
         </is>
       </c>
-      <c r="I39" s="79" t="inlineStr">
+      <c r="I39" s="72" t="inlineStr">
         <is>
           <t>1x1B_C</t>
         </is>
       </c>
-      <c r="J39" s="87" t="n">
+      <c r="J39" s="80" t="n">
         <v>622</v>
       </c>
-      <c r="K39" s="79" t="inlineStr">
+      <c r="K39" s="72" t="inlineStr">
         <is>
           <t>Rental, Meraki Rentals</t>
         </is>
       </c>
-      <c r="L39" s="88" t="n">
+      <c r="L39" s="81" t="n">
         <v>1234</v>
       </c>
-      <c r="M39" s="88">
+      <c r="M39" s="81">
         <f>Y39</f>
         <v/>
       </c>
-      <c r="N39" s="89" t="n">
+      <c r="N39" s="82" t="n">
         <v>45331</v>
       </c>
-      <c r="O39" s="89" t="n">
+      <c r="O39" s="82" t="n">
         <v>45786</v>
       </c>
-      <c r="P39" s="89" t="n">
+      <c r="P39" s="82" t="n">
         <v>46242</v>
       </c>
-      <c r="R39" s="88">
+      <c r="R39" s="81">
         <f>SUM(AB39:AI39)</f>
         <v/>
       </c>
-      <c r="S39" s="88">
+      <c r="S39" s="81">
         <f>AK39</f>
         <v/>
       </c>
-      <c r="T39" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="88" t="n">
+      <c r="T39" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="81" t="n">
         <v>1230</v>
       </c>
-      <c r="AB39" s="88" t="n">
+      <c r="AB39" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AD39" s="88" t="n">
+      <c r="AD39" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE39" s="88" t="n">
+      <c r="AE39" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF39" s="88" t="n">
+      <c r="AF39" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG39" s="88" t="n">
+      <c r="AG39" s="81" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="79">
+      <c r="A40" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B40" s="79">
+      <c r="B40" s="72">
         <f>B39+1</f>
         <v/>
       </c>
-      <c r="C40" s="79">
+      <c r="C40" s="72">
         <f>IF(K40="Vacant","Vac",IF(K40="Model","Model",IF(K40="Admin","Admin",IF(K40="Down","Down",IF(K40="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D40" s="79">
+      <c r="D40" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I40,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E40" s="79">
+      <c r="E40" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D40,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F40" s="79">
+      <c r="F40" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D40,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G40" s="79">
+      <c r="G40" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D40,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H40" s="79" t="inlineStr">
+      <c r="H40" s="72" t="inlineStr">
         <is>
           <t>800-2C</t>
         </is>
       </c>
-      <c r="I40" s="79" t="inlineStr">
+      <c r="I40" s="72" t="inlineStr">
         <is>
           <t>1x1B_C</t>
         </is>
       </c>
-      <c r="J40" s="87" t="n">
+      <c r="J40" s="80" t="n">
         <v>745</v>
       </c>
-      <c r="K40" s="79" t="inlineStr">
+      <c r="K40" s="72" t="inlineStr">
         <is>
           <t>Dobbs, Warren</t>
         </is>
       </c>
-      <c r="L40" s="88" t="n">
+      <c r="L40" s="81" t="n">
         <v>1249</v>
       </c>
-      <c r="M40" s="88">
+      <c r="M40" s="81">
         <f>Y40</f>
         <v/>
       </c>
-      <c r="N40" s="89" t="n">
+      <c r="N40" s="82" t="n">
         <v>46108</v>
       </c>
-      <c r="O40" s="89" t="n">
+      <c r="O40" s="82" t="n">
         <v>46108</v>
       </c>
-      <c r="P40" s="89" t="n">
+      <c r="P40" s="82" t="n">
         <v>46472</v>
       </c>
-      <c r="R40" s="88">
+      <c r="R40" s="81">
         <f>SUM(AB40:AI40)</f>
         <v/>
       </c>
-      <c r="S40" s="88">
+      <c r="S40" s="81">
         <f>AK40</f>
         <v/>
       </c>
-      <c r="T40" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="88" t="n">
+      <c r="T40" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="81" t="n">
         <v>1249</v>
       </c>
-      <c r="AB40" s="88" t="n">
+      <c r="AB40" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD40" s="88" t="n">
+      <c r="AD40" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE40" s="88" t="n">
+      <c r="AE40" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF40" s="88" t="n">
+      <c r="AF40" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG40" s="88" t="n">
+      <c r="AG40" s="81" t="n">
         <v>65</v>
       </c>
-      <c r="AK40" s="88" t="n">
+      <c r="AK40" s="81" t="n">
         <v>-374.7</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="79">
+      <c r="A41" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B41" s="79">
+      <c r="B41" s="72">
         <f>B40+1</f>
         <v/>
       </c>
-      <c r="C41" s="79">
+      <c r="C41" s="72">
         <f>IF(K41="Vacant","Vac",IF(K41="Model","Model",IF(K41="Admin","Admin",IF(K41="Down","Down",IF(K41="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D41" s="79">
+      <c r="D41" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I41,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E41" s="79">
+      <c r="E41" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D41,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F41" s="79">
+      <c r="F41" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D41,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G41" s="79">
+      <c r="G41" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D41,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H41" s="79" t="inlineStr">
+      <c r="H41" s="72" t="inlineStr">
         <is>
           <t>800-2D</t>
         </is>
       </c>
-      <c r="I41" s="79" t="inlineStr">
+      <c r="I41" s="72" t="inlineStr">
         <is>
           <t>1x1B_C</t>
         </is>
       </c>
-      <c r="J41" s="87" t="n">
+      <c r="J41" s="80" t="n">
         <v>479</v>
       </c>
-      <c r="K41" s="79" t="inlineStr">
+      <c r="K41" s="72" t="inlineStr">
         <is>
           <t>Filbeck, Daniel</t>
         </is>
       </c>
-      <c r="L41" s="88" t="n">
+      <c r="L41" s="81" t="n">
         <v>1234</v>
       </c>
-      <c r="M41" s="88">
+      <c r="M41" s="81">
         <f>Y41</f>
         <v/>
       </c>
-      <c r="N41" s="89" t="n">
+      <c r="N41" s="82" t="n">
         <v>45057</v>
       </c>
-      <c r="O41" s="89" t="n">
+      <c r="O41" s="82" t="n">
         <v>45788</v>
       </c>
-      <c r="P41" s="89" t="n">
+      <c r="P41" s="82" t="n">
         <v>46244</v>
       </c>
-      <c r="R41" s="88">
+      <c r="R41" s="81">
         <f>SUM(AB41:AI41)</f>
         <v/>
       </c>
-      <c r="S41" s="88">
+      <c r="S41" s="81">
         <f>AK41</f>
         <v/>
       </c>
-      <c r="T41" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="88" t="n">
+      <c r="T41" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="81" t="n">
         <v>1325</v>
       </c>
-      <c r="AB41" s="88" t="n">
+      <c r="AB41" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AC41" s="88" t="n">
+      <c r="AC41" s="81" t="n">
         <v>35</v>
       </c>
-      <c r="AD41" s="88" t="n">
+      <c r="AD41" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE41" s="88" t="n">
+      <c r="AE41" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF41" s="88" t="n">
+      <c r="AF41" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG41" s="88" t="n">
+      <c r="AG41" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="79">
+      <c r="A42" s="83">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B42" s="79">
+      <c r="B42" s="83">
         <f>B41+1</f>
         <v/>
       </c>
-      <c r="C42" s="79">
+      <c r="C42" s="83">
         <f>IF(K42="Vacant","Vac",IF(K42="Model","Model",IF(K42="Admin","Admin",IF(K42="Down","Down",IF(K42="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D42" s="79">
+      <c r="D42" s="83">
         <f>INDEX($C$5:$C$8,MATCH(I42,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E42" s="79">
+      <c r="E42" s="83">
         <f>INDEX($E$5:$E$8,MATCH(D42,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F42" s="79">
+      <c r="F42" s="83">
         <f>INDEX($F$5:$F$8,MATCH(D42,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G42" s="79">
+      <c r="G42" s="83">
         <f>INDEX($G$5:$G$8,MATCH(D42,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H42" s="79" t="inlineStr">
+      <c r="H42" s="83" t="inlineStr">
         <is>
           <t>800-3A</t>
         </is>
       </c>
-      <c r="I42" s="79" t="inlineStr">
+      <c r="I42" s="83" t="inlineStr">
         <is>
           <t>2x2B_C</t>
         </is>
       </c>
-      <c r="J42" s="87" t="n">
+      <c r="J42" s="84" t="n">
         <v>1153</v>
       </c>
-      <c r="K42" s="79" t="inlineStr">
+      <c r="K42" s="83" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L42" s="88" t="n">
+      <c r="L42" s="85" t="n">
         <v>1799</v>
       </c>
-      <c r="M42" s="88">
+      <c r="M42" s="85">
         <f>Y42</f>
         <v/>
       </c>
-      <c r="R42" s="88">
+      <c r="N42" s="86" t="n"/>
+      <c r="O42" s="86" t="n"/>
+      <c r="P42" s="86" t="n"/>
+      <c r="Q42" s="86" t="n"/>
+      <c r="R42" s="85">
         <f>SUM(AB42:AI42)</f>
         <v/>
       </c>
-      <c r="S42" s="88">
+      <c r="S42" s="85">
         <f>AK42</f>
         <v/>
       </c>
-      <c r="T42" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="88" t="n">
-        <v>0</v>
-      </c>
+      <c r="T42" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="86" t="n"/>
+      <c r="V42" s="86" t="n"/>
+      <c r="W42" s="86" t="n"/>
+      <c r="X42" s="86" t="n"/>
+      <c r="Y42" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="86" t="n"/>
+      <c r="AA42" s="86" t="n"/>
+      <c r="AB42" s="86" t="n"/>
+      <c r="AC42" s="86" t="n"/>
+      <c r="AD42" s="86" t="n"/>
+      <c r="AE42" s="86" t="n"/>
+      <c r="AF42" s="86" t="n"/>
+      <c r="AG42" s="86" t="n"/>
+      <c r="AH42" s="86" t="n"/>
+      <c r="AI42" s="86" t="n"/>
+      <c r="AJ42" s="86" t="n"/>
+      <c r="AK42" s="86" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="79">
+      <c r="A43" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B43" s="79">
+      <c r="B43" s="72">
         <f>B42+1</f>
         <v/>
       </c>
-      <c r="C43" s="79">
+      <c r="C43" s="72">
         <f>IF(K43="Vacant","Vac",IF(K43="Model","Model",IF(K43="Admin","Admin",IF(K43="Down","Down",IF(K43="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D43" s="79">
+      <c r="D43" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I43,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E43" s="79">
+      <c r="E43" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D43,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F43" s="79">
+      <c r="F43" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D43,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G43" s="79">
+      <c r="G43" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D43,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H43" s="79" t="inlineStr">
+      <c r="H43" s="72" t="inlineStr">
         <is>
           <t>800-3B</t>
         </is>
       </c>
-      <c r="I43" s="79" t="inlineStr">
+      <c r="I43" s="72" t="inlineStr">
         <is>
           <t>2x2B_C</t>
         </is>
       </c>
-      <c r="J43" s="87" t="n">
+      <c r="J43" s="80" t="n">
         <v>844</v>
       </c>
-      <c r="K43" s="79" t="inlineStr">
+      <c r="K43" s="72" t="inlineStr">
         <is>
           <t>Castillo, Jamie</t>
         </is>
       </c>
-      <c r="L43" s="88" t="n">
+      <c r="L43" s="81" t="n">
         <v>1599</v>
       </c>
-      <c r="M43" s="88">
+      <c r="M43" s="81">
         <f>Y43</f>
         <v/>
       </c>
-      <c r="N43" s="89" t="n">
+      <c r="N43" s="82" t="n">
         <v>46032</v>
       </c>
-      <c r="O43" s="89" t="n">
+      <c r="O43" s="82" t="n">
         <v>46032</v>
       </c>
-      <c r="P43" s="89" t="n">
+      <c r="P43" s="82" t="n">
         <v>46396</v>
       </c>
-      <c r="R43" s="88">
+      <c r="R43" s="81">
         <f>SUM(AB43:AI43)</f>
         <v/>
       </c>
-      <c r="S43" s="88">
+      <c r="S43" s="81">
         <f>AK43</f>
         <v/>
       </c>
-      <c r="T43" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="88" t="n">
+      <c r="T43" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="81" t="n">
         <v>1799</v>
       </c>
-      <c r="AB43" s="88" t="n">
+      <c r="AB43" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD43" s="88" t="n">
+      <c r="AD43" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE43" s="88" t="n">
+      <c r="AE43" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF43" s="88" t="n">
+      <c r="AF43" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG43" s="88" t="n">
+      <c r="AG43" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="79">
+      <c r="A44" s="83">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B44" s="79">
+      <c r="B44" s="83">
         <f>B43+1</f>
         <v/>
       </c>
-      <c r="C44" s="79">
+      <c r="C44" s="83">
         <f>IF(K44="Vacant","Vac",IF(K44="Model","Model",IF(K44="Admin","Admin",IF(K44="Down","Down",IF(K44="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D44" s="79">
+      <c r="D44" s="83">
         <f>INDEX($C$5:$C$8,MATCH(I44,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E44" s="79">
+      <c r="E44" s="83">
         <f>INDEX($E$5:$E$8,MATCH(D44,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F44" s="79">
+      <c r="F44" s="83">
         <f>INDEX($F$5:$F$8,MATCH(D44,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G44" s="79">
+      <c r="G44" s="83">
         <f>INDEX($G$5:$G$8,MATCH(D44,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H44" s="79" t="inlineStr">
+      <c r="H44" s="83" t="inlineStr">
         <is>
           <t>800-3C</t>
         </is>
       </c>
-      <c r="I44" s="79" t="inlineStr">
+      <c r="I44" s="83" t="inlineStr">
         <is>
           <t>2x2B_C</t>
         </is>
       </c>
-      <c r="J44" s="87" t="n">
+      <c r="J44" s="84" t="n">
         <v>972</v>
       </c>
-      <c r="K44" s="79" t="inlineStr">
+      <c r="K44" s="83" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L44" s="88" t="n">
+      <c r="L44" s="85" t="n">
         <v>1799</v>
       </c>
-      <c r="M44" s="88">
+      <c r="M44" s="85">
         <f>Y44</f>
         <v/>
       </c>
-      <c r="R44" s="88">
+      <c r="N44" s="86" t="n"/>
+      <c r="O44" s="86" t="n"/>
+      <c r="P44" s="86" t="n"/>
+      <c r="Q44" s="86" t="n"/>
+      <c r="R44" s="85">
         <f>SUM(AB44:AI44)</f>
         <v/>
       </c>
-      <c r="S44" s="88">
+      <c r="S44" s="85">
         <f>AK44</f>
         <v/>
       </c>
-      <c r="T44" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="88" t="n">
-        <v>0</v>
-      </c>
+      <c r="T44" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="86" t="n"/>
+      <c r="V44" s="86" t="n"/>
+      <c r="W44" s="86" t="n"/>
+      <c r="X44" s="86" t="n"/>
+      <c r="Y44" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="86" t="n"/>
+      <c r="AA44" s="86" t="n"/>
+      <c r="AB44" s="86" t="n"/>
+      <c r="AC44" s="86" t="n"/>
+      <c r="AD44" s="86" t="n"/>
+      <c r="AE44" s="86" t="n"/>
+      <c r="AF44" s="86" t="n"/>
+      <c r="AG44" s="86" t="n"/>
+      <c r="AH44" s="86" t="n"/>
+      <c r="AI44" s="86" t="n"/>
+      <c r="AJ44" s="86" t="n"/>
+      <c r="AK44" s="86" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="79">
+      <c r="A45" s="83">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B45" s="79">
+      <c r="B45" s="83">
         <f>B44+1</f>
         <v/>
       </c>
-      <c r="C45" s="79">
+      <c r="C45" s="83">
         <f>IF(K45="Vacant","Vac",IF(K45="Model","Model",IF(K45="Admin","Admin",IF(K45="Down","Down",IF(K45="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D45" s="79">
+      <c r="D45" s="83">
         <f>INDEX($C$5:$C$8,MATCH(I45,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E45" s="79">
+      <c r="E45" s="83">
         <f>INDEX($E$5:$E$8,MATCH(D45,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F45" s="79">
+      <c r="F45" s="83">
         <f>INDEX($F$5:$F$8,MATCH(D45,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G45" s="79">
+      <c r="G45" s="83">
         <f>INDEX($G$5:$G$8,MATCH(D45,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H45" s="79" t="inlineStr">
+      <c r="H45" s="83" t="inlineStr">
         <is>
           <t>800-3D</t>
         </is>
       </c>
-      <c r="I45" s="79" t="inlineStr">
+      <c r="I45" s="83" t="inlineStr">
         <is>
           <t>2x2B_C</t>
         </is>
       </c>
-      <c r="J45" s="87" t="n">
+      <c r="J45" s="84" t="n">
         <v>972</v>
       </c>
-      <c r="K45" s="79" t="inlineStr">
+      <c r="K45" s="83" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L45" s="88" t="n">
+      <c r="L45" s="85" t="n">
         <v>1799</v>
       </c>
-      <c r="M45" s="88">
+      <c r="M45" s="85">
         <f>Y45</f>
         <v/>
       </c>
-      <c r="R45" s="88">
+      <c r="N45" s="86" t="n"/>
+      <c r="O45" s="86" t="n"/>
+      <c r="P45" s="86" t="n"/>
+      <c r="Q45" s="86" t="n"/>
+      <c r="R45" s="85">
         <f>SUM(AB45:AI45)</f>
         <v/>
       </c>
-      <c r="S45" s="88">
+      <c r="S45" s="85">
         <f>AK45</f>
         <v/>
       </c>
-      <c r="T45" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="88" t="n">
-        <v>0</v>
-      </c>
+      <c r="T45" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="86" t="n"/>
+      <c r="V45" s="86" t="n"/>
+      <c r="W45" s="86" t="n"/>
+      <c r="X45" s="86" t="n"/>
+      <c r="Y45" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="86" t="n"/>
+      <c r="AA45" s="86" t="n"/>
+      <c r="AB45" s="86" t="n"/>
+      <c r="AC45" s="86" t="n"/>
+      <c r="AD45" s="86" t="n"/>
+      <c r="AE45" s="86" t="n"/>
+      <c r="AF45" s="86" t="n"/>
+      <c r="AG45" s="86" t="n"/>
+      <c r="AH45" s="86" t="n"/>
+      <c r="AI45" s="86" t="n"/>
+      <c r="AJ45" s="86" t="n"/>
+      <c r="AK45" s="86" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="79">
+      <c r="A46" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B46" s="79">
+      <c r="B46" s="72">
         <f>B45+1</f>
         <v/>
       </c>
-      <c r="C46" s="79">
+      <c r="C46" s="72">
         <f>IF(K46="Vacant","Vac",IF(K46="Model","Model",IF(K46="Admin","Admin",IF(K46="Down","Down",IF(K46="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D46" s="79">
+      <c r="D46" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I46,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E46" s="79">
+      <c r="E46" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D46,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F46" s="79">
+      <c r="F46" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D46,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G46" s="79">
+      <c r="G46" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D46,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H46" s="79" t="inlineStr">
+      <c r="H46" s="72" t="inlineStr">
         <is>
           <t>CL - 806-1</t>
         </is>
       </c>
-      <c r="I46" s="79" t="inlineStr">
+      <c r="I46" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J46" s="87" t="n">
+      <c r="J46" s="80" t="n">
         <v>810</v>
       </c>
-      <c r="K46" s="79" t="inlineStr">
+      <c r="K46" s="72" t="inlineStr">
         <is>
           <t>Collins, Nancy</t>
         </is>
       </c>
-      <c r="L46" s="88" t="n">
+      <c r="L46" s="81" t="n">
         <v>1379</v>
       </c>
-      <c r="M46" s="88">
+      <c r="M46" s="81">
         <f>Y46</f>
         <v/>
       </c>
-      <c r="N46" s="89" t="n">
+      <c r="N46" s="82" t="n">
         <v>44075</v>
       </c>
-      <c r="O46" s="89" t="n">
+      <c r="O46" s="82" t="n">
         <v>45901</v>
       </c>
-      <c r="P46" s="89" t="n">
+      <c r="P46" s="82" t="n">
         <v>46265</v>
       </c>
-      <c r="R46" s="88">
+      <c r="R46" s="81">
         <f>SUM(AB46:AI46)</f>
         <v/>
       </c>
-      <c r="S46" s="88">
+      <c r="S46" s="81">
         <f>AK46</f>
         <v/>
       </c>
-      <c r="T46" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="88" t="n">
+      <c r="T46" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="81" t="n">
         <v>1249</v>
       </c>
-      <c r="AB46" s="88" t="n">
+      <c r="AB46" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD46" s="88" t="n">
+      <c r="AD46" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE46" s="88" t="n">
+      <c r="AE46" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF46" s="88" t="n">
+      <c r="AF46" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG46" s="88" t="n">
+      <c r="AG46" s="81" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="79">
+      <c r="A47" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B47" s="79">
+      <c r="B47" s="72">
         <f>B46+1</f>
         <v/>
       </c>
-      <c r="C47" s="79">
+      <c r="C47" s="72">
         <f>IF(K47="Vacant","Vac",IF(K47="Model","Model",IF(K47="Admin","Admin",IF(K47="Down","Down",IF(K47="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D47" s="79">
+      <c r="D47" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I47,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E47" s="79">
+      <c r="E47" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D47,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F47" s="79">
+      <c r="F47" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D47,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G47" s="79">
+      <c r="G47" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D47,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H47" s="79" t="inlineStr">
+      <c r="H47" s="72" t="inlineStr">
         <is>
           <t>CL - 806-2</t>
         </is>
       </c>
-      <c r="I47" s="79" t="inlineStr">
+      <c r="I47" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J47" s="87" t="n">
+      <c r="J47" s="80" t="n">
         <v>935</v>
       </c>
-      <c r="K47" s="79" t="inlineStr">
+      <c r="K47" s="72" t="inlineStr">
         <is>
           <t>Humphrey, Alyson</t>
         </is>
       </c>
-      <c r="L47" s="88" t="n">
+      <c r="L47" s="81" t="n">
         <v>1379</v>
       </c>
-      <c r="M47" s="88">
+      <c r="M47" s="81">
         <f>Y47</f>
         <v/>
       </c>
-      <c r="N47" s="89" t="n">
+      <c r="N47" s="82" t="n">
         <v>45551</v>
       </c>
-      <c r="O47" s="89" t="n">
+      <c r="O47" s="82" t="n">
         <v>45916</v>
       </c>
-      <c r="P47" s="89" t="n">
+      <c r="P47" s="82" t="n">
         <v>46280</v>
       </c>
-      <c r="R47" s="88">
+      <c r="R47" s="81">
         <f>SUM(AB47:AI47)</f>
         <v/>
       </c>
-      <c r="S47" s="88">
+      <c r="S47" s="81">
         <f>AK47</f>
         <v/>
       </c>
-      <c r="T47" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="88" t="n">
+      <c r="T47" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="81" t="n">
         <v>1249</v>
       </c>
-      <c r="AB47" s="88" t="n">
+      <c r="AB47" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD47" s="88" t="n">
+      <c r="AD47" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE47" s="88" t="n">
+      <c r="AE47" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF47" s="88" t="n">
+      <c r="AF47" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG47" s="88" t="n">
+      <c r="AG47" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="79">
+      <c r="A48" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B48" s="79">
+      <c r="B48" s="72">
         <f>B47+1</f>
         <v/>
       </c>
-      <c r="C48" s="79">
+      <c r="C48" s="72">
         <f>IF(K48="Vacant","Vac",IF(K48="Model","Model",IF(K48="Admin","Admin",IF(K48="Down","Down",IF(K48="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D48" s="79">
+      <c r="D48" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I48,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E48" s="79">
+      <c r="E48" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D48,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F48" s="79">
+      <c r="F48" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D48,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G48" s="79">
+      <c r="G48" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D48,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H48" s="79" t="inlineStr">
+      <c r="H48" s="72" t="inlineStr">
         <is>
           <t>CL - 806-3</t>
         </is>
       </c>
-      <c r="I48" s="79" t="inlineStr">
+      <c r="I48" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J48" s="87" t="n">
+      <c r="J48" s="80" t="n">
         <v>820</v>
       </c>
-      <c r="K48" s="79" t="inlineStr">
+      <c r="K48" s="72" t="inlineStr">
         <is>
           <t>Waugh, Christopher</t>
         </is>
       </c>
-      <c r="L48" s="88" t="n">
+      <c r="L48" s="81" t="n">
         <v>1404</v>
       </c>
-      <c r="M48" s="88">
+      <c r="M48" s="81">
         <f>Y48</f>
         <v/>
       </c>
-      <c r="N48" s="89" t="n">
+      <c r="N48" s="82" t="n">
         <v>45121</v>
       </c>
-      <c r="O48" s="89" t="n">
+      <c r="O48" s="82" t="n">
         <v>45879</v>
       </c>
-      <c r="P48" s="89" t="n">
+      <c r="P48" s="82" t="n">
         <v>46243</v>
       </c>
-      <c r="R48" s="88">
+      <c r="R48" s="81">
         <f>SUM(AB48:AI48)</f>
         <v/>
       </c>
-      <c r="S48" s="88">
+      <c r="S48" s="81">
         <f>AK48</f>
         <v/>
       </c>
-      <c r="T48" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="88" t="n">
+      <c r="T48" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="81" t="n">
         <v>1245</v>
       </c>
-      <c r="AB48" s="88" t="n">
+      <c r="AB48" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD48" s="88" t="n">
+      <c r="AD48" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE48" s="88" t="n">
+      <c r="AE48" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF48" s="88" t="n">
+      <c r="AF48" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG48" s="88" t="n">
+      <c r="AG48" s="81" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="79">
+      <c r="A49" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B49" s="79">
+      <c r="B49" s="72">
         <f>B48+1</f>
         <v/>
       </c>
-      <c r="C49" s="79">
+      <c r="C49" s="72">
         <f>IF(K49="Vacant","Vac",IF(K49="Model","Model",IF(K49="Admin","Admin",IF(K49="Down","Down",IF(K49="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D49" s="79">
+      <c r="D49" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I49,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E49" s="79">
+      <c r="E49" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D49,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F49" s="79">
+      <c r="F49" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D49,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G49" s="79">
+      <c r="G49" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D49,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H49" s="79" t="inlineStr">
+      <c r="H49" s="72" t="inlineStr">
         <is>
           <t>CL - 806-4</t>
         </is>
       </c>
-      <c r="I49" s="79" t="inlineStr">
+      <c r="I49" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J49" s="87" t="n">
+      <c r="J49" s="80" t="n">
         <v>935</v>
       </c>
-      <c r="K49" s="79" t="inlineStr">
+      <c r="K49" s="72" t="inlineStr">
         <is>
           <t>McClarty, Nicole</t>
         </is>
       </c>
-      <c r="L49" s="88" t="n">
+      <c r="L49" s="81" t="n">
         <v>1404</v>
       </c>
-      <c r="M49" s="88">
+      <c r="M49" s="81">
         <f>Y49</f>
         <v/>
       </c>
-      <c r="N49" s="89" t="n">
+      <c r="N49" s="82" t="n">
         <v>44241</v>
       </c>
-      <c r="O49" s="89" t="n">
+      <c r="O49" s="82" t="n">
         <v>45805</v>
       </c>
-      <c r="P49" s="89" t="n">
+      <c r="P49" s="82" t="n">
         <v>46261</v>
       </c>
-      <c r="R49" s="88">
+      <c r="R49" s="81">
         <f>SUM(AB49:AI49)</f>
         <v/>
       </c>
-      <c r="S49" s="88">
+      <c r="S49" s="81">
         <f>AK49</f>
         <v/>
       </c>
-      <c r="T49" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="88" t="n">
+      <c r="T49" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="81" t="n">
         <v>1215</v>
       </c>
-      <c r="AB49" s="88" t="n">
+      <c r="AB49" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AC49" s="88" t="n">
+      <c r="AC49" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="AD49" s="88" t="n">
+      <c r="AD49" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE49" s="88" t="n">
+      <c r="AE49" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF49" s="88" t="n">
+      <c r="AF49" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG49" s="88" t="n">
+      <c r="AG49" s="81" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="79">
+      <c r="A50" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B50" s="79">
+      <c r="B50" s="72">
         <f>B49+1</f>
         <v/>
       </c>
-      <c r="C50" s="79">
+      <c r="C50" s="72">
         <f>IF(K50="Vacant","Vac",IF(K50="Model","Model",IF(K50="Admin","Admin",IF(K50="Down","Down",IF(K50="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D50" s="79">
+      <c r="D50" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I50,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E50" s="79">
+      <c r="E50" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D50,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F50" s="79">
+      <c r="F50" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D50,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G50" s="79">
+      <c r="G50" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D50,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H50" s="79" t="inlineStr">
+      <c r="H50" s="72" t="inlineStr">
         <is>
           <t>CL - 806-5</t>
         </is>
       </c>
-      <c r="I50" s="79" t="inlineStr">
+      <c r="I50" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J50" s="87" t="n">
+      <c r="J50" s="80" t="n">
         <v>1066</v>
       </c>
-      <c r="K50" s="79" t="inlineStr">
+      <c r="K50" s="72" t="inlineStr">
         <is>
           <t>Belcher, Keira</t>
         </is>
       </c>
-      <c r="L50" s="88" t="n">
+      <c r="L50" s="81" t="n">
         <v>1349</v>
       </c>
-      <c r="M50" s="88">
+      <c r="M50" s="81">
         <f>Y50</f>
         <v/>
       </c>
-      <c r="N50" s="89" t="n">
+      <c r="N50" s="82" t="n">
         <v>45495</v>
       </c>
-      <c r="O50" s="89" t="n">
+      <c r="O50" s="82" t="n">
         <v>45860</v>
       </c>
-      <c r="P50" s="89" t="n">
+      <c r="P50" s="82" t="n">
         <v>46224</v>
       </c>
-      <c r="R50" s="88">
+      <c r="R50" s="81">
         <f>SUM(AB50:AI50)</f>
         <v/>
       </c>
-      <c r="S50" s="88">
+      <c r="S50" s="81">
         <f>AK50</f>
         <v/>
       </c>
-      <c r="T50" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="88" t="n">
+      <c r="T50" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="81" t="n">
         <v>1345</v>
       </c>
-      <c r="AB50" s="88" t="n">
+      <c r="AB50" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AC50" s="88" t="n">
+      <c r="AC50" s="81" t="n">
         <v>35</v>
       </c>
-      <c r="AD50" s="88" t="n">
+      <c r="AD50" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE50" s="88" t="n">
+      <c r="AE50" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF50" s="88" t="n">
+      <c r="AF50" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG50" s="88" t="n">
+      <c r="AG50" s="81" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="79">
+      <c r="A51" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B51" s="79">
+      <c r="B51" s="72">
         <f>B50+1</f>
         <v/>
       </c>
-      <c r="C51" s="79">
+      <c r="C51" s="72">
         <f>IF(K51="Vacant","Vac",IF(K51="Model","Model",IF(K51="Admin","Admin",IF(K51="Down","Down",IF(K51="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D51" s="79">
+      <c r="D51" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I51,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E51" s="79">
+      <c r="E51" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D51,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F51" s="79">
+      <c r="F51" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D51,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G51" s="79">
+      <c r="G51" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D51,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H51" s="79" t="inlineStr">
+      <c r="H51" s="72" t="inlineStr">
         <is>
           <t>CL - 806-6</t>
         </is>
       </c>
-      <c r="I51" s="79" t="inlineStr">
+      <c r="I51" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J51" s="87" t="n">
+      <c r="J51" s="80" t="n">
         <v>840</v>
       </c>
-      <c r="K51" s="79" t="inlineStr">
+      <c r="K51" s="72" t="inlineStr">
         <is>
           <t>Harrison, Davis</t>
         </is>
       </c>
-      <c r="L51" s="88" t="n">
+      <c r="L51" s="81" t="n">
         <v>1374</v>
       </c>
-      <c r="M51" s="88">
+      <c r="M51" s="81">
         <f>Y51</f>
         <v/>
       </c>
-      <c r="N51" s="89" t="n">
+      <c r="N51" s="82" t="n">
         <v>45709</v>
       </c>
-      <c r="O51" s="89" t="n">
+      <c r="O51" s="82" t="n">
         <v>46074</v>
       </c>
-      <c r="P51" s="89" t="n">
+      <c r="P51" s="82" t="n">
         <v>46438</v>
       </c>
-      <c r="R51" s="88">
+      <c r="R51" s="81">
         <f>SUM(AB51:AI51)</f>
         <v/>
       </c>
-      <c r="S51" s="88">
+      <c r="S51" s="81">
         <f>AK51</f>
         <v/>
       </c>
-      <c r="T51" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="88" t="n">
+      <c r="T51" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="81" t="n">
         <v>1244</v>
       </c>
-      <c r="AB51" s="88" t="n">
+      <c r="AB51" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD51" s="88" t="n">
+      <c r="AD51" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE51" s="88" t="n">
+      <c r="AE51" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF51" s="88" t="n">
+      <c r="AF51" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG51" s="88" t="n">
+      <c r="AG51" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="79">
+      <c r="A52" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B52" s="79">
+      <c r="B52" s="72">
         <f>B51+1</f>
         <v/>
       </c>
-      <c r="C52" s="79">
+      <c r="C52" s="72">
         <f>IF(K52="Vacant","Vac",IF(K52="Model","Model",IF(K52="Admin","Admin",IF(K52="Down","Down",IF(K52="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D52" s="79">
+      <c r="D52" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I52,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E52" s="79">
+      <c r="E52" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D52,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F52" s="79">
+      <c r="F52" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D52,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G52" s="79">
+      <c r="G52" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D52,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H52" s="79" t="inlineStr">
+      <c r="H52" s="72" t="inlineStr">
         <is>
           <t>CL - 806-7</t>
         </is>
       </c>
-      <c r="I52" s="79" t="inlineStr">
+      <c r="I52" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J52" s="87" t="n">
+      <c r="J52" s="80" t="n">
         <v>965</v>
       </c>
-      <c r="K52" s="79" t="inlineStr">
+      <c r="K52" s="72" t="inlineStr">
         <is>
           <t>Steele, Christopher</t>
         </is>
       </c>
-      <c r="L52" s="88" t="n">
+      <c r="L52" s="81" t="n">
         <v>1374</v>
       </c>
-      <c r="M52" s="88">
+      <c r="M52" s="81">
         <f>Y52</f>
         <v/>
       </c>
-      <c r="N52" s="89" t="n">
+      <c r="N52" s="82" t="n">
         <v>44281</v>
       </c>
-      <c r="O52" s="89" t="n">
+      <c r="O52" s="82" t="n">
         <v>45926</v>
       </c>
-      <c r="P52" s="89" t="n">
+      <c r="P52" s="82" t="n">
         <v>46290</v>
       </c>
-      <c r="R52" s="88">
+      <c r="R52" s="81">
         <f>SUM(AB52:AI52)</f>
         <v/>
       </c>
-      <c r="S52" s="88">
+      <c r="S52" s="81">
         <f>AK52</f>
         <v/>
       </c>
-      <c r="T52" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="88" t="n">
+      <c r="T52" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="81" t="n">
         <v>1320</v>
       </c>
-      <c r="AB52" s="88" t="n">
+      <c r="AB52" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AC52" s="88" t="n">
+      <c r="AC52" s="81" t="n">
         <v>35</v>
       </c>
-      <c r="AD52" s="88" t="n">
+      <c r="AD52" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE52" s="88" t="n">
+      <c r="AE52" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF52" s="88" t="n">
+      <c r="AF52" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG52" s="88" t="n">
+      <c r="AG52" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="79">
+      <c r="A53" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B53" s="79">
+      <c r="B53" s="72">
         <f>B52+1</f>
         <v/>
       </c>
-      <c r="C53" s="79">
+      <c r="C53" s="72">
         <f>IF(K53="Vacant","Vac",IF(K53="Model","Model",IF(K53="Admin","Admin",IF(K53="Down","Down",IF(K53="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D53" s="79">
+      <c r="D53" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I53,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E53" s="79">
+      <c r="E53" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D53,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F53" s="79">
+      <c r="F53" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D53,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G53" s="79">
+      <c r="G53" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D53,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H53" s="79" t="inlineStr">
+      <c r="H53" s="72" t="inlineStr">
         <is>
           <t>CL - 806-8</t>
         </is>
       </c>
-      <c r="I53" s="79" t="inlineStr">
+      <c r="I53" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J53" s="87" t="n">
+      <c r="J53" s="80" t="n">
         <v>475</v>
       </c>
-      <c r="K53" s="79" t="inlineStr">
+      <c r="K53" s="72" t="inlineStr">
         <is>
           <t>Rodriguez, Larissa</t>
         </is>
       </c>
-      <c r="L53" s="88" t="n">
+      <c r="L53" s="81" t="n">
         <v>1049</v>
       </c>
-      <c r="M53" s="88">
+      <c r="M53" s="81">
         <f>Y53</f>
         <v/>
       </c>
-      <c r="N53" s="89" t="n">
+      <c r="N53" s="82" t="n">
         <v>46042</v>
       </c>
-      <c r="O53" s="89" t="n">
+      <c r="O53" s="82" t="n">
         <v>46042</v>
       </c>
-      <c r="P53" s="89" t="n">
+      <c r="P53" s="82" t="n">
         <v>46496</v>
       </c>
-      <c r="R53" s="88">
+      <c r="R53" s="81">
         <f>SUM(AB53:AI53)</f>
         <v/>
       </c>
-      <c r="S53" s="88">
+      <c r="S53" s="81">
         <f>AK53</f>
         <v/>
       </c>
-      <c r="T53" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="88" t="n">
+      <c r="T53" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="81" t="n">
         <v>1049</v>
       </c>
-      <c r="AB53" s="88" t="n">
+      <c r="AB53" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD53" s="88" t="n">
+      <c r="AD53" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE53" s="88" t="n">
+      <c r="AE53" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF53" s="88" t="n">
+      <c r="AF53" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG53" s="88" t="n">
+      <c r="AG53" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="79">
+      <c r="A54" s="83">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B54" s="79">
+      <c r="B54" s="83">
         <f>B53+1</f>
         <v/>
       </c>
-      <c r="C54" s="79">
+      <c r="C54" s="83">
         <f>IF(K54="Vacant","Vac",IF(K54="Model","Model",IF(K54="Admin","Admin",IF(K54="Down","Down",IF(K54="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D54" s="79">
+      <c r="D54" s="83">
         <f>INDEX($C$5:$C$8,MATCH(I54,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E54" s="79">
+      <c r="E54" s="83">
         <f>INDEX($E$5:$E$8,MATCH(D54,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F54" s="79">
+      <c r="F54" s="83">
         <f>INDEX($F$5:$F$8,MATCH(D54,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G54" s="79">
+      <c r="G54" s="83">
         <f>INDEX($G$5:$G$8,MATCH(D54,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H54" s="79" t="inlineStr">
+      <c r="H54" s="83" t="inlineStr">
         <is>
           <t>CL - 806-9</t>
         </is>
       </c>
-      <c r="I54" s="79" t="inlineStr">
+      <c r="I54" s="83" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J54" s="87" t="n">
+      <c r="J54" s="84" t="n">
         <v>723</v>
       </c>
-      <c r="K54" s="79" t="inlineStr">
+      <c r="K54" s="83" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L54" s="88" t="n">
+      <c r="L54" s="85" t="n">
         <v>1355</v>
       </c>
-      <c r="M54" s="88">
+      <c r="M54" s="85">
         <f>Y54</f>
         <v/>
       </c>
-      <c r="R54" s="88">
+      <c r="N54" s="86" t="n"/>
+      <c r="O54" s="86" t="n"/>
+      <c r="P54" s="86" t="n"/>
+      <c r="Q54" s="86" t="n"/>
+      <c r="R54" s="85">
         <f>SUM(AB54:AI54)</f>
         <v/>
       </c>
-      <c r="S54" s="88">
+      <c r="S54" s="85">
         <f>AK54</f>
         <v/>
       </c>
-      <c r="T54" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="88" t="n">
-        <v>0</v>
-      </c>
+      <c r="T54" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="86" t="n"/>
+      <c r="V54" s="86" t="n"/>
+      <c r="W54" s="86" t="n"/>
+      <c r="X54" s="86" t="n"/>
+      <c r="Y54" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="86" t="n"/>
+      <c r="AA54" s="86" t="n"/>
+      <c r="AB54" s="86" t="n"/>
+      <c r="AC54" s="86" t="n"/>
+      <c r="AD54" s="86" t="n"/>
+      <c r="AE54" s="86" t="n"/>
+      <c r="AF54" s="86" t="n"/>
+      <c r="AG54" s="86" t="n"/>
+      <c r="AH54" s="86" t="n"/>
+      <c r="AI54" s="86" t="n"/>
+      <c r="AJ54" s="86" t="n"/>
+      <c r="AK54" s="86" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="79">
+      <c r="A55" s="83">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B55" s="79">
+      <c r="B55" s="83">
         <f>B54+1</f>
         <v/>
       </c>
-      <c r="C55" s="79">
+      <c r="C55" s="83">
         <f>IF(K55="Vacant","Vac",IF(K55="Model","Model",IF(K55="Admin","Admin",IF(K55="Down","Down",IF(K55="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D55" s="79">
+      <c r="D55" s="83">
         <f>INDEX($C$5:$C$8,MATCH(I55,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E55" s="79">
+      <c r="E55" s="83">
         <f>INDEX($E$5:$E$8,MATCH(D55,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F55" s="79">
+      <c r="F55" s="83">
         <f>INDEX($F$5:$F$8,MATCH(D55,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G55" s="79">
+      <c r="G55" s="83">
         <f>INDEX($G$5:$G$8,MATCH(D55,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H55" s="79" t="inlineStr">
+      <c r="H55" s="83" t="inlineStr">
         <is>
           <t>CL - 806-10</t>
         </is>
       </c>
-      <c r="I55" s="79" t="inlineStr">
+      <c r="I55" s="83" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J55" s="87" t="n">
+      <c r="J55" s="84" t="n">
         <v>744</v>
       </c>
-      <c r="K55" s="79" t="inlineStr">
+      <c r="K55" s="83" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L55" s="88" t="n">
+      <c r="L55" s="85" t="n">
         <v>1355</v>
       </c>
-      <c r="M55" s="88">
+      <c r="M55" s="85">
         <f>Y55</f>
         <v/>
       </c>
-      <c r="R55" s="88">
+      <c r="N55" s="86" t="n"/>
+      <c r="O55" s="86" t="n"/>
+      <c r="P55" s="86" t="n"/>
+      <c r="Q55" s="86" t="n"/>
+      <c r="R55" s="85">
         <f>SUM(AB55:AI55)</f>
         <v/>
       </c>
-      <c r="S55" s="88">
+      <c r="S55" s="85">
         <f>AK55</f>
         <v/>
       </c>
-      <c r="T55" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" s="88" t="n">
-        <v>0</v>
-      </c>
+      <c r="T55" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="86" t="n"/>
+      <c r="V55" s="86" t="n"/>
+      <c r="W55" s="86" t="n"/>
+      <c r="X55" s="86" t="n"/>
+      <c r="Y55" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="86" t="n"/>
+      <c r="AA55" s="86" t="n"/>
+      <c r="AB55" s="86" t="n"/>
+      <c r="AC55" s="86" t="n"/>
+      <c r="AD55" s="86" t="n"/>
+      <c r="AE55" s="86" t="n"/>
+      <c r="AF55" s="86" t="n"/>
+      <c r="AG55" s="86" t="n"/>
+      <c r="AH55" s="86" t="n"/>
+      <c r="AI55" s="86" t="n"/>
+      <c r="AJ55" s="86" t="n"/>
+      <c r="AK55" s="86" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="79">
+      <c r="A56" s="83">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B56" s="79">
+      <c r="B56" s="83">
         <f>B55+1</f>
         <v/>
       </c>
-      <c r="C56" s="79">
+      <c r="C56" s="83">
         <f>IF(K56="Vacant","Vac",IF(K56="Model","Model",IF(K56="Admin","Admin",IF(K56="Down","Down",IF(K56="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D56" s="79">
+      <c r="D56" s="83">
         <f>INDEX($C$5:$C$8,MATCH(I56,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E56" s="79">
+      <c r="E56" s="83">
         <f>INDEX($E$5:$E$8,MATCH(D56,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F56" s="79">
+      <c r="F56" s="83">
         <f>INDEX($F$5:$F$8,MATCH(D56,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G56" s="79">
+      <c r="G56" s="83">
         <f>INDEX($G$5:$G$8,MATCH(D56,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H56" s="79" t="inlineStr">
+      <c r="H56" s="83" t="inlineStr">
         <is>
           <t>CL - 806-11</t>
         </is>
       </c>
-      <c r="I56" s="79" t="inlineStr">
+      <c r="I56" s="83" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J56" s="87" t="n">
+      <c r="J56" s="84" t="n">
         <v>720</v>
       </c>
-      <c r="K56" s="79" t="inlineStr">
+      <c r="K56" s="83" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L56" s="88" t="n">
+      <c r="L56" s="85" t="n">
         <v>990</v>
       </c>
-      <c r="M56" s="88">
+      <c r="M56" s="85">
         <f>Y56</f>
         <v/>
       </c>
-      <c r="R56" s="88">
+      <c r="N56" s="86" t="n"/>
+      <c r="O56" s="86" t="n"/>
+      <c r="P56" s="86" t="n"/>
+      <c r="Q56" s="86" t="n"/>
+      <c r="R56" s="85">
         <f>SUM(AB56:AI56)</f>
         <v/>
       </c>
-      <c r="S56" s="88">
+      <c r="S56" s="85">
         <f>AK56</f>
         <v/>
       </c>
-      <c r="T56" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" s="88" t="n">
-        <v>0</v>
-      </c>
+      <c r="T56" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="86" t="n"/>
+      <c r="V56" s="86" t="n"/>
+      <c r="W56" s="86" t="n"/>
+      <c r="X56" s="86" t="n"/>
+      <c r="Y56" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="86" t="n"/>
+      <c r="AA56" s="86" t="n"/>
+      <c r="AB56" s="86" t="n"/>
+      <c r="AC56" s="86" t="n"/>
+      <c r="AD56" s="86" t="n"/>
+      <c r="AE56" s="86" t="n"/>
+      <c r="AF56" s="86" t="n"/>
+      <c r="AG56" s="86" t="n"/>
+      <c r="AH56" s="86" t="n"/>
+      <c r="AI56" s="86" t="n"/>
+      <c r="AJ56" s="86" t="n"/>
+      <c r="AK56" s="86" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="79">
+      <c r="A57" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B57" s="79">
+      <c r="B57" s="72">
         <f>B56+1</f>
         <v/>
       </c>
-      <c r="C57" s="79">
+      <c r="C57" s="72">
         <f>IF(K57="Vacant","Vac",IF(K57="Model","Model",IF(K57="Admin","Admin",IF(K57="Down","Down",IF(K57="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D57" s="79">
+      <c r="D57" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I57,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E57" s="79">
+      <c r="E57" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D57,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F57" s="79">
+      <c r="F57" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D57,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G57" s="79">
+      <c r="G57" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D57,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H57" s="79" t="inlineStr">
+      <c r="H57" s="72" t="inlineStr">
         <is>
           <t>CL - 806-12</t>
         </is>
       </c>
-      <c r="I57" s="79" t="inlineStr">
+      <c r="I57" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J57" s="87" t="n">
+      <c r="J57" s="80" t="n">
         <v>656</v>
       </c>
-      <c r="K57" s="79" t="inlineStr">
+      <c r="K57" s="72" t="inlineStr">
         <is>
           <t>Montgomery-Lewis, Jaylynne</t>
         </is>
       </c>
-      <c r="L57" s="88" t="n">
+      <c r="L57" s="81" t="n">
         <v>1139</v>
       </c>
-      <c r="M57" s="88">
+      <c r="M57" s="81">
         <f>Y57</f>
         <v/>
       </c>
-      <c r="N57" s="89" t="n">
+      <c r="N57" s="82" t="n">
         <v>45863</v>
       </c>
-      <c r="O57" s="89" t="n">
+      <c r="O57" s="82" t="n">
         <v>45863</v>
       </c>
-      <c r="P57" s="89" t="n">
+      <c r="P57" s="82" t="n">
         <v>46227</v>
       </c>
-      <c r="R57" s="88">
+      <c r="R57" s="81">
         <f>SUM(AB57:AI57)</f>
         <v/>
       </c>
-      <c r="S57" s="88">
+      <c r="S57" s="81">
         <f>AK57</f>
         <v/>
       </c>
-      <c r="T57" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="88" t="n">
+      <c r="T57" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="81" t="n">
         <v>1139</v>
       </c>
-      <c r="AB57" s="88" t="n">
+      <c r="AB57" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AD57" s="88" t="n">
+      <c r="AD57" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE57" s="88" t="n">
+      <c r="AE57" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF57" s="88" t="n">
+      <c r="AF57" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG57" s="88" t="n">
+      <c r="AG57" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="79">
+      <c r="A58" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B58" s="79">
+      <c r="B58" s="72">
         <f>B57+1</f>
         <v/>
       </c>
-      <c r="C58" s="79">
+      <c r="C58" s="72">
         <f>IF(K58="Vacant","Vac",IF(K58="Model","Model",IF(K58="Admin","Admin",IF(K58="Down","Down",IF(K58="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D58" s="79">
+      <c r="D58" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I58,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E58" s="79">
+      <c r="E58" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D58,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F58" s="79">
+      <c r="F58" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D58,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G58" s="79">
+      <c r="G58" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D58,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H58" s="79" t="inlineStr">
+      <c r="H58" s="72" t="inlineStr">
         <is>
           <t>CL - 806-14</t>
         </is>
       </c>
-      <c r="I58" s="79" t="inlineStr">
+      <c r="I58" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J58" s="87" t="n">
+      <c r="J58" s="80" t="n">
         <v>476</v>
       </c>
-      <c r="K58" s="79" t="inlineStr">
+      <c r="K58" s="72" t="inlineStr">
         <is>
           <t>Von Hassell, Damontay</t>
         </is>
       </c>
-      <c r="L58" s="88" t="n">
+      <c r="L58" s="81" t="n">
         <v>1049</v>
       </c>
-      <c r="M58" s="88">
+      <c r="M58" s="81">
         <f>Y58</f>
         <v/>
       </c>
-      <c r="N58" s="89" t="n">
+      <c r="N58" s="82" t="n">
         <v>45831</v>
       </c>
-      <c r="O58" s="89" t="n">
+      <c r="O58" s="82" t="n">
         <v>45831</v>
       </c>
-      <c r="P58" s="89" t="n">
+      <c r="P58" s="82" t="n">
         <v>46195</v>
       </c>
-      <c r="R58" s="88">
+      <c r="R58" s="81">
         <f>SUM(AB58:AI58)</f>
         <v/>
       </c>
-      <c r="S58" s="88">
+      <c r="S58" s="81">
         <f>AK58</f>
         <v/>
       </c>
-      <c r="T58" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="88" t="n">
+      <c r="T58" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="81" t="n">
         <v>1099</v>
       </c>
-      <c r="AB58" s="88" t="n">
+      <c r="AB58" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AD58" s="88" t="n">
+      <c r="AD58" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE58" s="88" t="n">
+      <c r="AE58" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF58" s="88" t="n">
+      <c r="AF58" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG58" s="88" t="n">
+      <c r="AG58" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="79">
+      <c r="A59" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B59" s="79">
+      <c r="B59" s="72">
         <f>B58+1</f>
         <v/>
       </c>
-      <c r="C59" s="79">
+      <c r="C59" s="72">
         <f>IF(K59="Vacant","Vac",IF(K59="Model","Model",IF(K59="Admin","Admin",IF(K59="Down","Down",IF(K59="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D59" s="79">
+      <c r="D59" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I59,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E59" s="79">
+      <c r="E59" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D59,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F59" s="79">
+      <c r="F59" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D59,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G59" s="79">
+      <c r="G59" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D59,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H59" s="79" t="inlineStr">
+      <c r="H59" s="72" t="inlineStr">
         <is>
           <t>CL - 806-15</t>
         </is>
       </c>
-      <c r="I59" s="79" t="inlineStr">
+      <c r="I59" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J59" s="87" t="n">
+      <c r="J59" s="80" t="n">
         <v>723</v>
       </c>
-      <c r="K59" s="79" t="inlineStr">
+      <c r="K59" s="72" t="inlineStr">
         <is>
           <t>Sorrells, Kashon</t>
         </is>
       </c>
-      <c r="L59" s="88" t="n">
+      <c r="L59" s="81" t="n">
         <v>1164</v>
       </c>
-      <c r="M59" s="88">
+      <c r="M59" s="81">
         <f>Y59</f>
         <v/>
       </c>
-      <c r="N59" s="89" t="n">
+      <c r="N59" s="82" t="n">
         <v>44250</v>
       </c>
-      <c r="O59" s="89" t="n">
+      <c r="O59" s="82" t="n">
         <v>46113</v>
       </c>
-      <c r="R59" s="88">
+      <c r="R59" s="81">
         <f>SUM(AB59:AI59)</f>
         <v/>
       </c>
-      <c r="S59" s="88">
+      <c r="S59" s="81">
         <f>AK59</f>
         <v/>
       </c>
-      <c r="T59" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="88" t="n">
+      <c r="T59" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="81" t="n">
         <v>990</v>
       </c>
-      <c r="AB59" s="88" t="n">
+      <c r="AB59" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD59" s="88" t="n">
+      <c r="AD59" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE59" s="88" t="n">
+      <c r="AE59" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF59" s="88" t="n">
+      <c r="AF59" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG59" s="88" t="n">
+      <c r="AG59" s="81" t="n">
         <v>65</v>
       </c>
-      <c r="AH59" s="88" t="n">
+      <c r="AH59" s="81" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="79">
+      <c r="A60" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B60" s="79">
+      <c r="B60" s="72">
         <f>B59+1</f>
         <v/>
       </c>
-      <c r="C60" s="79">
+      <c r="C60" s="72">
         <f>IF(K60="Vacant","Vac",IF(K60="Model","Model",IF(K60="Admin","Admin",IF(K60="Down","Down",IF(K60="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D60" s="79">
+      <c r="D60" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I60,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E60" s="79">
+      <c r="E60" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D60,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F60" s="79">
+      <c r="F60" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D60,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G60" s="79">
+      <c r="G60" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D60,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H60" s="79" t="inlineStr">
+      <c r="H60" s="72" t="inlineStr">
         <is>
           <t>CL - 806-16</t>
         </is>
       </c>
-      <c r="I60" s="79" t="inlineStr">
+      <c r="I60" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J60" s="87" t="n">
+      <c r="J60" s="80" t="n">
         <v>516</v>
       </c>
-      <c r="K60" s="79" t="inlineStr">
+      <c r="K60" s="72" t="inlineStr">
         <is>
           <t>Pitvorec, Jeremy</t>
         </is>
       </c>
-      <c r="L60" s="88" t="n">
+      <c r="L60" s="81" t="n">
         <v>1149</v>
       </c>
-      <c r="M60" s="88">
+      <c r="M60" s="81">
         <f>Y60</f>
         <v/>
       </c>
-      <c r="N60" s="89" t="n">
+      <c r="N60" s="82" t="n">
         <v>44621</v>
       </c>
-      <c r="O60" s="89" t="n">
+      <c r="O60" s="82" t="n">
         <v>46082</v>
       </c>
-      <c r="P60" s="89" t="n">
+      <c r="P60" s="82" t="n">
         <v>46538</v>
       </c>
-      <c r="R60" s="88">
+      <c r="R60" s="81">
         <f>SUM(AB60:AI60)</f>
         <v/>
       </c>
-      <c r="S60" s="88">
+      <c r="S60" s="81">
         <f>AK60</f>
         <v/>
       </c>
-      <c r="T60" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="88" t="n">
+      <c r="T60" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="81" t="n">
         <v>1125</v>
       </c>
-      <c r="AB60" s="88" t="n">
+      <c r="AB60" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD60" s="88" t="n">
+      <c r="AD60" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE60" s="88" t="n">
+      <c r="AE60" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF60" s="88" t="n">
+      <c r="AF60" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG60" s="88" t="n">
+      <c r="AG60" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="79">
+      <c r="A61" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B61" s="79">
+      <c r="B61" s="72">
         <f>B60+1</f>
         <v/>
       </c>
-      <c r="C61" s="79">
+      <c r="C61" s="72">
         <f>IF(K61="Vacant","Vac",IF(K61="Model","Model",IF(K61="Admin","Admin",IF(K61="Down","Down",IF(K61="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D61" s="79">
+      <c r="D61" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I61,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E61" s="79">
+      <c r="E61" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D61,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F61" s="79">
+      <c r="F61" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D61,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G61" s="79">
+      <c r="G61" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D61,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H61" s="79" t="inlineStr">
+      <c r="H61" s="72" t="inlineStr">
         <is>
           <t>CL - 806-17</t>
         </is>
       </c>
-      <c r="I61" s="79" t="inlineStr">
+      <c r="I61" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J61" s="87" t="n">
+      <c r="J61" s="80" t="n">
         <v>765</v>
       </c>
-      <c r="K61" s="79" t="inlineStr">
+      <c r="K61" s="72" t="inlineStr">
         <is>
           <t>Quiroz, Espie</t>
         </is>
       </c>
-      <c r="L61" s="88" t="n">
+      <c r="L61" s="81" t="n">
         <v>1179</v>
       </c>
-      <c r="M61" s="88">
+      <c r="M61" s="81">
         <f>Y61</f>
         <v/>
       </c>
-      <c r="N61" s="89" t="n">
+      <c r="N61" s="82" t="n">
         <v>45971</v>
       </c>
-      <c r="O61" s="89" t="n">
+      <c r="O61" s="82" t="n">
         <v>45971</v>
       </c>
-      <c r="P61" s="89" t="n">
+      <c r="P61" s="82" t="n">
         <v>46335</v>
       </c>
-      <c r="R61" s="88">
+      <c r="R61" s="81">
         <f>SUM(AB61:AI61)</f>
         <v/>
       </c>
-      <c r="S61" s="88">
+      <c r="S61" s="81">
         <f>AK61</f>
         <v/>
       </c>
-      <c r="T61" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="88" t="n">
+      <c r="T61" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="81" t="n">
         <v>1179</v>
       </c>
-      <c r="AB61" s="88" t="n">
+      <c r="AB61" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD61" s="88" t="n">
+      <c r="AD61" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE61" s="88" t="n">
+      <c r="AE61" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF61" s="88" t="n">
+      <c r="AF61" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG61" s="88" t="n">
+      <c r="AG61" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="79">
+      <c r="A62" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B62" s="79">
+      <c r="B62" s="72">
         <f>B61+1</f>
         <v/>
       </c>
-      <c r="C62" s="79">
+      <c r="C62" s="72">
         <f>IF(K62="Vacant","Vac",IF(K62="Model","Model",IF(K62="Admin","Admin",IF(K62="Down","Down",IF(K62="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D62" s="79">
+      <c r="D62" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I62,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E62" s="79">
+      <c r="E62" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D62,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F62" s="79">
+      <c r="F62" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D62,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G62" s="79">
+      <c r="G62" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D62,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H62" s="79" t="inlineStr">
+      <c r="H62" s="72" t="inlineStr">
         <is>
           <t>CL - 806-18</t>
         </is>
       </c>
-      <c r="I62" s="79" t="inlineStr">
+      <c r="I62" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J62" s="87" t="n">
+      <c r="J62" s="80" t="n">
         <v>765</v>
       </c>
-      <c r="K62" s="79" t="inlineStr">
+      <c r="K62" s="72" t="inlineStr">
         <is>
           <t>Ostrander, Bradley</t>
         </is>
       </c>
-      <c r="L62" s="88" t="n">
+      <c r="L62" s="81" t="n">
         <v>1124</v>
       </c>
-      <c r="M62" s="88">
+      <c r="M62" s="81">
         <f>Y62</f>
         <v/>
       </c>
-      <c r="N62" s="89" t="n">
+      <c r="N62" s="82" t="n">
         <v>45946</v>
       </c>
-      <c r="O62" s="89" t="n">
+      <c r="O62" s="82" t="n">
         <v>45946</v>
       </c>
-      <c r="P62" s="89" t="n">
+      <c r="P62" s="82" t="n">
         <v>46310</v>
       </c>
-      <c r="R62" s="88">
+      <c r="R62" s="81">
         <f>SUM(AB62:AI62)</f>
         <v/>
       </c>
-      <c r="S62" s="88">
+      <c r="S62" s="81">
         <f>AK62</f>
         <v/>
       </c>
-      <c r="T62" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="88" t="n">
+      <c r="T62" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="81" t="n">
         <v>1124</v>
       </c>
-      <c r="AB62" s="88" t="n">
+      <c r="AB62" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD62" s="88" t="n">
+      <c r="AD62" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE62" s="88" t="n">
+      <c r="AE62" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF62" s="88" t="n">
+      <c r="AF62" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG62" s="88" t="n">
+      <c r="AG62" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="79">
+      <c r="A63" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B63" s="79">
+      <c r="B63" s="72">
         <f>B62+1</f>
         <v/>
       </c>
-      <c r="C63" s="79">
+      <c r="C63" s="72">
         <f>IF(K63="Vacant","Vac",IF(K63="Model","Model",IF(K63="Admin","Admin",IF(K63="Down","Down",IF(K63="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D63" s="79">
+      <c r="D63" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I63,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E63" s="79">
+      <c r="E63" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D63,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F63" s="79">
+      <c r="F63" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D63,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G63" s="79">
+      <c r="G63" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D63,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H63" s="79" t="inlineStr">
+      <c r="H63" s="72" t="inlineStr">
         <is>
           <t>CL - 806-19</t>
         </is>
       </c>
-      <c r="I63" s="79" t="inlineStr">
+      <c r="I63" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J63" s="87" t="n">
+      <c r="J63" s="80" t="n">
         <v>781</v>
       </c>
-      <c r="K63" s="79" t="inlineStr">
+      <c r="K63" s="72" t="inlineStr">
         <is>
           <t>Webb, Kennetha</t>
         </is>
       </c>
-      <c r="L63" s="88" t="n">
+      <c r="L63" s="81" t="n">
         <v>1324</v>
       </c>
-      <c r="M63" s="88">
+      <c r="M63" s="81">
         <f>Y63</f>
         <v/>
       </c>
-      <c r="N63" s="89" t="n">
+      <c r="N63" s="82" t="n">
         <v>45926</v>
       </c>
-      <c r="O63" s="89" t="n">
+      <c r="O63" s="82" t="n">
         <v>45926</v>
       </c>
-      <c r="P63" s="89" t="n">
+      <c r="P63" s="82" t="n">
         <v>46381</v>
       </c>
-      <c r="R63" s="88">
+      <c r="R63" s="81">
         <f>SUM(AB63:AI63)</f>
         <v/>
       </c>
-      <c r="S63" s="88">
+      <c r="S63" s="81">
         <f>AK63</f>
         <v/>
       </c>
-      <c r="T63" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" s="88" t="n">
+      <c r="T63" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="81" t="n">
         <v>1324</v>
       </c>
-      <c r="AB63" s="88" t="n">
+      <c r="AB63" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AC63" s="88" t="n">
+      <c r="AC63" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="AD63" s="88" t="n">
+      <c r="AD63" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE63" s="88" t="n">
+      <c r="AE63" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF63" s="88" t="n">
+      <c r="AF63" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG63" s="88" t="n">
+      <c r="AG63" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="79">
+      <c r="A64" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B64" s="79">
+      <c r="B64" s="72">
         <f>B63+1</f>
         <v/>
       </c>
-      <c r="C64" s="79">
+      <c r="C64" s="72">
         <f>IF(K64="Vacant","Vac",IF(K64="Model","Model",IF(K64="Admin","Admin",IF(K64="Down","Down",IF(K64="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D64" s="79">
+      <c r="D64" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I64,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E64" s="79">
+      <c r="E64" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D64,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F64" s="79">
+      <c r="F64" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D64,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G64" s="79">
+      <c r="G64" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D64,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H64" s="79" t="inlineStr">
+      <c r="H64" s="72" t="inlineStr">
         <is>
           <t>CL - 806-20</t>
         </is>
       </c>
-      <c r="I64" s="79" t="inlineStr">
+      <c r="I64" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J64" s="87" t="n">
+      <c r="J64" s="80" t="n">
         <v>515</v>
       </c>
-      <c r="K64" s="79" t="inlineStr">
+      <c r="K64" s="72" t="inlineStr">
         <is>
           <t>Keaton, Aniya</t>
         </is>
       </c>
-      <c r="L64" s="88" t="n">
+      <c r="L64" s="81" t="n">
         <v>1114</v>
       </c>
-      <c r="M64" s="88">
+      <c r="M64" s="81">
         <f>Y64</f>
         <v/>
       </c>
-      <c r="N64" s="89" t="n">
+      <c r="N64" s="82" t="n">
         <v>45836</v>
       </c>
-      <c r="O64" s="89" t="n">
+      <c r="O64" s="82" t="n">
         <v>45836</v>
       </c>
-      <c r="P64" s="89" t="n">
+      <c r="P64" s="82" t="n">
         <v>46200</v>
       </c>
-      <c r="R64" s="88">
+      <c r="R64" s="81">
         <f>SUM(AB64:AI64)</f>
         <v/>
       </c>
-      <c r="S64" s="88">
+      <c r="S64" s="81">
         <f>AK64</f>
         <v/>
       </c>
-      <c r="T64" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" s="88" t="n">
+      <c r="T64" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="81" t="n">
         <v>1114</v>
       </c>
-      <c r="AB64" s="88" t="n">
+      <c r="AB64" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AD64" s="88" t="n">
+      <c r="AD64" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE64" s="88" t="n">
+      <c r="AE64" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF64" s="88" t="n">
+      <c r="AF64" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG64" s="88" t="n">
+      <c r="AG64" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="79">
+      <c r="A65" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B65" s="79">
+      <c r="B65" s="72">
         <f>B64+1</f>
         <v/>
       </c>
-      <c r="C65" s="79">
+      <c r="C65" s="72">
         <f>IF(K65="Vacant","Vac",IF(K65="Model","Model",IF(K65="Admin","Admin",IF(K65="Down","Down",IF(K65="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D65" s="79">
+      <c r="D65" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I65,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E65" s="79">
+      <c r="E65" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D65,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F65" s="79">
+      <c r="F65" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D65,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G65" s="79">
+      <c r="G65" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D65,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H65" s="79" t="inlineStr">
+      <c r="H65" s="72" t="inlineStr">
         <is>
           <t>CL - 806-21</t>
         </is>
       </c>
-      <c r="I65" s="79" t="inlineStr">
+      <c r="I65" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J65" s="87" t="n">
+      <c r="J65" s="80" t="n">
         <v>515</v>
       </c>
-      <c r="K65" s="79" t="inlineStr">
+      <c r="K65" s="72" t="inlineStr">
         <is>
           <t>Sanchez Hernandez, Jose Adolfo</t>
         </is>
       </c>
-      <c r="L65" s="88" t="n">
+      <c r="L65" s="81" t="n">
         <v>1169</v>
       </c>
-      <c r="M65" s="88">
+      <c r="M65" s="81">
         <f>Y65</f>
         <v/>
       </c>
-      <c r="N65" s="89" t="n">
+      <c r="N65" s="82" t="n">
         <v>45623</v>
       </c>
-      <c r="O65" s="89" t="n">
+      <c r="O65" s="82" t="n">
         <v>45988</v>
       </c>
-      <c r="P65" s="89" t="n">
+      <c r="P65" s="82" t="n">
         <v>46352</v>
       </c>
-      <c r="R65" s="88">
+      <c r="R65" s="81">
         <f>SUM(AB65:AI65)</f>
         <v/>
       </c>
-      <c r="S65" s="88">
+      <c r="S65" s="81">
         <f>AK65</f>
         <v/>
       </c>
-      <c r="T65" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" s="88" t="n">
+      <c r="T65" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="81" t="n">
         <v>1245</v>
       </c>
-      <c r="AB65" s="88" t="n">
+      <c r="AB65" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD65" s="88" t="n">
+      <c r="AD65" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE65" s="88" t="n">
+      <c r="AE65" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF65" s="88" t="n">
+      <c r="AF65" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG65" s="88" t="n">
+      <c r="AG65" s="81" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="79">
+      <c r="A66" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B66" s="79">
+      <c r="B66" s="72">
         <f>B65+1</f>
         <v/>
       </c>
-      <c r="C66" s="79">
+      <c r="C66" s="72">
         <f>IF(K66="Vacant","Vac",IF(K66="Model","Model",IF(K66="Admin","Admin",IF(K66="Down","Down",IF(K66="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D66" s="79">
+      <c r="D66" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I66,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E66" s="79">
+      <c r="E66" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D66,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F66" s="79">
+      <c r="F66" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D66,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G66" s="79">
+      <c r="G66" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D66,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H66" s="79" t="inlineStr">
+      <c r="H66" s="72" t="inlineStr">
         <is>
           <t>CL - 806-22</t>
         </is>
       </c>
-      <c r="I66" s="79" t="inlineStr">
+      <c r="I66" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J66" s="87" t="n">
+      <c r="J66" s="80" t="n">
         <v>748</v>
       </c>
-      <c r="K66" s="79" t="inlineStr">
+      <c r="K66" s="72" t="inlineStr">
         <is>
           <t>Sablas, Mary</t>
         </is>
       </c>
-      <c r="L66" s="88" t="n">
+      <c r="L66" s="81" t="n">
         <v>1109</v>
       </c>
-      <c r="M66" s="88">
+      <c r="M66" s="81">
         <f>Y66</f>
         <v/>
       </c>
-      <c r="N66" s="89" t="n">
+      <c r="N66" s="82" t="n">
         <v>45308</v>
       </c>
-      <c r="O66" s="89" t="n">
+      <c r="O66" s="82" t="n">
         <v>46039</v>
       </c>
-      <c r="P66" s="89" t="n">
+      <c r="P66" s="82" t="n">
         <v>46493</v>
       </c>
-      <c r="R66" s="88">
+      <c r="R66" s="81">
         <f>SUM(AB66:AI66)</f>
         <v/>
       </c>
-      <c r="S66" s="88">
+      <c r="S66" s="81">
         <f>AK66</f>
         <v/>
       </c>
-      <c r="T66" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="88" t="n">
+      <c r="T66" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="81" t="n">
         <v>1059</v>
       </c>
-      <c r="AB66" s="88" t="n">
+      <c r="AB66" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD66" s="88" t="n">
+      <c r="AD66" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE66" s="88" t="n">
+      <c r="AE66" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF66" s="88" t="n">
+      <c r="AF66" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG66" s="88" t="n">
+      <c r="AG66" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="79">
+      <c r="A67" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B67" s="79">
+      <c r="B67" s="72">
         <f>B66+1</f>
         <v/>
       </c>
-      <c r="C67" s="79">
+      <c r="C67" s="72">
         <f>IF(K67="Vacant","Vac",IF(K67="Model","Model",IF(K67="Admin","Admin",IF(K67="Down","Down",IF(K67="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D67" s="79">
+      <c r="D67" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I67,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E67" s="79">
+      <c r="E67" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D67,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F67" s="79">
+      <c r="F67" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D67,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G67" s="79">
+      <c r="G67" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D67,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H67" s="79" t="inlineStr">
+      <c r="H67" s="72" t="inlineStr">
         <is>
           <t>CL - 806-23</t>
         </is>
       </c>
-      <c r="I67" s="79" t="inlineStr">
+      <c r="I67" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J67" s="87" t="n">
+      <c r="J67" s="80" t="n">
         <v>888</v>
       </c>
-      <c r="K67" s="79" t="inlineStr">
+      <c r="K67" s="72" t="inlineStr">
         <is>
           <t>Sell, Miranda</t>
         </is>
       </c>
-      <c r="L67" s="88" t="n">
+      <c r="L67" s="81" t="n">
         <v>1384</v>
       </c>
-      <c r="M67" s="88">
+      <c r="M67" s="81">
         <f>Y67</f>
         <v/>
       </c>
-      <c r="N67" s="89" t="n">
+      <c r="N67" s="82" t="n">
         <v>45990</v>
       </c>
-      <c r="O67" s="89" t="n">
+      <c r="O67" s="82" t="n">
         <v>45990</v>
       </c>
-      <c r="P67" s="89" t="n">
+      <c r="P67" s="82" t="n">
         <v>46354</v>
       </c>
-      <c r="R67" s="88">
+      <c r="R67" s="81">
         <f>SUM(AB67:AI67)</f>
         <v/>
       </c>
-      <c r="S67" s="88">
+      <c r="S67" s="81">
         <f>AK67</f>
         <v/>
       </c>
-      <c r="T67" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y67" s="88" t="n">
+      <c r="T67" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="81" t="n">
         <v>1384</v>
       </c>
-      <c r="AB67" s="88" t="n">
+      <c r="AB67" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD67" s="88" t="n">
+      <c r="AD67" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE67" s="88" t="n">
+      <c r="AE67" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF67" s="88" t="n">
+      <c r="AF67" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG67" s="88" t="n">
+      <c r="AG67" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="79">
+      <c r="A68" s="83">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B68" s="79">
+      <c r="B68" s="83">
         <f>B67+1</f>
         <v/>
       </c>
-      <c r="C68" s="79">
+      <c r="C68" s="83">
         <f>IF(K68="Vacant","Vac",IF(K68="Model","Model",IF(K68="Admin","Admin",IF(K68="Down","Down",IF(K68="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D68" s="79">
+      <c r="D68" s="83">
         <f>INDEX($C$5:$C$8,MATCH(I68,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E68" s="79">
+      <c r="E68" s="83">
         <f>INDEX($E$5:$E$8,MATCH(D68,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F68" s="79">
+      <c r="F68" s="83">
         <f>INDEX($F$5:$F$8,MATCH(D68,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G68" s="79">
+      <c r="G68" s="83">
         <f>INDEX($G$5:$G$8,MATCH(D68,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H68" s="79" t="inlineStr">
+      <c r="H68" s="83" t="inlineStr">
         <is>
           <t>CL - 806-24</t>
         </is>
       </c>
-      <c r="I68" s="79" t="inlineStr">
+      <c r="I68" s="83" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J68" s="87" t="n">
+      <c r="J68" s="84" t="n">
         <v>683</v>
       </c>
-      <c r="K68" s="79" t="inlineStr">
+      <c r="K68" s="83" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L68" s="88" t="n">
+      <c r="L68" s="85" t="n">
         <v>1355</v>
       </c>
-      <c r="M68" s="88">
+      <c r="M68" s="85">
         <f>Y68</f>
         <v/>
       </c>
-      <c r="R68" s="88">
+      <c r="N68" s="86" t="n"/>
+      <c r="O68" s="86" t="n"/>
+      <c r="P68" s="86" t="n"/>
+      <c r="Q68" s="86" t="n"/>
+      <c r="R68" s="85">
         <f>SUM(AB68:AI68)</f>
         <v/>
       </c>
-      <c r="S68" s="88">
+      <c r="S68" s="85">
         <f>AK68</f>
         <v/>
       </c>
-      <c r="T68" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" s="88" t="n">
-        <v>0</v>
-      </c>
+      <c r="T68" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="86" t="n"/>
+      <c r="V68" s="86" t="n"/>
+      <c r="W68" s="86" t="n"/>
+      <c r="X68" s="86" t="n"/>
+      <c r="Y68" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="86" t="n"/>
+      <c r="AA68" s="86" t="n"/>
+      <c r="AB68" s="86" t="n"/>
+      <c r="AC68" s="86" t="n"/>
+      <c r="AD68" s="86" t="n"/>
+      <c r="AE68" s="86" t="n"/>
+      <c r="AF68" s="86" t="n"/>
+      <c r="AG68" s="86" t="n"/>
+      <c r="AH68" s="86" t="n"/>
+      <c r="AI68" s="86" t="n"/>
+      <c r="AJ68" s="86" t="n"/>
+      <c r="AK68" s="86" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="79">
+      <c r="A69" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B69" s="79">
+      <c r="B69" s="72">
         <f>B68+1</f>
         <v/>
       </c>
-      <c r="C69" s="79">
+      <c r="C69" s="72">
         <f>IF(K69="Vacant","Vac",IF(K69="Model","Model",IF(K69="Admin","Admin",IF(K69="Down","Down",IF(K69="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D69" s="79">
+      <c r="D69" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I69,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E69" s="79">
+      <c r="E69" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D69,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F69" s="79">
+      <c r="F69" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D69,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G69" s="79">
+      <c r="G69" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D69,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H69" s="79" t="inlineStr">
+      <c r="H69" s="72" t="inlineStr">
         <is>
           <t>CL - 806-25</t>
         </is>
       </c>
-      <c r="I69" s="79" t="inlineStr">
+      <c r="I69" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J69" s="87" t="n">
+      <c r="J69" s="80" t="n">
         <v>781</v>
       </c>
-      <c r="K69" s="79" t="inlineStr">
+      <c r="K69" s="72" t="inlineStr">
         <is>
           <t>Williams, Andre</t>
         </is>
       </c>
-      <c r="L69" s="88" t="n">
+      <c r="L69" s="81" t="n">
         <v>1314</v>
       </c>
-      <c r="M69" s="88">
+      <c r="M69" s="81">
         <f>Y69</f>
         <v/>
       </c>
-      <c r="N69" s="89" t="n">
+      <c r="N69" s="82" t="n">
         <v>45717</v>
       </c>
-      <c r="O69" s="89" t="n">
+      <c r="O69" s="82" t="n">
         <v>46082</v>
       </c>
-      <c r="P69" s="89" t="n">
+      <c r="P69" s="82" t="n">
         <v>46446</v>
       </c>
-      <c r="R69" s="88">
+      <c r="R69" s="81">
         <f>SUM(AB69:AI69)</f>
         <v/>
       </c>
-      <c r="S69" s="88">
+      <c r="S69" s="81">
         <f>AK69</f>
         <v/>
       </c>
-      <c r="T69" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y69" s="88" t="n">
+      <c r="T69" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="81" t="n">
         <v>1184</v>
       </c>
-      <c r="AB69" s="88" t="n">
+      <c r="AB69" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AC69" s="88" t="n">
+      <c r="AC69" s="81" t="n">
         <v>35</v>
       </c>
-      <c r="AD69" s="88" t="n">
+      <c r="AD69" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE69" s="88" t="n">
+      <c r="AE69" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF69" s="88" t="n">
+      <c r="AF69" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG69" s="88" t="n">
+      <c r="AG69" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="79">
+      <c r="A70" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B70" s="79">
+      <c r="B70" s="72">
         <f>B69+1</f>
         <v/>
       </c>
-      <c r="C70" s="79">
+      <c r="C70" s="72">
         <f>IF(K70="Vacant","Vac",IF(K70="Model","Model",IF(K70="Admin","Admin",IF(K70="Down","Down",IF(K70="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D70" s="79">
+      <c r="D70" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I70,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E70" s="79">
+      <c r="E70" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D70,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F70" s="79">
+      <c r="F70" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D70,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G70" s="79">
+      <c r="G70" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D70,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H70" s="79" t="inlineStr">
+      <c r="H70" s="72" t="inlineStr">
         <is>
           <t>CL - 806-26</t>
         </is>
       </c>
-      <c r="I70" s="79" t="inlineStr">
+      <c r="I70" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J70" s="87" t="n">
+      <c r="J70" s="80" t="n">
         <v>685</v>
       </c>
-      <c r="K70" s="79" t="inlineStr">
+      <c r="K70" s="72" t="inlineStr">
         <is>
           <t>Hausley, Isaiah</t>
         </is>
       </c>
-      <c r="L70" s="88" t="n">
+      <c r="L70" s="81" t="n">
         <v>1364</v>
       </c>
-      <c r="M70" s="88">
+      <c r="M70" s="81">
         <f>Y70</f>
         <v/>
       </c>
-      <c r="N70" s="89" t="n">
+      <c r="N70" s="82" t="n">
         <v>44909</v>
       </c>
-      <c r="O70" s="89" t="n">
+      <c r="O70" s="82" t="n">
         <v>46039</v>
       </c>
-      <c r="P70" s="89" t="n">
+      <c r="P70" s="82" t="n">
         <v>46403</v>
       </c>
-      <c r="R70" s="88">
+      <c r="R70" s="81">
         <f>SUM(AB70:AI70)</f>
         <v/>
       </c>
-      <c r="S70" s="88">
+      <c r="S70" s="81">
         <f>AK70</f>
         <v/>
       </c>
-      <c r="T70" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y70" s="88" t="n">
+      <c r="T70" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="81" t="n">
         <v>1255</v>
       </c>
-      <c r="AB70" s="88" t="n">
+      <c r="AB70" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD70" s="88" t="n">
+      <c r="AD70" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE70" s="88" t="n">
+      <c r="AE70" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF70" s="88" t="n">
+      <c r="AF70" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG70" s="88" t="n">
+      <c r="AG70" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="79">
+      <c r="A71" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B71" s="79">
+      <c r="B71" s="72">
         <f>B70+1</f>
         <v/>
       </c>
-      <c r="C71" s="79">
+      <c r="C71" s="72">
         <f>IF(K71="Vacant","Vac",IF(K71="Model","Model",IF(K71="Admin","Admin",IF(K71="Down","Down",IF(K71="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D71" s="79">
+      <c r="D71" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I71,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E71" s="79">
+      <c r="E71" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D71,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F71" s="79">
+      <c r="F71" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D71,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G71" s="79">
+      <c r="G71" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D71,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H71" s="79" t="inlineStr">
+      <c r="H71" s="72" t="inlineStr">
         <is>
           <t>CL - 806-27</t>
         </is>
       </c>
-      <c r="I71" s="79" t="inlineStr">
+      <c r="I71" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J71" s="87" t="n">
+      <c r="J71" s="80" t="n">
         <v>516</v>
       </c>
-      <c r="K71" s="79" t="inlineStr">
+      <c r="K71" s="72" t="inlineStr">
         <is>
           <t>West, Brayden</t>
         </is>
       </c>
-      <c r="L71" s="88" t="n">
+      <c r="L71" s="81" t="n">
         <v>1149</v>
       </c>
-      <c r="M71" s="88">
+      <c r="M71" s="81">
         <f>Y71</f>
         <v/>
       </c>
-      <c r="N71" s="89" t="n">
+      <c r="N71" s="82" t="n">
         <v>45869</v>
       </c>
-      <c r="O71" s="89" t="n">
+      <c r="O71" s="82" t="n">
         <v>45869</v>
       </c>
-      <c r="P71" s="89" t="n">
+      <c r="P71" s="82" t="n">
         <v>46233</v>
       </c>
-      <c r="R71" s="88">
+      <c r="R71" s="81">
         <f>SUM(AB71:AI71)</f>
         <v/>
       </c>
-      <c r="S71" s="88">
+      <c r="S71" s="81">
         <f>AK71</f>
         <v/>
       </c>
-      <c r="T71" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y71" s="88" t="n">
+      <c r="T71" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="81" t="n">
         <v>1149</v>
       </c>
-      <c r="AB71" s="88" t="n">
+      <c r="AB71" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD71" s="88" t="n">
+      <c r="AD71" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE71" s="88" t="n">
+      <c r="AE71" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF71" s="88" t="n">
+      <c r="AF71" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG71" s="88" t="n">
+      <c r="AG71" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="79">
+      <c r="A72" s="83">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B72" s="79">
+      <c r="B72" s="83">
         <f>B71+1</f>
         <v/>
       </c>
-      <c r="C72" s="79">
+      <c r="C72" s="83">
         <f>IF(K72="Vacant","Vac",IF(K72="Model","Model",IF(K72="Admin","Admin",IF(K72="Down","Down",IF(K72="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D72" s="79">
+      <c r="D72" s="83">
         <f>INDEX($C$5:$C$8,MATCH(I72,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E72" s="79">
+      <c r="E72" s="83">
         <f>INDEX($E$5:$E$8,MATCH(D72,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F72" s="79">
+      <c r="F72" s="83">
         <f>INDEX($F$5:$F$8,MATCH(D72,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G72" s="79">
+      <c r="G72" s="83">
         <f>INDEX($G$5:$G$8,MATCH(D72,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H72" s="79" t="inlineStr">
+      <c r="H72" s="83" t="inlineStr">
         <is>
           <t>CL - 806-28</t>
         </is>
       </c>
-      <c r="I72" s="79" t="inlineStr">
+      <c r="I72" s="83" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J72" s="87" t="n">
+      <c r="J72" s="84" t="n">
         <v>775</v>
       </c>
-      <c r="K72" s="79" t="inlineStr">
+      <c r="K72" s="83" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="L72" s="88" t="n">
+      <c r="L72" s="85" t="n">
         <v>1355</v>
       </c>
-      <c r="M72" s="88">
+      <c r="M72" s="85">
         <f>Y72</f>
         <v/>
       </c>
-      <c r="R72" s="88">
+      <c r="N72" s="86" t="n"/>
+      <c r="O72" s="86" t="n"/>
+      <c r="P72" s="86" t="n"/>
+      <c r="Q72" s="86" t="n"/>
+      <c r="R72" s="85">
         <f>SUM(AB72:AI72)</f>
         <v/>
       </c>
-      <c r="S72" s="88">
+      <c r="S72" s="85">
         <f>AK72</f>
         <v/>
       </c>
-      <c r="T72" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="88" t="n">
-        <v>0</v>
-      </c>
+      <c r="T72" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="86" t="n"/>
+      <c r="V72" s="86" t="n"/>
+      <c r="W72" s="86" t="n"/>
+      <c r="X72" s="86" t="n"/>
+      <c r="Y72" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="86" t="n"/>
+      <c r="AA72" s="86" t="n"/>
+      <c r="AB72" s="86" t="n"/>
+      <c r="AC72" s="86" t="n"/>
+      <c r="AD72" s="86" t="n"/>
+      <c r="AE72" s="86" t="n"/>
+      <c r="AF72" s="86" t="n"/>
+      <c r="AG72" s="86" t="n"/>
+      <c r="AH72" s="86" t="n"/>
+      <c r="AI72" s="86" t="n"/>
+      <c r="AJ72" s="86" t="n"/>
+      <c r="AK72" s="86" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="79">
+      <c r="A73" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B73" s="79">
+      <c r="B73" s="72">
         <f>B72+1</f>
         <v/>
       </c>
-      <c r="C73" s="79">
+      <c r="C73" s="72">
         <f>IF(K73="Vacant","Vac",IF(K73="Model","Model",IF(K73="Admin","Admin",IF(K73="Down","Down",IF(K73="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D73" s="79">
+      <c r="D73" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I73,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E73" s="79">
+      <c r="E73" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D73,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F73" s="79">
+      <c r="F73" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D73,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G73" s="79">
+      <c r="G73" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D73,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H73" s="79" t="inlineStr">
+      <c r="H73" s="72" t="inlineStr">
         <is>
           <t>CL - 806-29</t>
         </is>
       </c>
-      <c r="I73" s="79" t="inlineStr">
+      <c r="I73" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J73" s="87" t="n">
+      <c r="J73" s="80" t="n">
         <v>712</v>
       </c>
-      <c r="K73" s="79" t="inlineStr">
+      <c r="K73" s="72" t="inlineStr">
         <is>
           <t>Ndiaye, Omar</t>
         </is>
       </c>
-      <c r="L73" s="88" t="n">
+      <c r="L73" s="81" t="n">
         <v>1349</v>
       </c>
-      <c r="M73" s="88">
+      <c r="M73" s="81">
         <f>Y73</f>
         <v/>
       </c>
-      <c r="N73" s="89" t="n">
+      <c r="N73" s="82" t="n">
         <v>45120</v>
       </c>
-      <c r="O73" s="89" t="n">
+      <c r="O73" s="82" t="n">
         <v>45851</v>
       </c>
-      <c r="P73" s="89" t="n">
+      <c r="P73" s="82" t="n">
         <v>46215</v>
       </c>
-      <c r="R73" s="88">
+      <c r="R73" s="81">
         <f>SUM(AB73:AI73)</f>
         <v/>
       </c>
-      <c r="S73" s="88">
+      <c r="S73" s="81">
         <f>AK73</f>
         <v/>
       </c>
-      <c r="T73" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y73" s="88" t="n">
+      <c r="T73" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="81" t="n">
         <v>1330</v>
       </c>
-      <c r="AB73" s="88" t="n">
+      <c r="AB73" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AD73" s="88" t="n">
+      <c r="AD73" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE73" s="88" t="n">
+      <c r="AE73" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF73" s="88" t="n">
+      <c r="AF73" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG73" s="88" t="n">
+      <c r="AG73" s="81" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="79">
+      <c r="A74" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B74" s="79">
+      <c r="B74" s="72">
         <f>B73+1</f>
         <v/>
       </c>
-      <c r="C74" s="79">
+      <c r="C74" s="72">
         <f>IF(K74="Vacant","Vac",IF(K74="Model","Model",IF(K74="Admin","Admin",IF(K74="Down","Down",IF(K74="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D74" s="79">
+      <c r="D74" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I74,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E74" s="79">
+      <c r="E74" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D74,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F74" s="79">
+      <c r="F74" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D74,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G74" s="79">
+      <c r="G74" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D74,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H74" s="79" t="inlineStr">
+      <c r="H74" s="72" t="inlineStr">
         <is>
           <t>CL - 806-30</t>
         </is>
       </c>
-      <c r="I74" s="79" t="inlineStr">
+      <c r="I74" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J74" s="87" t="n">
+      <c r="J74" s="80" t="n">
         <v>712</v>
       </c>
-      <c r="K74" s="79" t="inlineStr">
+      <c r="K74" s="72" t="inlineStr">
         <is>
           <t>Ogundipe, Eniola</t>
         </is>
       </c>
-      <c r="L74" s="88" t="n">
+      <c r="L74" s="81" t="n">
         <v>1124</v>
       </c>
-      <c r="M74" s="88">
+      <c r="M74" s="81">
         <f>Y74</f>
         <v/>
       </c>
-      <c r="N74" s="89" t="n">
+      <c r="N74" s="82" t="n">
         <v>45077</v>
       </c>
-      <c r="O74" s="89" t="n">
+      <c r="O74" s="82" t="n">
         <v>45808</v>
       </c>
-      <c r="P74" s="89" t="n">
+      <c r="P74" s="82" t="n">
         <v>46172</v>
       </c>
-      <c r="R74" s="88">
+      <c r="R74" s="81">
         <f>SUM(AB74:AI74)</f>
         <v/>
       </c>
-      <c r="S74" s="88">
+      <c r="S74" s="81">
         <f>AK74</f>
         <v/>
       </c>
-      <c r="T74" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y74" s="88" t="n">
+      <c r="T74" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="81" t="n">
         <v>1185</v>
       </c>
-      <c r="AB74" s="88" t="n">
+      <c r="AB74" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AC74" s="88" t="n">
+      <c r="AC74" s="81" t="n">
         <v>35</v>
       </c>
-      <c r="AD74" s="88" t="n">
+      <c r="AD74" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE74" s="88" t="n">
+      <c r="AE74" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF74" s="88" t="n">
+      <c r="AF74" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG74" s="88" t="n">
+      <c r="AG74" s="81" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="79">
+      <c r="A75" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B75" s="79">
+      <c r="B75" s="72">
         <f>B74+1</f>
         <v/>
       </c>
-      <c r="C75" s="79">
+      <c r="C75" s="72">
         <f>IF(K75="Vacant","Vac",IF(K75="Model","Model",IF(K75="Admin","Admin",IF(K75="Down","Down",IF(K75="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D75" s="79">
+      <c r="D75" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I75,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E75" s="79">
+      <c r="E75" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D75,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F75" s="79">
+      <c r="F75" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D75,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G75" s="79">
+      <c r="G75" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D75,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H75" s="79" t="inlineStr">
+      <c r="H75" s="72" t="inlineStr">
         <is>
           <t>CL - 806-31</t>
         </is>
       </c>
-      <c r="I75" s="79" t="inlineStr">
+      <c r="I75" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J75" s="87" t="n">
+      <c r="J75" s="80" t="n">
         <v>781</v>
       </c>
-      <c r="K75" s="79" t="inlineStr">
+      <c r="K75" s="72" t="inlineStr">
         <is>
           <t>HUTZELL, LILLIAN</t>
         </is>
       </c>
-      <c r="L75" s="88" t="n">
+      <c r="L75" s="81" t="n">
         <v>1349</v>
       </c>
-      <c r="M75" s="88">
+      <c r="M75" s="81">
         <f>Y75</f>
         <v/>
       </c>
-      <c r="N75" s="89" t="n">
+      <c r="N75" s="82" t="n">
         <v>44678</v>
       </c>
-      <c r="O75" s="89" t="n">
+      <c r="O75" s="82" t="n">
         <v>46139</v>
       </c>
-      <c r="P75" s="89" t="n">
+      <c r="P75" s="82" t="n">
         <v>46503</v>
       </c>
-      <c r="R75" s="88">
+      <c r="R75" s="81">
         <f>SUM(AB75:AI75)</f>
         <v/>
       </c>
-      <c r="S75" s="88">
+      <c r="S75" s="81">
         <f>AK75</f>
         <v/>
       </c>
-      <c r="T75" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y75" s="88" t="n">
+      <c r="T75" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="81" t="n">
         <v>1355</v>
       </c>
-      <c r="AB75" s="88" t="n">
+      <c r="AB75" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AC75" s="88" t="n">
+      <c r="AC75" s="81" t="n">
         <v>35</v>
       </c>
-      <c r="AD75" s="88" t="n">
+      <c r="AD75" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE75" s="88" t="n">
+      <c r="AE75" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF75" s="88" t="n">
+      <c r="AF75" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG75" s="88" t="n">
+      <c r="AG75" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="79">
+      <c r="A76" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B76" s="79">
+      <c r="B76" s="72">
         <f>B75+1</f>
         <v/>
       </c>
-      <c r="C76" s="79">
+      <c r="C76" s="72">
         <f>IF(K76="Vacant","Vac",IF(K76="Model","Model",IF(K76="Admin","Admin",IF(K76="Down","Down",IF(K76="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D76" s="79">
+      <c r="D76" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I76,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E76" s="79">
+      <c r="E76" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D76,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F76" s="79">
+      <c r="F76" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D76,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G76" s="79">
+      <c r="G76" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D76,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H76" s="79" t="inlineStr">
+      <c r="H76" s="72" t="inlineStr">
         <is>
           <t>CL - 806-32</t>
         </is>
       </c>
-      <c r="I76" s="79" t="inlineStr">
+      <c r="I76" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J76" s="87" t="n">
+      <c r="J76" s="80" t="n">
         <v>686</v>
       </c>
-      <c r="K76" s="79" t="inlineStr">
+      <c r="K76" s="72" t="inlineStr">
         <is>
           <t>La Flower, Michael</t>
         </is>
       </c>
-      <c r="L76" s="88" t="n">
+      <c r="L76" s="81" t="n">
         <v>1334</v>
       </c>
-      <c r="M76" s="88">
+      <c r="M76" s="81">
         <f>Y76</f>
         <v/>
       </c>
-      <c r="N76" s="89" t="n">
+      <c r="N76" s="82" t="n">
         <v>45898</v>
       </c>
-      <c r="O76" s="89" t="n">
+      <c r="O76" s="82" t="n">
         <v>45898</v>
       </c>
-      <c r="P76" s="89" t="n">
+      <c r="P76" s="82" t="n">
         <v>46262</v>
       </c>
-      <c r="R76" s="88">
+      <c r="R76" s="81">
         <f>SUM(AB76:AI76)</f>
         <v/>
       </c>
-      <c r="S76" s="88">
+      <c r="S76" s="81">
         <f>AK76</f>
         <v/>
       </c>
-      <c r="T76" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="88" t="n">
+      <c r="T76" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="81" t="n">
         <v>1334</v>
       </c>
-      <c r="AB76" s="88" t="n">
+      <c r="AB76" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD76" s="88" t="n">
+      <c r="AD76" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE76" s="88" t="n">
+      <c r="AE76" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF76" s="88" t="n">
+      <c r="AF76" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG76" s="88" t="n">
+      <c r="AG76" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="79">
+      <c r="A77" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B77" s="79">
+      <c r="B77" s="72">
         <f>B76+1</f>
         <v/>
       </c>
-      <c r="C77" s="79">
+      <c r="C77" s="72">
         <f>IF(K77="Vacant","Vac",IF(K77="Model","Model",IF(K77="Admin","Admin",IF(K77="Down","Down",IF(K77="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D77" s="79">
+      <c r="D77" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I77,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E77" s="79">
+      <c r="E77" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D77,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F77" s="79">
+      <c r="F77" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D77,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G77" s="79">
+      <c r="G77" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D77,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H77" s="79" t="inlineStr">
+      <c r="H77" s="72" t="inlineStr">
         <is>
           <t>CL - 806-33</t>
         </is>
       </c>
-      <c r="I77" s="79" t="inlineStr">
+      <c r="I77" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J77" s="87" t="n">
+      <c r="J77" s="80" t="n">
         <v>516</v>
       </c>
-      <c r="K77" s="79" t="inlineStr">
+      <c r="K77" s="72" t="inlineStr">
         <is>
           <t>Bowman, Katherine</t>
         </is>
       </c>
-      <c r="L77" s="88" t="n">
+      <c r="L77" s="81" t="n">
         <v>1124</v>
       </c>
-      <c r="M77" s="88">
+      <c r="M77" s="81">
         <f>Y77</f>
         <v/>
       </c>
-      <c r="N77" s="89" t="n">
+      <c r="N77" s="82" t="n">
         <v>45821</v>
       </c>
-      <c r="O77" s="89" t="n">
+      <c r="O77" s="82" t="n">
         <v>45821</v>
       </c>
-      <c r="P77" s="89" t="n">
+      <c r="P77" s="82" t="n">
         <v>46186</v>
       </c>
-      <c r="R77" s="88">
+      <c r="R77" s="81">
         <f>SUM(AB77:AI77)</f>
         <v/>
       </c>
-      <c r="S77" s="88">
+      <c r="S77" s="81">
         <f>AK77</f>
         <v/>
       </c>
-      <c r="T77" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y77" s="88" t="n">
+      <c r="T77" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="81" t="n">
         <v>1124</v>
       </c>
-      <c r="AB77" s="88" t="n">
+      <c r="AB77" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AD77" s="88" t="n">
+      <c r="AD77" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE77" s="88" t="n">
+      <c r="AE77" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF77" s="88" t="n">
+      <c r="AF77" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG77" s="88" t="n">
+      <c r="AG77" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="79">
+      <c r="A78" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B78" s="79">
+      <c r="B78" s="72">
         <f>B77+1</f>
         <v/>
       </c>
-      <c r="C78" s="79">
+      <c r="C78" s="72">
         <f>IF(K78="Vacant","Vac",IF(K78="Model","Model",IF(K78="Admin","Admin",IF(K78="Down","Down",IF(K78="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D78" s="79">
+      <c r="D78" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I78,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E78" s="79">
+      <c r="E78" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D78,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F78" s="79">
+      <c r="F78" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D78,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G78" s="79">
+      <c r="G78" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D78,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H78" s="79" t="inlineStr">
+      <c r="H78" s="72" t="inlineStr">
         <is>
           <t>CL - 806-34</t>
         </is>
       </c>
-      <c r="I78" s="79" t="inlineStr">
+      <c r="I78" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J78" s="87" t="n">
+      <c r="J78" s="80" t="n">
         <v>748</v>
       </c>
-      <c r="K78" s="79" t="inlineStr">
+      <c r="K78" s="72" t="inlineStr">
         <is>
           <t>Asher, Derrick</t>
         </is>
       </c>
-      <c r="L78" s="88" t="n">
+      <c r="L78" s="81" t="n">
         <v>1334</v>
       </c>
-      <c r="M78" s="88">
+      <c r="M78" s="81">
         <f>Y78</f>
         <v/>
       </c>
-      <c r="N78" s="89" t="n">
+      <c r="N78" s="82" t="n">
         <v>45855</v>
       </c>
-      <c r="O78" s="89" t="n">
+      <c r="O78" s="82" t="n">
         <v>45855</v>
       </c>
-      <c r="P78" s="89" t="n">
+      <c r="P78" s="82" t="n">
         <v>46219</v>
       </c>
-      <c r="R78" s="88">
+      <c r="R78" s="81">
         <f>SUM(AB78:AI78)</f>
         <v/>
       </c>
-      <c r="S78" s="88">
+      <c r="S78" s="81">
         <f>AK78</f>
         <v/>
       </c>
-      <c r="T78" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y78" s="88" t="n">
+      <c r="T78" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="81" t="n">
         <v>1334</v>
       </c>
-      <c r="AB78" s="88" t="n">
+      <c r="AB78" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AD78" s="88" t="n">
+      <c r="AD78" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE78" s="88" t="n">
+      <c r="AE78" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF78" s="88" t="n">
+      <c r="AF78" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG78" s="88" t="n">
+      <c r="AG78" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="79">
+      <c r="A79" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B79" s="79">
+      <c r="B79" s="72">
         <f>B78+1</f>
         <v/>
       </c>
-      <c r="C79" s="79">
+      <c r="C79" s="72">
         <f>IF(K79="Vacant","Vac",IF(K79="Model","Model",IF(K79="Admin","Admin",IF(K79="Down","Down",IF(K79="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D79" s="79">
+      <c r="D79" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I79,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E79" s="79">
+      <c r="E79" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D79,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F79" s="79">
+      <c r="F79" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D79,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G79" s="79">
+      <c r="G79" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D79,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H79" s="79" t="inlineStr">
+      <c r="H79" s="72" t="inlineStr">
         <is>
           <t>CL - 806-35</t>
         </is>
       </c>
-      <c r="I79" s="79" t="inlineStr">
+      <c r="I79" s="72" t="inlineStr">
         <is>
           <t>2x1A_C</t>
         </is>
       </c>
-      <c r="J79" s="87" t="n">
+      <c r="J79" s="80" t="n">
         <v>1078</v>
       </c>
-      <c r="K79" s="79" t="inlineStr">
+      <c r="K79" s="72" t="inlineStr">
         <is>
           <t>Mack, Morgan</t>
         </is>
       </c>
-      <c r="L79" s="88" t="n">
+      <c r="L79" s="81" t="n">
         <v>1394</v>
       </c>
-      <c r="M79" s="88">
+      <c r="M79" s="81">
         <f>Y79</f>
         <v/>
       </c>
-      <c r="N79" s="89" t="n">
+      <c r="N79" s="82" t="n">
         <v>46112</v>
       </c>
-      <c r="O79" s="89" t="n">
+      <c r="O79" s="82" t="n">
         <v>46112</v>
       </c>
-      <c r="P79" s="89" t="n">
+      <c r="P79" s="82" t="n">
         <v>46476</v>
       </c>
-      <c r="R79" s="88">
+      <c r="R79" s="81">
         <f>SUM(AB79:AI79)</f>
         <v/>
       </c>
-      <c r="S79" s="88">
+      <c r="S79" s="81">
         <f>AK79</f>
         <v/>
       </c>
-      <c r="T79" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" s="88" t="n">
+      <c r="T79" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="81" t="n">
         <v>1394</v>
       </c>
-      <c r="AB79" s="88" t="n">
+      <c r="AB79" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD79" s="88" t="n">
+      <c r="AD79" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE79" s="88" t="n">
+      <c r="AE79" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF79" s="88" t="n">
+      <c r="AF79" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG79" s="88" t="n">
+      <c r="AG79" s="81" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="79">
+      <c r="A80" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B80" s="79">
+      <c r="B80" s="72">
         <f>B79+1</f>
         <v/>
       </c>
-      <c r="C80" s="79">
+      <c r="C80" s="72">
         <f>IF(K80="Vacant","Vac",IF(K80="Model","Model",IF(K80="Admin","Admin",IF(K80="Down","Down",IF(K80="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D80" s="79">
+      <c r="D80" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I80,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E80" s="79">
+      <c r="E80" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D80,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F80" s="79">
+      <c r="F80" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D80,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G80" s="79">
+      <c r="G80" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D80,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H80" s="79" t="inlineStr">
+      <c r="H80" s="72" t="inlineStr">
         <is>
           <t>CL - 816-1</t>
         </is>
       </c>
-      <c r="I80" s="79" t="inlineStr">
+      <c r="I80" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J80" s="87" t="n">
+      <c r="J80" s="80" t="n">
         <v>540</v>
       </c>
-      <c r="K80" s="79" t="inlineStr">
+      <c r="K80" s="72" t="inlineStr">
         <is>
           <t>Miller, Brian</t>
         </is>
       </c>
-      <c r="L80" s="88" t="n">
+      <c r="L80" s="81" t="n">
         <v>1189</v>
       </c>
-      <c r="M80" s="88">
+      <c r="M80" s="81">
         <f>Y80</f>
         <v/>
       </c>
-      <c r="N80" s="89" t="n">
+      <c r="N80" s="82" t="n">
         <v>45595</v>
       </c>
-      <c r="O80" s="89" t="n">
+      <c r="O80" s="82" t="n">
         <v>45960</v>
       </c>
-      <c r="P80" s="89" t="n">
+      <c r="P80" s="82" t="n">
         <v>46416</v>
       </c>
-      <c r="R80" s="88">
+      <c r="R80" s="81">
         <f>SUM(AB80:AI80)</f>
         <v/>
       </c>
-      <c r="S80" s="88">
+      <c r="S80" s="81">
         <f>AK80</f>
         <v/>
       </c>
-      <c r="T80" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y80" s="88" t="n">
+      <c r="T80" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="81" t="n">
         <v>1300</v>
       </c>
-      <c r="AB80" s="88" t="n">
+      <c r="AB80" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD80" s="88" t="n">
+      <c r="AD80" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE80" s="88" t="n">
+      <c r="AE80" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF80" s="88" t="n">
+      <c r="AF80" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG80" s="88" t="n">
+      <c r="AG80" s="81" t="n">
         <v>65</v>
       </c>
-      <c r="AI80" s="88" t="n">
+      <c r="AI80" s="81" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="79">
+      <c r="A81" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B81" s="79">
+      <c r="B81" s="72">
         <f>B80+1</f>
         <v/>
       </c>
-      <c r="C81" s="79">
+      <c r="C81" s="72">
         <f>IF(K81="Vacant","Vac",IF(K81="Model","Model",IF(K81="Admin","Admin",IF(K81="Down","Down",IF(K81="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D81" s="79">
+      <c r="D81" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I81,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E81" s="79">
+      <c r="E81" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D81,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F81" s="79">
+      <c r="F81" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D81,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G81" s="79">
+      <c r="G81" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D81,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H81" s="79" t="inlineStr">
+      <c r="H81" s="72" t="inlineStr">
         <is>
           <t>CL - 816-2</t>
         </is>
       </c>
-      <c r="I81" s="79" t="inlineStr">
+      <c r="I81" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J81" s="87" t="n">
+      <c r="J81" s="80" t="n">
         <v>775</v>
       </c>
-      <c r="K81" s="79" t="inlineStr">
+      <c r="K81" s="72" t="inlineStr">
         <is>
           <t>Holbrook, Kendrick</t>
         </is>
       </c>
-      <c r="L81" s="88" t="n">
+      <c r="L81" s="81" t="n">
         <v>1189</v>
       </c>
-      <c r="M81" s="88">
+      <c r="M81" s="81">
         <f>Y81</f>
         <v/>
       </c>
-      <c r="N81" s="89" t="n">
+      <c r="N81" s="82" t="n">
         <v>45456</v>
       </c>
-      <c r="O81" s="89" t="n">
+      <c r="O81" s="82" t="n">
         <v>45821</v>
       </c>
-      <c r="P81" s="89" t="n">
+      <c r="P81" s="82" t="n">
         <v>46185</v>
       </c>
-      <c r="R81" s="88">
+      <c r="R81" s="81">
         <f>SUM(AB81:AI81)</f>
         <v/>
       </c>
-      <c r="S81" s="88">
+      <c r="S81" s="81">
         <f>AK81</f>
         <v/>
       </c>
-      <c r="T81" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y81" s="88" t="n">
+      <c r="T81" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="81" t="n">
         <v>1145</v>
       </c>
-      <c r="AB81" s="88" t="n">
+      <c r="AB81" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="AC81" s="88" t="n">
+      <c r="AC81" s="81" t="n">
         <v>65</v>
       </c>
-      <c r="AD81" s="88" t="n">
+      <c r="AD81" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE81" s="88" t="n">
+      <c r="AE81" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF81" s="88" t="n">
+      <c r="AF81" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG81" s="88" t="n">
+      <c r="AG81" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="AI81" s="88" t="n">
+      <c r="AI81" s="81" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="79">
+      <c r="A82" s="72">
         <f>$D$21</f>
         <v/>
       </c>
-      <c r="B82" s="79">
+      <c r="B82" s="72">
         <f>B81+1</f>
         <v/>
       </c>
-      <c r="C82" s="79">
+      <c r="C82" s="72">
         <f>IF(K82="Vacant","Vac",IF(K82="Model","Model",IF(K82="Admin","Admin",IF(K82="Down","Down",IF(K82="Super","Super","Occ")))))</f>
         <v/>
       </c>
-      <c r="D82" s="79">
+      <c r="D82" s="72">
         <f>INDEX($C$5:$C$8,MATCH(I82,$D$5:$D$8,0))</f>
         <v/>
       </c>
-      <c r="E82" s="79">
+      <c r="E82" s="72">
         <f>INDEX($E$5:$E$8,MATCH(D82,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="F82" s="79">
+      <c r="F82" s="72">
         <f>INDEX($F$5:$F$8,MATCH(D82,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="G82" s="79">
+      <c r="G82" s="72">
         <f>INDEX($G$5:$G$8,MATCH(D82,$C$5:$C$8,0))</f>
         <v/>
       </c>
-      <c r="H82" s="79" t="inlineStr">
+      <c r="H82" s="72" t="inlineStr">
         <is>
           <t>CL - 816-3</t>
         </is>
       </c>
-      <c r="I82" s="79" t="inlineStr">
+      <c r="I82" s="72" t="inlineStr">
         <is>
           <t>1x1A_C</t>
         </is>
       </c>
-      <c r="J82" s="87" t="n">
+      <c r="J82" s="80" t="n">
         <v>775</v>
       </c>
-      <c r="K82" s="79" t="inlineStr">
+      <c r="K82" s="72" t="inlineStr">
         <is>
           <t>Bariff, Mae</t>
         </is>
       </c>
-      <c r="L82" s="88" t="n">
+      <c r="L82" s="81" t="n">
         <v>1189</v>
       </c>
-      <c r="M82" s="88">
+      <c r="M82" s="81">
         <f>Y82</f>
         <v/>
       </c>
-      <c r="N82" s="89" t="n">
+      <c r="N82" s="82" t="n">
         <v>45838</v>
       </c>
-      <c r="O82" s="89" t="n">
+      <c r="O82" s="82" t="n">
         <v>45838</v>
       </c>
-      <c r="P82" s="89" t="n">
+      <c r="P82" s="82" t="n">
         <v>46232</v>
       </c>
-      <c r="R82" s="88">
+      <c r="R82" s="81">
         <f>SUM(AB82:AI82)</f>
         <v/>
       </c>
-      <c r="S82" s="88">
+      <c r="S82" s="81">
         <f>AK82</f>
         <v/>
       </c>
-      <c r="T82" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" s="88" t="n">
+      <c r="T82" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="81" t="n">
         <v>1189</v>
       </c>
-      <c r="AB82" s="88" t="n">
+      <c r="AB82" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AD82" s="88" t="n">
+      <c r="AD82" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AE82" s="88" t="n">
+      <c r="AE82" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="AF82" s="88" t="n">
+      <c r="AF82" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AG82" s="88" t="n">
+      <c r="AG82" s="81" t="n">
         <v>65</v>
       </c>
-      <c r="AI82" s="88" t="n">
+      <c r="AI82" s="81" t="n">
         <v>150</v>
       </c>
     </row>

--- a/examples/outputs/Birgo RR Exhibits - Maven @ 806v07.01.26.xlsx
+++ b/examples/outputs/Birgo RR Exhibits - Maven @ 806v07.01.26.xlsx
@@ -6849,6 +6849,9 @@
       <c r="P33" s="82" t="n">
         <v>46248</v>
       </c>
+      <c r="Q33" s="82" t="n">
+        <v>46295</v>
+      </c>
       <c r="R33" s="81">
         <f>SUM(AB33:AI33)</f>
         <v/>
@@ -7403,6 +7406,9 @@
       <c r="P39" s="82" t="n">
         <v>46242</v>
       </c>
+      <c r="Q39" s="82" t="n">
+        <v>46295</v>
+      </c>
       <c r="R39" s="81">
         <f>SUM(AB39:AI39)</f>
         <v/>
@@ -8423,6 +8429,9 @@
       <c r="P50" s="82" t="n">
         <v>46224</v>
       </c>
+      <c r="Q50" s="82" t="n">
+        <v>46204</v>
+      </c>
       <c r="R50" s="81">
         <f>SUM(AB50:AI50)</f>
         <v/>

--- a/examples/outputs/Birgo RR Exhibits - Maven @ 806v07.01.26.xlsx
+++ b/examples/outputs/Birgo RR Exhibits - Maven @ 806v07.01.26.xlsx
@@ -915,13 +915,13 @@
         <v>1.80252000477726</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>29100.3</v>
+        <v>29475</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>1164.012</v>
+        <v>1179</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>1.815818045675777</v>
+        <v>1.839198801946836</v>
       </c>
       <c r="P6" s="11" t="n">
         <v>1325</v>
@@ -1065,13 +1065,13 @@
         <v>1.725271002710027</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>51660.3</v>
+        <v>52035</v>
       </c>
       <c r="N9" s="17" t="n">
-        <v>1230.007142857143</v>
+        <v>1238.928571428571</v>
       </c>
       <c r="O9" s="18" t="n">
-        <v>1.700414732892268</v>
+        <v>1.712748099140911</v>
       </c>
       <c r="P9" s="17" t="n">
         <v>1398.529411764706</v>
@@ -1184,7 +1184,7 @@
       <c r="E19" s="20" t="n"/>
       <c r="F19" s="20" t="n"/>
       <c r="G19" s="24" t="n">
-        <v>619923.6000000001</v>
+        <v>624420</v>
       </c>
     </row>
     <row r="20">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="W49" s="27" t="n">
-        <v>51660.3</v>
+        <v>52035</v>
       </c>
     </row>
     <row r="50">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="W50" s="27" t="n">
-        <v>-374.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1555,31 +1555,31 @@
         <v>1167.8</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>1164.012</v>
+        <v>1179</v>
       </c>
       <c r="M7" s="39" t="n">
-        <v>0.9967562938859393</v>
+        <v>1.009590683336188</v>
       </c>
       <c r="N7" s="38" t="n">
-        <v>1133.53</v>
+        <v>1171</v>
       </c>
       <c r="O7" s="40" t="n">
         <v>10</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>1121.144444444444</v>
+        <v>1162.777777777778</v>
       </c>
       <c r="Q7" s="40" t="n">
         <v>9</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>1140.328571428571</v>
+        <v>1193.857142857143</v>
       </c>
       <c r="S7" s="40" t="n">
         <v>7</v>
       </c>
       <c r="T7" s="11" t="n">
-        <v>1142.883333333333</v>
+        <v>1205.333333333333</v>
       </c>
       <c r="U7" s="40" t="n">
         <v>6</v>
@@ -1758,10 +1758,10 @@
         <v>1252.452380952381</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>1230.007142857143</v>
+        <v>1238.928571428571</v>
       </c>
       <c r="M10" s="43" t="n">
-        <v>0.9820789688801019</v>
+        <v>0.9892021367602607</v>
       </c>
       <c r="N10" s="42" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="AB66" s="27" t="n">
-        <v>51660.3</v>
+        <v>52035</v>
       </c>
     </row>
   </sheetData>
@@ -2063,13 +2063,13 @@
         <v>1.80252000477726</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>29100.3</v>
+        <v>29475</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>1164.012</v>
+        <v>1179</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>1.815818045675777</v>
+        <v>1.839198801946836</v>
       </c>
       <c r="P6" s="11" t="n">
         <v>1325</v>
@@ -2160,13 +2160,13 @@
         <v>1.725271002710027</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>51660.3</v>
+        <v>52035</v>
       </c>
       <c r="N8" s="17" t="n">
-        <v>1230.007142857143</v>
+        <v>1238.928571428571</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>1.700414732892268</v>
+        <v>1.712748099140911</v>
       </c>
       <c r="P8" s="17" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
       <c r="E18" s="20" t="n"/>
       <c r="F18" s="20" t="n"/>
       <c r="G18" s="24" t="n">
-        <v>619923.6000000001</v>
+        <v>624420</v>
       </c>
     </row>
     <row r="19">
@@ -3244,10 +3244,10 @@
         <v>1249</v>
       </c>
       <c r="W16" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="58" t="n">
         <v>-374.7</v>
-      </c>
-      <c r="X16" s="58" t="n">
-        <v>0</v>
       </c>
       <c r="Y16" s="58" t="n">
         <v>134</v>
@@ -5948,13 +5948,13 @@
         <v>66209</v>
       </c>
       <c r="V59" s="64" t="n">
-        <v>51660.3</v>
+        <v>52035</v>
       </c>
       <c r="W59" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="64" t="n">
         <v>-374.7</v>
-      </c>
-      <c r="X59" s="64" t="n">
-        <v>0</v>
       </c>
       <c r="Y59" s="64" t="n">
         <v>6361</v>
@@ -5983,7 +5983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:AK82"/>
+  <dimension ref="A3:AM82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.6" customWidth="1" min="1" max="1"/>
@@ -6014,7 +6014,7 @@
     <col width="13" customWidth="1" min="33" max="33"/>
     <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -6523,9 +6523,9 @@
           <t>Other Income</t>
         </is>
       </c>
-      <c r="AK30" s="67" t="inlineStr">
-        <is>
-          <t>Concessions</t>
+      <c r="AM30" s="67" t="inlineStr">
+        <is>
+          <t>Employee Discounts</t>
         </is>
       </c>
     </row>
@@ -6685,9 +6685,9 @@
           <t>Resident Utilities (Rubs) Charge</t>
         </is>
       </c>
-      <c r="AK31" s="67" t="inlineStr">
-        <is>
-          <t>Concession</t>
+      <c r="AM31" s="67" t="inlineStr">
+        <is>
+          <t>Employee Discount</t>
         </is>
       </c>
     </row>
@@ -6757,12 +6757,12 @@
         <f>SUM(AB32:AI32)</f>
         <v/>
       </c>
-      <c r="S32" s="81">
-        <f>AK32</f>
-        <v/>
-      </c>
-      <c r="T32" s="81" t="n">
-        <v>0</v>
+      <c r="S32" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="81">
+        <f>AM32</f>
+        <v/>
       </c>
       <c r="Y32" s="81" t="n">
         <v>1285</v>
@@ -6856,12 +6856,12 @@
         <f>SUM(AB33:AI33)</f>
         <v/>
       </c>
-      <c r="S33" s="81">
-        <f>AK33</f>
-        <v/>
-      </c>
-      <c r="T33" s="81" t="n">
-        <v>0</v>
+      <c r="S33" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="81">
+        <f>AM33</f>
+        <v/>
       </c>
       <c r="Y33" s="81" t="n">
         <v>1229</v>
@@ -6949,12 +6949,12 @@
         <f>SUM(AB34:AI34)</f>
         <v/>
       </c>
-      <c r="S34" s="81">
-        <f>AK34</f>
-        <v/>
-      </c>
-      <c r="T34" s="81" t="n">
-        <v>0</v>
+      <c r="S34" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="81">
+        <f>AM34</f>
+        <v/>
       </c>
       <c r="Y34" s="81" t="n">
         <v>1249</v>
@@ -7042,12 +7042,12 @@
         <f>SUM(AB35:AI35)</f>
         <v/>
       </c>
-      <c r="S35" s="81">
-        <f>AK35</f>
-        <v/>
-      </c>
-      <c r="T35" s="81" t="n">
-        <v>0</v>
+      <c r="S35" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="81">
+        <f>AM35</f>
+        <v/>
       </c>
       <c r="Y35" s="81" t="n">
         <v>1239</v>
@@ -7135,12 +7135,12 @@
         <f>SUM(AB36:AI36)</f>
         <v/>
       </c>
-      <c r="S36" s="81">
-        <f>AK36</f>
-        <v/>
-      </c>
-      <c r="T36" s="81" t="n">
-        <v>0</v>
+      <c r="S36" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="81">
+        <f>AM36</f>
+        <v/>
       </c>
       <c r="Y36" s="81" t="n">
         <v>1220</v>
@@ -7228,12 +7228,12 @@
         <f>SUM(AB37:AI37)</f>
         <v/>
       </c>
-      <c r="S37" s="81">
-        <f>AK37</f>
-        <v/>
-      </c>
-      <c r="T37" s="81" t="n">
-        <v>0</v>
+      <c r="S37" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="81">
+        <f>AM37</f>
+        <v/>
       </c>
       <c r="Y37" s="81" t="n">
         <v>1234</v>
@@ -7316,12 +7316,12 @@
         <f>SUM(AB38:AI38)</f>
         <v/>
       </c>
-      <c r="S38" s="85">
-        <f>AK38</f>
-        <v/>
-      </c>
-      <c r="T38" s="85" t="n">
-        <v>0</v>
+      <c r="S38" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="85">
+        <f>AM38</f>
+        <v/>
       </c>
       <c r="U38" s="86" t="n"/>
       <c r="V38" s="86" t="n"/>
@@ -7342,6 +7342,8 @@
       <c r="AI38" s="86" t="n"/>
       <c r="AJ38" s="86" t="n"/>
       <c r="AK38" s="86" t="n"/>
+      <c r="AL38" s="86" t="n"/>
+      <c r="AM38" s="86" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="72">
@@ -7413,12 +7415,12 @@
         <f>SUM(AB39:AI39)</f>
         <v/>
       </c>
-      <c r="S39" s="81">
-        <f>AK39</f>
-        <v/>
-      </c>
-      <c r="T39" s="81" t="n">
-        <v>0</v>
+      <c r="S39" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="81">
+        <f>AM39</f>
+        <v/>
       </c>
       <c r="Y39" s="81" t="n">
         <v>1230</v>
@@ -7506,12 +7508,12 @@
         <f>SUM(AB40:AI40)</f>
         <v/>
       </c>
-      <c r="S40" s="81">
-        <f>AK40</f>
-        <v/>
-      </c>
-      <c r="T40" s="81" t="n">
-        <v>0</v>
+      <c r="S40" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="81">
+        <f>AM40</f>
+        <v/>
       </c>
       <c r="Y40" s="81" t="n">
         <v>1249</v>
@@ -7531,7 +7533,7 @@
       <c r="AG40" s="81" t="n">
         <v>65</v>
       </c>
-      <c r="AK40" s="81" t="n">
+      <c r="AM40" s="81" t="n">
         <v>-374.7</v>
       </c>
     </row>
@@ -7602,12 +7604,12 @@
         <f>SUM(AB41:AI41)</f>
         <v/>
       </c>
-      <c r="S41" s="81">
-        <f>AK41</f>
-        <v/>
-      </c>
-      <c r="T41" s="81" t="n">
-        <v>0</v>
+      <c r="S41" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="81">
+        <f>AM41</f>
+        <v/>
       </c>
       <c r="Y41" s="81" t="n">
         <v>1325</v>
@@ -7693,12 +7695,12 @@
         <f>SUM(AB42:AI42)</f>
         <v/>
       </c>
-      <c r="S42" s="85">
-        <f>AK42</f>
-        <v/>
-      </c>
-      <c r="T42" s="85" t="n">
-        <v>0</v>
+      <c r="S42" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="85">
+        <f>AM42</f>
+        <v/>
       </c>
       <c r="U42" s="86" t="n"/>
       <c r="V42" s="86" t="n"/>
@@ -7719,6 +7721,8 @@
       <c r="AI42" s="86" t="n"/>
       <c r="AJ42" s="86" t="n"/>
       <c r="AK42" s="86" t="n"/>
+      <c r="AL42" s="86" t="n"/>
+      <c r="AM42" s="86" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="72">
@@ -7787,12 +7791,12 @@
         <f>SUM(AB43:AI43)</f>
         <v/>
       </c>
-      <c r="S43" s="81">
-        <f>AK43</f>
-        <v/>
-      </c>
-      <c r="T43" s="81" t="n">
-        <v>0</v>
+      <c r="S43" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="81">
+        <f>AM43</f>
+        <v/>
       </c>
       <c r="Y43" s="81" t="n">
         <v>1799</v>
@@ -7875,12 +7879,12 @@
         <f>SUM(AB44:AI44)</f>
         <v/>
       </c>
-      <c r="S44" s="85">
-        <f>AK44</f>
-        <v/>
-      </c>
-      <c r="T44" s="85" t="n">
-        <v>0</v>
+      <c r="S44" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="85">
+        <f>AM44</f>
+        <v/>
       </c>
       <c r="U44" s="86" t="n"/>
       <c r="V44" s="86" t="n"/>
@@ -7901,6 +7905,8 @@
       <c r="AI44" s="86" t="n"/>
       <c r="AJ44" s="86" t="n"/>
       <c r="AK44" s="86" t="n"/>
+      <c r="AL44" s="86" t="n"/>
+      <c r="AM44" s="86" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="83">
@@ -7964,12 +7970,12 @@
         <f>SUM(AB45:AI45)</f>
         <v/>
       </c>
-      <c r="S45" s="85">
-        <f>AK45</f>
-        <v/>
-      </c>
-      <c r="T45" s="85" t="n">
-        <v>0</v>
+      <c r="S45" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="85">
+        <f>AM45</f>
+        <v/>
       </c>
       <c r="U45" s="86" t="n"/>
       <c r="V45" s="86" t="n"/>
@@ -7990,6 +7996,8 @@
       <c r="AI45" s="86" t="n"/>
       <c r="AJ45" s="86" t="n"/>
       <c r="AK45" s="86" t="n"/>
+      <c r="AL45" s="86" t="n"/>
+      <c r="AM45" s="86" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="72">
@@ -8058,12 +8066,12 @@
         <f>SUM(AB46:AI46)</f>
         <v/>
       </c>
-      <c r="S46" s="81">
-        <f>AK46</f>
-        <v/>
-      </c>
-      <c r="T46" s="81" t="n">
-        <v>0</v>
+      <c r="S46" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="81">
+        <f>AM46</f>
+        <v/>
       </c>
       <c r="Y46" s="81" t="n">
         <v>1249</v>
@@ -8151,12 +8159,12 @@
         <f>SUM(AB47:AI47)</f>
         <v/>
       </c>
-      <c r="S47" s="81">
-        <f>AK47</f>
-        <v/>
-      </c>
-      <c r="T47" s="81" t="n">
-        <v>0</v>
+      <c r="S47" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="81">
+        <f>AM47</f>
+        <v/>
       </c>
       <c r="Y47" s="81" t="n">
         <v>1249</v>
@@ -8244,12 +8252,12 @@
         <f>SUM(AB48:AI48)</f>
         <v/>
       </c>
-      <c r="S48" s="81">
-        <f>AK48</f>
-        <v/>
-      </c>
-      <c r="T48" s="81" t="n">
-        <v>0</v>
+      <c r="S48" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="81">
+        <f>AM48</f>
+        <v/>
       </c>
       <c r="Y48" s="81" t="n">
         <v>1245</v>
@@ -8337,12 +8345,12 @@
         <f>SUM(AB49:AI49)</f>
         <v/>
       </c>
-      <c r="S49" s="81">
-        <f>AK49</f>
-        <v/>
-      </c>
-      <c r="T49" s="81" t="n">
-        <v>0</v>
+      <c r="S49" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="81">
+        <f>AM49</f>
+        <v/>
       </c>
       <c r="Y49" s="81" t="n">
         <v>1215</v>
@@ -8436,12 +8444,12 @@
         <f>SUM(AB50:AI50)</f>
         <v/>
       </c>
-      <c r="S50" s="81">
-        <f>AK50</f>
-        <v/>
-      </c>
-      <c r="T50" s="81" t="n">
-        <v>0</v>
+      <c r="S50" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="81">
+        <f>AM50</f>
+        <v/>
       </c>
       <c r="Y50" s="81" t="n">
         <v>1345</v>
@@ -8532,12 +8540,12 @@
         <f>SUM(AB51:AI51)</f>
         <v/>
       </c>
-      <c r="S51" s="81">
-        <f>AK51</f>
-        <v/>
-      </c>
-      <c r="T51" s="81" t="n">
-        <v>0</v>
+      <c r="S51" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="81">
+        <f>AM51</f>
+        <v/>
       </c>
       <c r="Y51" s="81" t="n">
         <v>1244</v>
@@ -8625,12 +8633,12 @@
         <f>SUM(AB52:AI52)</f>
         <v/>
       </c>
-      <c r="S52" s="81">
-        <f>AK52</f>
-        <v/>
-      </c>
-      <c r="T52" s="81" t="n">
-        <v>0</v>
+      <c r="S52" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="81">
+        <f>AM52</f>
+        <v/>
       </c>
       <c r="Y52" s="81" t="n">
         <v>1320</v>
@@ -8721,12 +8729,12 @@
         <f>SUM(AB53:AI53)</f>
         <v/>
       </c>
-      <c r="S53" s="81">
-        <f>AK53</f>
-        <v/>
-      </c>
-      <c r="T53" s="81" t="n">
-        <v>0</v>
+      <c r="S53" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="81">
+        <f>AM53</f>
+        <v/>
       </c>
       <c r="Y53" s="81" t="n">
         <v>1049</v>
@@ -8809,12 +8817,12 @@
         <f>SUM(AB54:AI54)</f>
         <v/>
       </c>
-      <c r="S54" s="85">
-        <f>AK54</f>
-        <v/>
-      </c>
-      <c r="T54" s="85" t="n">
-        <v>0</v>
+      <c r="S54" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="85">
+        <f>AM54</f>
+        <v/>
       </c>
       <c r="U54" s="86" t="n"/>
       <c r="V54" s="86" t="n"/>
@@ -8835,6 +8843,8 @@
       <c r="AI54" s="86" t="n"/>
       <c r="AJ54" s="86" t="n"/>
       <c r="AK54" s="86" t="n"/>
+      <c r="AL54" s="86" t="n"/>
+      <c r="AM54" s="86" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="83">
@@ -8898,12 +8908,12 @@
         <f>SUM(AB55:AI55)</f>
         <v/>
       </c>
-      <c r="S55" s="85">
-        <f>AK55</f>
-        <v/>
-      </c>
-      <c r="T55" s="85" t="n">
-        <v>0</v>
+      <c r="S55" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="85">
+        <f>AM55</f>
+        <v/>
       </c>
       <c r="U55" s="86" t="n"/>
       <c r="V55" s="86" t="n"/>
@@ -8924,6 +8934,8 @@
       <c r="AI55" s="86" t="n"/>
       <c r="AJ55" s="86" t="n"/>
       <c r="AK55" s="86" t="n"/>
+      <c r="AL55" s="86" t="n"/>
+      <c r="AM55" s="86" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="83">
@@ -8987,12 +8999,12 @@
         <f>SUM(AB56:AI56)</f>
         <v/>
       </c>
-      <c r="S56" s="85">
-        <f>AK56</f>
-        <v/>
-      </c>
-      <c r="T56" s="85" t="n">
-        <v>0</v>
+      <c r="S56" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="85">
+        <f>AM56</f>
+        <v/>
       </c>
       <c r="U56" s="86" t="n"/>
       <c r="V56" s="86" t="n"/>
@@ -9013,6 +9025,8 @@
       <c r="AI56" s="86" t="n"/>
       <c r="AJ56" s="86" t="n"/>
       <c r="AK56" s="86" t="n"/>
+      <c r="AL56" s="86" t="n"/>
+      <c r="AM56" s="86" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="72">
@@ -9081,12 +9095,12 @@
         <f>SUM(AB57:AI57)</f>
         <v/>
       </c>
-      <c r="S57" s="81">
-        <f>AK57</f>
-        <v/>
-      </c>
-      <c r="T57" s="81" t="n">
-        <v>0</v>
+      <c r="S57" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="81">
+        <f>AM57</f>
+        <v/>
       </c>
       <c r="Y57" s="81" t="n">
         <v>1139</v>
@@ -9174,12 +9188,12 @@
         <f>SUM(AB58:AI58)</f>
         <v/>
       </c>
-      <c r="S58" s="81">
-        <f>AK58</f>
-        <v/>
-      </c>
-      <c r="T58" s="81" t="n">
-        <v>0</v>
+      <c r="S58" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="81">
+        <f>AM58</f>
+        <v/>
       </c>
       <c r="Y58" s="81" t="n">
         <v>1099</v>
@@ -9264,12 +9278,12 @@
         <f>SUM(AB59:AI59)</f>
         <v/>
       </c>
-      <c r="S59" s="81">
-        <f>AK59</f>
-        <v/>
-      </c>
-      <c r="T59" s="81" t="n">
-        <v>0</v>
+      <c r="S59" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="81">
+        <f>AM59</f>
+        <v/>
       </c>
       <c r="Y59" s="81" t="n">
         <v>990</v>
@@ -9360,12 +9374,12 @@
         <f>SUM(AB60:AI60)</f>
         <v/>
       </c>
-      <c r="S60" s="81">
-        <f>AK60</f>
-        <v/>
-      </c>
-      <c r="T60" s="81" t="n">
-        <v>0</v>
+      <c r="S60" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="81">
+        <f>AM60</f>
+        <v/>
       </c>
       <c r="Y60" s="81" t="n">
         <v>1125</v>
@@ -9453,12 +9467,12 @@
         <f>SUM(AB61:AI61)</f>
         <v/>
       </c>
-      <c r="S61" s="81">
-        <f>AK61</f>
-        <v/>
-      </c>
-      <c r="T61" s="81" t="n">
-        <v>0</v>
+      <c r="S61" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="81">
+        <f>AM61</f>
+        <v/>
       </c>
       <c r="Y61" s="81" t="n">
         <v>1179</v>
@@ -9546,12 +9560,12 @@
         <f>SUM(AB62:AI62)</f>
         <v/>
       </c>
-      <c r="S62" s="81">
-        <f>AK62</f>
-        <v/>
-      </c>
-      <c r="T62" s="81" t="n">
-        <v>0</v>
+      <c r="S62" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="81">
+        <f>AM62</f>
+        <v/>
       </c>
       <c r="Y62" s="81" t="n">
         <v>1124</v>
@@ -9639,12 +9653,12 @@
         <f>SUM(AB63:AI63)</f>
         <v/>
       </c>
-      <c r="S63" s="81">
-        <f>AK63</f>
-        <v/>
-      </c>
-      <c r="T63" s="81" t="n">
-        <v>0</v>
+      <c r="S63" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="81">
+        <f>AM63</f>
+        <v/>
       </c>
       <c r="Y63" s="81" t="n">
         <v>1324</v>
@@ -9735,12 +9749,12 @@
         <f>SUM(AB64:AI64)</f>
         <v/>
       </c>
-      <c r="S64" s="81">
-        <f>AK64</f>
-        <v/>
-      </c>
-      <c r="T64" s="81" t="n">
-        <v>0</v>
+      <c r="S64" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="81">
+        <f>AM64</f>
+        <v/>
       </c>
       <c r="Y64" s="81" t="n">
         <v>1114</v>
@@ -9828,12 +9842,12 @@
         <f>SUM(AB65:AI65)</f>
         <v/>
       </c>
-      <c r="S65" s="81">
-        <f>AK65</f>
-        <v/>
-      </c>
-      <c r="T65" s="81" t="n">
-        <v>0</v>
+      <c r="S65" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="81">
+        <f>AM65</f>
+        <v/>
       </c>
       <c r="Y65" s="81" t="n">
         <v>1245</v>
@@ -9921,12 +9935,12 @@
         <f>SUM(AB66:AI66)</f>
         <v/>
       </c>
-      <c r="S66" s="81">
-        <f>AK66</f>
-        <v/>
-      </c>
-      <c r="T66" s="81" t="n">
-        <v>0</v>
+      <c r="S66" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="81">
+        <f>AM66</f>
+        <v/>
       </c>
       <c r="Y66" s="81" t="n">
         <v>1059</v>
@@ -10014,12 +10028,12 @@
         <f>SUM(AB67:AI67)</f>
         <v/>
       </c>
-      <c r="S67" s="81">
-        <f>AK67</f>
-        <v/>
-      </c>
-      <c r="T67" s="81" t="n">
-        <v>0</v>
+      <c r="S67" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="81">
+        <f>AM67</f>
+        <v/>
       </c>
       <c r="Y67" s="81" t="n">
         <v>1384</v>
@@ -10102,12 +10116,12 @@
         <f>SUM(AB68:AI68)</f>
         <v/>
       </c>
-      <c r="S68" s="85">
-        <f>AK68</f>
-        <v/>
-      </c>
-      <c r="T68" s="85" t="n">
-        <v>0</v>
+      <c r="S68" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="85">
+        <f>AM68</f>
+        <v/>
       </c>
       <c r="U68" s="86" t="n"/>
       <c r="V68" s="86" t="n"/>
@@ -10128,6 +10142,8 @@
       <c r="AI68" s="86" t="n"/>
       <c r="AJ68" s="86" t="n"/>
       <c r="AK68" s="86" t="n"/>
+      <c r="AL68" s="86" t="n"/>
+      <c r="AM68" s="86" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="72">
@@ -10196,12 +10212,12 @@
         <f>SUM(AB69:AI69)</f>
         <v/>
       </c>
-      <c r="S69" s="81">
-        <f>AK69</f>
-        <v/>
-      </c>
-      <c r="T69" s="81" t="n">
-        <v>0</v>
+      <c r="S69" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="81">
+        <f>AM69</f>
+        <v/>
       </c>
       <c r="Y69" s="81" t="n">
         <v>1184</v>
@@ -10292,12 +10308,12 @@
         <f>SUM(AB70:AI70)</f>
         <v/>
       </c>
-      <c r="S70" s="81">
-        <f>AK70</f>
-        <v/>
-      </c>
-      <c r="T70" s="81" t="n">
-        <v>0</v>
+      <c r="S70" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="81">
+        <f>AM70</f>
+        <v/>
       </c>
       <c r="Y70" s="81" t="n">
         <v>1255</v>
@@ -10385,12 +10401,12 @@
         <f>SUM(AB71:AI71)</f>
         <v/>
       </c>
-      <c r="S71" s="81">
-        <f>AK71</f>
-        <v/>
-      </c>
-      <c r="T71" s="81" t="n">
-        <v>0</v>
+      <c r="S71" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="81">
+        <f>AM71</f>
+        <v/>
       </c>
       <c r="Y71" s="81" t="n">
         <v>1149</v>
@@ -10473,12 +10489,12 @@
         <f>SUM(AB72:AI72)</f>
         <v/>
       </c>
-      <c r="S72" s="85">
-        <f>AK72</f>
-        <v/>
-      </c>
-      <c r="T72" s="85" t="n">
-        <v>0</v>
+      <c r="S72" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="85">
+        <f>AM72</f>
+        <v/>
       </c>
       <c r="U72" s="86" t="n"/>
       <c r="V72" s="86" t="n"/>
@@ -10499,6 +10515,8 @@
       <c r="AI72" s="86" t="n"/>
       <c r="AJ72" s="86" t="n"/>
       <c r="AK72" s="86" t="n"/>
+      <c r="AL72" s="86" t="n"/>
+      <c r="AM72" s="86" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="72">
@@ -10567,12 +10585,12 @@
         <f>SUM(AB73:AI73)</f>
         <v/>
       </c>
-      <c r="S73" s="81">
-        <f>AK73</f>
-        <v/>
-      </c>
-      <c r="T73" s="81" t="n">
-        <v>0</v>
+      <c r="S73" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" s="81">
+        <f>AM73</f>
+        <v/>
       </c>
       <c r="Y73" s="81" t="n">
         <v>1330</v>
@@ -10660,12 +10678,12 @@
         <f>SUM(AB74:AI74)</f>
         <v/>
       </c>
-      <c r="S74" s="81">
-        <f>AK74</f>
-        <v/>
-      </c>
-      <c r="T74" s="81" t="n">
-        <v>0</v>
+      <c r="S74" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="81">
+        <f>AM74</f>
+        <v/>
       </c>
       <c r="Y74" s="81" t="n">
         <v>1185</v>
@@ -10756,12 +10774,12 @@
         <f>SUM(AB75:AI75)</f>
         <v/>
       </c>
-      <c r="S75" s="81">
-        <f>AK75</f>
-        <v/>
-      </c>
-      <c r="T75" s="81" t="n">
-        <v>0</v>
+      <c r="S75" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" s="81">
+        <f>AM75</f>
+        <v/>
       </c>
       <c r="Y75" s="81" t="n">
         <v>1355</v>
@@ -10852,12 +10870,12 @@
         <f>SUM(AB76:AI76)</f>
         <v/>
       </c>
-      <c r="S76" s="81">
-        <f>AK76</f>
-        <v/>
-      </c>
-      <c r="T76" s="81" t="n">
-        <v>0</v>
+      <c r="S76" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="81">
+        <f>AM76</f>
+        <v/>
       </c>
       <c r="Y76" s="81" t="n">
         <v>1334</v>
@@ -10945,12 +10963,12 @@
         <f>SUM(AB77:AI77)</f>
         <v/>
       </c>
-      <c r="S77" s="81">
-        <f>AK77</f>
-        <v/>
-      </c>
-      <c r="T77" s="81" t="n">
-        <v>0</v>
+      <c r="S77" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="81">
+        <f>AM77</f>
+        <v/>
       </c>
       <c r="Y77" s="81" t="n">
         <v>1124</v>
@@ -11038,12 +11056,12 @@
         <f>SUM(AB78:AI78)</f>
         <v/>
       </c>
-      <c r="S78" s="81">
-        <f>AK78</f>
-        <v/>
-      </c>
-      <c r="T78" s="81" t="n">
-        <v>0</v>
+      <c r="S78" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="81">
+        <f>AM78</f>
+        <v/>
       </c>
       <c r="Y78" s="81" t="n">
         <v>1334</v>
@@ -11131,12 +11149,12 @@
         <f>SUM(AB79:AI79)</f>
         <v/>
       </c>
-      <c r="S79" s="81">
-        <f>AK79</f>
-        <v/>
-      </c>
-      <c r="T79" s="81" t="n">
-        <v>0</v>
+      <c r="S79" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="81">
+        <f>AM79</f>
+        <v/>
       </c>
       <c r="Y79" s="81" t="n">
         <v>1394</v>
@@ -11224,12 +11242,12 @@
         <f>SUM(AB80:AI80)</f>
         <v/>
       </c>
-      <c r="S80" s="81">
-        <f>AK80</f>
-        <v/>
-      </c>
-      <c r="T80" s="81" t="n">
-        <v>0</v>
+      <c r="S80" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="81">
+        <f>AM80</f>
+        <v/>
       </c>
       <c r="Y80" s="81" t="n">
         <v>1300</v>
@@ -11320,12 +11338,12 @@
         <f>SUM(AB81:AI81)</f>
         <v/>
       </c>
-      <c r="S81" s="81">
-        <f>AK81</f>
-        <v/>
-      </c>
-      <c r="T81" s="81" t="n">
-        <v>0</v>
+      <c r="S81" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="81">
+        <f>AM81</f>
+        <v/>
       </c>
       <c r="Y81" s="81" t="n">
         <v>1145</v>
@@ -11419,12 +11437,12 @@
         <f>SUM(AB82:AI82)</f>
         <v/>
       </c>
-      <c r="S82" s="81">
-        <f>AK82</f>
-        <v/>
-      </c>
-      <c r="T82" s="81" t="n">
-        <v>0</v>
+      <c r="S82" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="81">
+        <f>AM82</f>
+        <v/>
       </c>
       <c r="Y82" s="81" t="n">
         <v>1189</v>

--- a/examples/outputs/Birgo RR Exhibits - Maven @ 806v07.01.26.xlsx
+++ b/examples/outputs/Birgo RR Exhibits - Maven @ 806v07.01.26.xlsx
@@ -6647,12 +6647,12 @@
       </c>
       <c r="AB31" s="67" t="inlineStr">
         <is>
+          <t>Pet Rent</t>
+        </is>
+      </c>
+      <c r="AC31" s="67" t="inlineStr">
+        <is>
           <t>Building Protection Policy</t>
-        </is>
-      </c>
-      <c r="AC31" s="67" t="inlineStr">
-        <is>
-          <t>Pet Rent</t>
         </is>
       </c>
       <c r="AD31" s="67" t="inlineStr">
@@ -6768,10 +6768,10 @@
         <v>1285</v>
       </c>
       <c r="AB32" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC32" s="81" t="n">
         <v>15</v>
-      </c>
-      <c r="AC32" s="81" t="n">
-        <v>35</v>
       </c>
       <c r="AD32" s="81" t="n">
         <v>5</v>
@@ -6866,7 +6866,7 @@
       <c r="Y33" s="81" t="n">
         <v>1229</v>
       </c>
-      <c r="AB33" s="81" t="n">
+      <c r="AC33" s="81" t="n">
         <v>12</v>
       </c>
       <c r="AD33" s="81" t="n">
@@ -6959,7 +6959,7 @@
       <c r="Y34" s="81" t="n">
         <v>1249</v>
       </c>
-      <c r="AB34" s="81" t="n">
+      <c r="AC34" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD34" s="81" t="n">
@@ -7052,7 +7052,7 @@
       <c r="Y35" s="81" t="n">
         <v>1239</v>
       </c>
-      <c r="AB35" s="81" t="n">
+      <c r="AC35" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD35" s="81" t="n">
@@ -7145,7 +7145,7 @@
       <c r="Y36" s="81" t="n">
         <v>1220</v>
       </c>
-      <c r="AB36" s="81" t="n">
+      <c r="AC36" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD36" s="81" t="n">
@@ -7238,7 +7238,7 @@
       <c r="Y37" s="81" t="n">
         <v>1234</v>
       </c>
-      <c r="AB37" s="81" t="n">
+      <c r="AC37" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD37" s="81" t="n">
@@ -7425,7 +7425,7 @@
       <c r="Y39" s="81" t="n">
         <v>1230</v>
       </c>
-      <c r="AB39" s="81" t="n">
+      <c r="AC39" s="81" t="n">
         <v>12</v>
       </c>
       <c r="AD39" s="81" t="n">
@@ -7518,7 +7518,7 @@
       <c r="Y40" s="81" t="n">
         <v>1249</v>
       </c>
-      <c r="AB40" s="81" t="n">
+      <c r="AC40" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD40" s="81" t="n">
@@ -7615,10 +7615,10 @@
         <v>1325</v>
       </c>
       <c r="AB41" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC41" s="81" t="n">
         <v>12</v>
-      </c>
-      <c r="AC41" s="81" t="n">
-        <v>35</v>
       </c>
       <c r="AD41" s="81" t="n">
         <v>5</v>
@@ -7801,7 +7801,7 @@
       <c r="Y43" s="81" t="n">
         <v>1799</v>
       </c>
-      <c r="AB43" s="81" t="n">
+      <c r="AC43" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD43" s="81" t="n">
@@ -8076,7 +8076,7 @@
       <c r="Y46" s="81" t="n">
         <v>1249</v>
       </c>
-      <c r="AB46" s="81" t="n">
+      <c r="AC46" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD46" s="81" t="n">
@@ -8169,7 +8169,7 @@
       <c r="Y47" s="81" t="n">
         <v>1249</v>
       </c>
-      <c r="AB47" s="81" t="n">
+      <c r="AC47" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD47" s="81" t="n">
@@ -8262,7 +8262,7 @@
       <c r="Y48" s="81" t="n">
         <v>1245</v>
       </c>
-      <c r="AB48" s="81" t="n">
+      <c r="AC48" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD48" s="81" t="n">
@@ -8356,10 +8356,10 @@
         <v>1215</v>
       </c>
       <c r="AB49" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC49" s="81" t="n">
         <v>12</v>
-      </c>
-      <c r="AC49" s="81" t="n">
-        <v>30</v>
       </c>
       <c r="AD49" s="81" t="n">
         <v>5</v>
@@ -8455,10 +8455,10 @@
         <v>1345</v>
       </c>
       <c r="AB50" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC50" s="81" t="n">
         <v>12</v>
-      </c>
-      <c r="AC50" s="81" t="n">
-        <v>35</v>
       </c>
       <c r="AD50" s="81" t="n">
         <v>5</v>
@@ -8550,7 +8550,7 @@
       <c r="Y51" s="81" t="n">
         <v>1244</v>
       </c>
-      <c r="AB51" s="81" t="n">
+      <c r="AC51" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD51" s="81" t="n">
@@ -8644,10 +8644,10 @@
         <v>1320</v>
       </c>
       <c r="AB52" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC52" s="81" t="n">
         <v>12</v>
-      </c>
-      <c r="AC52" s="81" t="n">
-        <v>35</v>
       </c>
       <c r="AD52" s="81" t="n">
         <v>5</v>
@@ -8739,7 +8739,7 @@
       <c r="Y53" s="81" t="n">
         <v>1049</v>
       </c>
-      <c r="AB53" s="81" t="n">
+      <c r="AC53" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD53" s="81" t="n">
@@ -9105,7 +9105,7 @@
       <c r="Y57" s="81" t="n">
         <v>1139</v>
       </c>
-      <c r="AB57" s="81" t="n">
+      <c r="AC57" s="81" t="n">
         <v>12</v>
       </c>
       <c r="AD57" s="81" t="n">
@@ -9198,7 +9198,7 @@
       <c r="Y58" s="81" t="n">
         <v>1099</v>
       </c>
-      <c r="AB58" s="81" t="n">
+      <c r="AC58" s="81" t="n">
         <v>12</v>
       </c>
       <c r="AD58" s="81" t="n">
@@ -9288,7 +9288,7 @@
       <c r="Y59" s="81" t="n">
         <v>990</v>
       </c>
-      <c r="AB59" s="81" t="n">
+      <c r="AC59" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD59" s="81" t="n">
@@ -9384,7 +9384,7 @@
       <c r="Y60" s="81" t="n">
         <v>1125</v>
       </c>
-      <c r="AB60" s="81" t="n">
+      <c r="AC60" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD60" s="81" t="n">
@@ -9477,7 +9477,7 @@
       <c r="Y61" s="81" t="n">
         <v>1179</v>
       </c>
-      <c r="AB61" s="81" t="n">
+      <c r="AC61" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD61" s="81" t="n">
@@ -9570,7 +9570,7 @@
       <c r="Y62" s="81" t="n">
         <v>1124</v>
       </c>
-      <c r="AB62" s="81" t="n">
+      <c r="AC62" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD62" s="81" t="n">
@@ -9664,10 +9664,10 @@
         <v>1324</v>
       </c>
       <c r="AB63" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC63" s="81" t="n">
         <v>15</v>
-      </c>
-      <c r="AC63" s="81" t="n">
-        <v>30</v>
       </c>
       <c r="AD63" s="81" t="n">
         <v>5</v>
@@ -9759,7 +9759,7 @@
       <c r="Y64" s="81" t="n">
         <v>1114</v>
       </c>
-      <c r="AB64" s="81" t="n">
+      <c r="AC64" s="81" t="n">
         <v>12</v>
       </c>
       <c r="AD64" s="81" t="n">
@@ -9852,7 +9852,7 @@
       <c r="Y65" s="81" t="n">
         <v>1245</v>
       </c>
-      <c r="AB65" s="81" t="n">
+      <c r="AC65" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD65" s="81" t="n">
@@ -9945,7 +9945,7 @@
       <c r="Y66" s="81" t="n">
         <v>1059</v>
       </c>
-      <c r="AB66" s="81" t="n">
+      <c r="AC66" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD66" s="81" t="n">
@@ -10038,7 +10038,7 @@
       <c r="Y67" s="81" t="n">
         <v>1384</v>
       </c>
-      <c r="AB67" s="81" t="n">
+      <c r="AC67" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD67" s="81" t="n">
@@ -10223,10 +10223,10 @@
         <v>1184</v>
       </c>
       <c r="AB69" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC69" s="81" t="n">
         <v>15</v>
-      </c>
-      <c r="AC69" s="81" t="n">
-        <v>35</v>
       </c>
       <c r="AD69" s="81" t="n">
         <v>5</v>
@@ -10318,7 +10318,7 @@
       <c r="Y70" s="81" t="n">
         <v>1255</v>
       </c>
-      <c r="AB70" s="81" t="n">
+      <c r="AC70" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD70" s="81" t="n">
@@ -10411,7 +10411,7 @@
       <c r="Y71" s="81" t="n">
         <v>1149</v>
       </c>
-      <c r="AB71" s="81" t="n">
+      <c r="AC71" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD71" s="81" t="n">
@@ -10595,7 +10595,7 @@
       <c r="Y73" s="81" t="n">
         <v>1330</v>
       </c>
-      <c r="AB73" s="81" t="n">
+      <c r="AC73" s="81" t="n">
         <v>12</v>
       </c>
       <c r="AD73" s="81" t="n">
@@ -10689,10 +10689,10 @@
         <v>1185</v>
       </c>
       <c r="AB74" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC74" s="81" t="n">
         <v>12</v>
-      </c>
-      <c r="AC74" s="81" t="n">
-        <v>35</v>
       </c>
       <c r="AD74" s="81" t="n">
         <v>5</v>
@@ -10785,10 +10785,10 @@
         <v>1355</v>
       </c>
       <c r="AB75" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC75" s="81" t="n">
         <v>15</v>
-      </c>
-      <c r="AC75" s="81" t="n">
-        <v>35</v>
       </c>
       <c r="AD75" s="81" t="n">
         <v>5</v>
@@ -10880,7 +10880,7 @@
       <c r="Y76" s="81" t="n">
         <v>1334</v>
       </c>
-      <c r="AB76" s="81" t="n">
+      <c r="AC76" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD76" s="81" t="n">
@@ -10973,7 +10973,7 @@
       <c r="Y77" s="81" t="n">
         <v>1124</v>
       </c>
-      <c r="AB77" s="81" t="n">
+      <c r="AC77" s="81" t="n">
         <v>12</v>
       </c>
       <c r="AD77" s="81" t="n">
@@ -11066,7 +11066,7 @@
       <c r="Y78" s="81" t="n">
         <v>1334</v>
       </c>
-      <c r="AB78" s="81" t="n">
+      <c r="AC78" s="81" t="n">
         <v>12</v>
       </c>
       <c r="AD78" s="81" t="n">
@@ -11159,7 +11159,7 @@
       <c r="Y79" s="81" t="n">
         <v>1394</v>
       </c>
-      <c r="AB79" s="81" t="n">
+      <c r="AC79" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD79" s="81" t="n">
@@ -11252,7 +11252,7 @@
       <c r="Y80" s="81" t="n">
         <v>1300</v>
       </c>
-      <c r="AB80" s="81" t="n">
+      <c r="AC80" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD80" s="81" t="n">
@@ -11349,10 +11349,10 @@
         <v>1145</v>
       </c>
       <c r="AB81" s="81" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC81" s="81" t="n">
         <v>12</v>
-      </c>
-      <c r="AC81" s="81" t="n">
-        <v>65</v>
       </c>
       <c r="AD81" s="81" t="n">
         <v>5</v>
@@ -11447,7 +11447,7 @@
       <c r="Y82" s="81" t="n">
         <v>1189</v>
       </c>
-      <c r="AB82" s="81" t="n">
+      <c r="AC82" s="81" t="n">
         <v>15</v>
       </c>
       <c r="AD82" s="81" t="n">
